--- a/output/Tables/Best practice/cases_prev_target_area_age.xlsx
+++ b/output/Tables/Best practice/cases_prev_target_area_age.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O148"/>
+  <dimension ref="A1:O127"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -448,22 +448,22 @@
         </is>
       </c>
       <c r="D2">
-        <v>4.970926501168741</v>
+        <v>184.0297908221409</v>
       </c>
       <c r="E2">
-        <v>5.067145000838581</v>
+        <v>158.468138051187</v>
       </c>
       <c r="F2">
-        <v>4.934334599652514</v>
+        <v>207.9507005595431</v>
       </c>
       <c r="G2">
-        <v>48.77424073993396</v>
+        <v>10497.97547768416</v>
       </c>
       <c r="H2">
-        <v>49.75250689896501</v>
+        <v>9039.811542596595</v>
       </c>
       <c r="I2">
-        <v>48.38556713132133</v>
+        <v>11862.54326154825</v>
       </c>
       <c r="J2">
         <v>0</v>
@@ -475,13 +475,13 @@
         <v>0</v>
       </c>
       <c r="M2">
-        <v>6486974.018411216</v>
+        <v>1396230738.531993</v>
       </c>
       <c r="N2">
-        <v>6617083.417562346</v>
+        <v>1202294935.165347</v>
       </c>
       <c r="O2">
-        <v>6435280.428465737</v>
+        <v>1577718253.785918</v>
       </c>
     </row>
     <row r="3">
@@ -501,22 +501,22 @@
         </is>
       </c>
       <c r="D3">
-        <v>24.41476347463195</v>
+        <v>125.6772031842816</v>
       </c>
       <c r="E3">
-        <v>23.58127318609526</v>
+        <v>120.6843500203786</v>
       </c>
       <c r="F3">
-        <v>25.3679023321041</v>
+        <v>131.1925729230239</v>
       </c>
       <c r="G3">
-        <v>232.5078718703804</v>
+        <v>7134.554233129396</v>
       </c>
       <c r="H3">
-        <v>224.5501316862081</v>
+        <v>6851.115544382604</v>
       </c>
       <c r="I3">
-        <v>241.6023525993418</v>
+        <v>7447.655603304865</v>
       </c>
       <c r="J3">
         <v>0</v>
@@ -528,13 +528,13 @@
         <v>0</v>
       </c>
       <c r="M3">
-        <v>30923546.95876059</v>
+        <v>948895713.0062097</v>
       </c>
       <c r="N3">
-        <v>29865167.51426568</v>
+        <v>911198367.4028863</v>
       </c>
       <c r="O3">
-        <v>32133112.89571246</v>
+        <v>990538195.239547</v>
       </c>
     </row>
     <row r="4">
@@ -554,22 +554,22 @@
         </is>
       </c>
       <c r="D4">
-        <v>181.1239710120057</v>
+        <v>272.2016759993704</v>
       </c>
       <c r="E4">
-        <v>166.0808728687371</v>
+        <v>222.4626736210622</v>
       </c>
       <c r="F4">
-        <v>195.8915415970363</v>
+        <v>317.9538950406766</v>
       </c>
       <c r="G4">
-        <v>1718.697109044016</v>
+        <v>15503.52272221162</v>
       </c>
       <c r="H4">
-        <v>1576.216224670272</v>
+        <v>12670.58736014563</v>
       </c>
       <c r="I4">
-        <v>1858.598550230109</v>
+        <v>18109.38679301233</v>
       </c>
       <c r="J4">
         <v>0</v>
@@ -581,13 +581,13 @@
         <v>0</v>
       </c>
       <c r="M4">
-        <v>228586715.5028541</v>
+        <v>2061968522.054146</v>
       </c>
       <c r="N4">
-        <v>209636757.8811462</v>
+        <v>1685188118.899369</v>
       </c>
       <c r="O4">
-        <v>247193607.1806045</v>
+        <v>2408548443.470641</v>
       </c>
     </row>
     <row r="5">
@@ -607,22 +607,22 @@
         </is>
       </c>
       <c r="D5">
-        <v>29.68736154977378</v>
+        <v>423.6560280423507</v>
       </c>
       <c r="E5">
-        <v>30.34242253579681</v>
+        <v>374.1107619285679</v>
       </c>
       <c r="F5">
-        <v>29.3991571699538</v>
+        <v>470.646258824306</v>
       </c>
       <c r="G5">
-        <v>231.7782341599894</v>
+        <v>19460.46263922942</v>
       </c>
       <c r="H5">
-        <v>236.5284676845395</v>
+        <v>17184.62154093741</v>
       </c>
       <c r="I5">
-        <v>229.8439078909026</v>
+        <v>21618.93925708036</v>
       </c>
       <c r="J5">
         <v>0</v>
@@ -634,13 +634,13 @@
         <v>0</v>
       </c>
       <c r="M5">
-        <v>30826505.14327859</v>
+        <v>2588241531.017513</v>
       </c>
       <c r="N5">
-        <v>31458286.20204375</v>
+        <v>2285554664.944675</v>
       </c>
       <c r="O5">
-        <v>30569239.74949004</v>
+        <v>2875318921.191688</v>
       </c>
     </row>
     <row r="6">
@@ -660,22 +660,22 @@
         </is>
       </c>
       <c r="D6">
-        <v>31.97832233469884</v>
+        <v>416.5691614117125</v>
       </c>
       <c r="E6">
-        <v>30.85782642896726</v>
+        <v>369.5751040134195</v>
       </c>
       <c r="F6">
-        <v>33.25225248804212</v>
+        <v>461.2775696290753</v>
       </c>
       <c r="G6">
-        <v>254.5109920925613</v>
+        <v>19125.54070477013</v>
       </c>
       <c r="H6">
-        <v>245.723622770651</v>
+        <v>16967.94758240013</v>
       </c>
       <c r="I6">
-        <v>264.5367229205218</v>
+        <v>21178.19500666059</v>
       </c>
       <c r="J6">
         <v>0</v>
@@ -687,13 +687,13 @@
         <v>0</v>
       </c>
       <c r="M6">
-        <v>33849961.94831065</v>
+        <v>2543696913.734427</v>
       </c>
       <c r="N6">
-        <v>32681241.82849659</v>
+        <v>2256737028.459217</v>
       </c>
       <c r="O6">
-        <v>35183384.1484294</v>
+        <v>2816699935.885859</v>
       </c>
     </row>
     <row r="7">
@@ -713,22 +713,22 @@
         </is>
       </c>
       <c r="D7">
-        <v>311.8669651860631</v>
+        <v>726.8503517840966</v>
       </c>
       <c r="E7">
-        <v>274.3027306619082</v>
+        <v>556.0948523070297</v>
       </c>
       <c r="F7">
-        <v>347.4331145075519</v>
+        <v>882.3809962541134</v>
       </c>
       <c r="G7">
-        <v>2421.738280272714</v>
+        <v>33509.6114144764</v>
       </c>
       <c r="H7">
-        <v>2132.022406936088</v>
+        <v>25637.35762754975</v>
       </c>
       <c r="I7">
-        <v>2696.199985035434</v>
+        <v>40679.96146857048</v>
       </c>
       <c r="J7">
         <v>0</v>
@@ -740,13 +740,13 @@
         <v>0</v>
       </c>
       <c r="M7">
-        <v>322091191.2762709</v>
+        <v>4456778318.125361</v>
       </c>
       <c r="N7">
-        <v>283558980.1224998</v>
+        <v>3409768564.464117</v>
       </c>
       <c r="O7">
-        <v>358594598.0097128</v>
+        <v>5410434875.319874</v>
       </c>
     </row>
     <row r="8">
@@ -766,22 +766,22 @@
         </is>
       </c>
       <c r="D8">
-        <v>141.1904121480072</v>
+        <v>1503.788598607241</v>
       </c>
       <c r="E8">
-        <v>142.8172105703249</v>
+        <v>1289.144674303293</v>
       </c>
       <c r="F8">
-        <v>141.1100880699659</v>
+        <v>1704.268448069612</v>
       </c>
       <c r="G8">
-        <v>800.4089110568954</v>
+        <v>55179.01918704273</v>
       </c>
       <c r="H8">
-        <v>811.4592217976747</v>
+        <v>47303.01771415012</v>
       </c>
       <c r="I8">
-        <v>798.3683185181974</v>
+        <v>62535.29351333099</v>
       </c>
       <c r="J8">
         <v>0</v>
@@ -793,13 +793,13 @@
         <v>0</v>
       </c>
       <c r="M8">
-        <v>106454385.1705671</v>
+        <v>7338809551.876683</v>
       </c>
       <c r="N8">
-        <v>107924076.4990907</v>
+        <v>6291301355.981966</v>
       </c>
       <c r="O8">
-        <v>106182986.3629203</v>
+        <v>8317194037.273023</v>
       </c>
     </row>
     <row r="9">
@@ -819,22 +819,22 @@
         </is>
       </c>
       <c r="D9">
-        <v>121.1153308248536</v>
+        <v>1206.08232659046</v>
       </c>
       <c r="E9">
-        <v>119.217403936597</v>
+        <v>1103.553010966539</v>
       </c>
       <c r="F9">
-        <v>123.9038396809448</v>
+        <v>1306.412284081256</v>
       </c>
       <c r="G9">
-        <v>746.1791946137787</v>
+        <v>43974.86365754621</v>
       </c>
       <c r="H9">
-        <v>734.4993135434006</v>
+        <v>40236.55112608794</v>
       </c>
       <c r="I9">
-        <v>763.3473878795394</v>
+        <v>47632.98558185762</v>
       </c>
       <c r="J9">
         <v>0</v>
@@ -846,13 +846,13 @@
         <v>0</v>
       </c>
       <c r="M9">
-        <v>99241832.88363257</v>
+        <v>5848656866.453646</v>
       </c>
       <c r="N9">
-        <v>97688408.70127228</v>
+        <v>5351461299.769695</v>
       </c>
       <c r="O9">
-        <v>101525202.5879787</v>
+        <v>6335187082.387063</v>
       </c>
     </row>
     <row r="10">
@@ -872,22 +872,22 @@
         </is>
       </c>
       <c r="D10">
-        <v>673.3173140123891</v>
+        <v>1957.015374270655</v>
       </c>
       <c r="E10">
-        <v>598.0915750525303</v>
+        <v>1492.542659390586</v>
       </c>
       <c r="F10">
-        <v>744.9927896310937</v>
+        <v>2379.322482136924</v>
       </c>
       <c r="G10">
-        <v>4268.523317724697</v>
+        <v>71417.36914009105</v>
       </c>
       <c r="H10">
-        <v>3794.461838971382</v>
+        <v>54467.36467400323</v>
       </c>
       <c r="I10">
-        <v>4720.448325058966</v>
+        <v>86828.62395673255</v>
       </c>
       <c r="J10">
         <v>0</v>
@@ -899,13 +899,13 @@
         <v>0</v>
       </c>
       <c r="M10">
-        <v>567713601.2573848</v>
+        <v>9498510095.632109</v>
       </c>
       <c r="N10">
-        <v>504663424.5831938</v>
+        <v>7244159501.64243</v>
       </c>
       <c r="O10">
-        <v>627819627.2328426</v>
+        <v>11548206986.24543</v>
       </c>
     </row>
     <row r="11">
@@ -925,22 +925,22 @@
         </is>
       </c>
       <c r="D11">
-        <v>272.6300945315634</v>
+        <v>2909.842257110345</v>
       </c>
       <c r="E11">
-        <v>274.4001966415757</v>
+        <v>2522.681343039547</v>
       </c>
       <c r="F11">
-        <v>273.6656443982849</v>
+        <v>3273.293882534601</v>
       </c>
       <c r="G11">
-        <v>1281.173877869877</v>
+        <v>77467.68185808836</v>
       </c>
       <c r="H11">
-        <v>1286.504055956646</v>
+        <v>67160.43635505956</v>
       </c>
       <c r="I11">
-        <v>1288.632328603621</v>
+        <v>87143.72351305129</v>
       </c>
       <c r="J11">
         <v>0</v>
@@ -952,13 +952,13 @@
         <v>0</v>
       </c>
       <c r="M11">
-        <v>170396125.7566937</v>
+        <v>10303201687.12575</v>
       </c>
       <c r="N11">
-        <v>171105039.4422339</v>
+        <v>8932338035.222921</v>
       </c>
       <c r="O11">
-        <v>171388099.7042816</v>
+        <v>11590115227.23582</v>
       </c>
     </row>
     <row r="12">
@@ -978,22 +978,22 @@
         </is>
       </c>
       <c r="D12">
-        <v>516.445045866781</v>
+        <v>2127.507217994631</v>
       </c>
       <c r="E12">
-        <v>504.2471721766867</v>
+        <v>2087.878605485205</v>
       </c>
       <c r="F12">
-        <v>531.8951868072173</v>
+        <v>2181.920916676962</v>
       </c>
       <c r="G12">
-        <v>2337.666583380209</v>
+        <v>56251.37102312798</v>
       </c>
       <c r="H12">
-        <v>2280.336945656417</v>
+        <v>55203.58901489555</v>
       </c>
       <c r="I12">
-        <v>2409.436921056645</v>
+        <v>57690.07126697757</v>
       </c>
       <c r="J12">
         <v>0</v>
@@ -1005,13 +1005,13 @@
         <v>0</v>
       </c>
       <c r="M12">
-        <v>310909655.5895677</v>
+        <v>7481432346.076021</v>
       </c>
       <c r="N12">
-        <v>303284813.7723035</v>
+        <v>7342077338.981109</v>
       </c>
       <c r="O12">
-        <v>320455110.5005338</v>
+        <v>7672779478.508017</v>
       </c>
     </row>
     <row r="13">
@@ -1031,22 +1031,22 @@
         </is>
       </c>
       <c r="D13">
-        <v>1065.370269415517</v>
+        <v>3493.570314426226</v>
       </c>
       <c r="E13">
-        <v>998.6101037619801</v>
+        <v>2695.870864716214</v>
       </c>
       <c r="F13">
-        <v>1133.371516067516</v>
+        <v>4219.674616467965</v>
       </c>
       <c r="G13">
-        <v>4759.650138800041</v>
+        <v>92476.73733384541</v>
       </c>
       <c r="H13">
-        <v>4463.006569766266</v>
+        <v>71361.19196251886</v>
       </c>
       <c r="I13">
-        <v>5062.051891878453</v>
+        <v>111697.1195713551</v>
       </c>
       <c r="J13">
         <v>0</v>
@@ -1058,13 +1058,13 @@
         <v>0</v>
       </c>
       <c r="M13">
-        <v>633033468.4604053</v>
+        <v>12299406065.40144</v>
       </c>
       <c r="N13">
-        <v>593579873.7789134</v>
+        <v>9491038531.015009</v>
       </c>
       <c r="O13">
-        <v>673252901.6198342</v>
+        <v>14855716902.99023</v>
       </c>
     </row>
     <row r="14">
@@ -1084,22 +1084,22 @@
         </is>
       </c>
       <c r="D14">
-        <v>493.5311452877883</v>
+        <v>5483.853455551071</v>
       </c>
       <c r="E14">
-        <v>492.4446628004433</v>
+        <v>4842.53370367655</v>
       </c>
       <c r="F14">
-        <v>499.1247049780873</v>
+        <v>6092.100529578328</v>
       </c>
       <c r="G14">
-        <v>1142.960679211078</v>
+        <v>90651.98160057292</v>
       </c>
       <c r="H14">
-        <v>1145.552321714148</v>
+        <v>80050.51188256592</v>
       </c>
       <c r="I14">
-        <v>1151.483673568714</v>
+        <v>100706.7365297927</v>
       </c>
       <c r="J14">
         <v>0</v>
@@ -1111,13 +1111,13 @@
         <v>0</v>
       </c>
       <c r="M14">
-        <v>152013770.3350734</v>
+        <v>12056713552.8762</v>
       </c>
       <c r="N14">
-        <v>152358458.7879817</v>
+        <v>10646718080.38127</v>
       </c>
       <c r="O14">
-        <v>153147328.5846389</v>
+        <v>13393995958.46243</v>
       </c>
     </row>
     <row r="15">
@@ -1137,22 +1137,22 @@
         </is>
       </c>
       <c r="D15">
-        <v>1118.284503840223</v>
+        <v>4440.597504877544</v>
       </c>
       <c r="E15">
-        <v>1110.569128999329</v>
+        <v>4347.396024316141</v>
       </c>
       <c r="F15">
-        <v>1135.512272760064</v>
+        <v>4563.270681242146</v>
       </c>
       <c r="G15">
-        <v>3245.269248148369</v>
+        <v>75313.91689811682</v>
       </c>
       <c r="H15">
-        <v>3227.799980164469</v>
+        <v>73733.19075617942</v>
       </c>
       <c r="I15">
-        <v>3290.995866641347</v>
+        <v>77394.49218110608</v>
       </c>
       <c r="J15">
         <v>0</v>
@@ -1164,13 +1164,13 @@
         <v>0</v>
       </c>
       <c r="M15">
-        <v>431620810.003733</v>
+        <v>10016750947.44954</v>
       </c>
       <c r="N15">
-        <v>429297397.3618744</v>
+        <v>9806514370.571863</v>
       </c>
       <c r="O15">
-        <v>437702450.2632991</v>
+        <v>10293467460.08711</v>
       </c>
     </row>
     <row r="16">
@@ -1190,22 +1190,22 @@
         </is>
       </c>
       <c r="D16">
-        <v>1916.879680004615</v>
+        <v>5366.253777700224</v>
       </c>
       <c r="E16">
-        <v>1819.43900354523</v>
+        <v>4402.554627554245</v>
       </c>
       <c r="F16">
-        <v>2019.536962635825</v>
+        <v>6253.552183834168</v>
       </c>
       <c r="G16">
-        <v>5340.935547595292</v>
+        <v>90963.70453714528</v>
       </c>
       <c r="H16">
-        <v>5048.082286583063</v>
+        <v>74627.9797675007</v>
       </c>
       <c r="I16">
-        <v>5645.502639040727</v>
+        <v>106004.355500626</v>
       </c>
       <c r="J16">
         <v>0</v>
@@ -1217,13 +1217,13 @@
         <v>0</v>
       </c>
       <c r="M16">
-        <v>710344427.8301737</v>
+        <v>12098172703.44032</v>
       </c>
       <c r="N16">
-        <v>671394944.1155474</v>
+        <v>9925521309.077593</v>
       </c>
       <c r="O16">
-        <v>750851850.9924166</v>
+        <v>14098579281.58325</v>
       </c>
     </row>
     <row r="17">
@@ -1243,22 +1243,22 @@
         </is>
       </c>
       <c r="D17">
-        <v>112.9601427420478</v>
+        <v>5677.779648050745</v>
       </c>
       <c r="E17">
-        <v>124.7571465904606</v>
+        <v>5680.032156242519</v>
       </c>
       <c r="F17">
-        <v>103.7925260930866</v>
+        <v>5729.288084721476</v>
       </c>
       <c r="G17">
-        <v>173.7881417465991</v>
+        <v>39984.07069352455</v>
       </c>
       <c r="H17">
-        <v>192.0863450509398</v>
+        <v>39999.93331101951</v>
       </c>
       <c r="I17">
-        <v>159.5549924876111</v>
+        <v>40346.80350473229</v>
       </c>
       <c r="J17">
         <v>0</v>
@@ -1270,13 +1270,13 @@
         <v>0</v>
       </c>
       <c r="M17">
-        <v>23113822.85229769</v>
+        <v>5317881402.238765</v>
       </c>
       <c r="N17">
-        <v>25547483.89177499</v>
+        <v>5319991130.365595</v>
       </c>
       <c r="O17">
-        <v>21220814.00085228</v>
+        <v>5366124866.129395</v>
       </c>
     </row>
     <row r="18">
@@ -1296,22 +1296,22 @@
         </is>
       </c>
       <c r="D18">
-        <v>1864.393927427088</v>
+        <v>5063.39385099504</v>
       </c>
       <c r="E18">
-        <v>1957.146681786433</v>
+        <v>5223.847843349879</v>
       </c>
       <c r="F18">
-        <v>1801.495849304209</v>
+        <v>4971.88485099111</v>
       </c>
       <c r="G18">
-        <v>2275.902101417014</v>
+        <v>36698.09950871272</v>
       </c>
       <c r="H18">
-        <v>2387.537041125838</v>
+        <v>37861.02634223382</v>
       </c>
       <c r="I18">
-        <v>2200.500120355502</v>
+        <v>36034.86720111192</v>
       </c>
       <c r="J18">
         <v>0</v>
@@ -1323,13 +1323,13 @@
         <v>0</v>
       </c>
       <c r="M18">
-        <v>302694979.4884629</v>
+        <v>4880847234.658792</v>
       </c>
       <c r="N18">
-        <v>317542426.4697365</v>
+        <v>5035516503.517098</v>
       </c>
       <c r="O18">
-        <v>292666516.0072818</v>
+        <v>4792637337.747886</v>
       </c>
     </row>
     <row r="19">
@@ -1349,22 +1349,22 @@
         </is>
       </c>
       <c r="D19">
-        <v>965.3535112599202</v>
+        <v>6277.883809061845</v>
       </c>
       <c r="E19">
-        <v>1013.634281407242</v>
+        <v>5771.856099969797</v>
       </c>
       <c r="F19">
-        <v>932.5700052548666</v>
+        <v>6776.111969480356</v>
       </c>
       <c r="G19">
-        <v>1347.945220390756</v>
+        <v>46646.0997561085</v>
       </c>
       <c r="H19">
-        <v>1415.182319773572</v>
+        <v>42886.19917247701</v>
       </c>
       <c r="I19">
-        <v>1302.322419209953</v>
+        <v>50348.04792511377</v>
       </c>
       <c r="J19">
         <v>0</v>
@@ -1376,13 +1376,13 @@
         <v>0</v>
       </c>
       <c r="M19">
-        <v>179276714.3119705</v>
+        <v>6203931267.56243</v>
       </c>
       <c r="N19">
-        <v>188219248.5298851</v>
+        <v>5703864489.939443</v>
       </c>
       <c r="O19">
-        <v>173208881.7549237</v>
+        <v>6696290374.040131</v>
       </c>
     </row>
     <row r="20">
@@ -1402,22 +1402,22 @@
         </is>
       </c>
       <c r="D20">
-        <v>326.136659804187</v>
+        <v>6914.503982485444</v>
       </c>
       <c r="E20">
-        <v>358.5762021798789</v>
+        <v>7050.093686732139</v>
       </c>
       <c r="F20">
-        <v>301.0731477050436</v>
+        <v>6861.990101827048</v>
       </c>
       <c r="G20">
-        <v>15.73167453313277</v>
+        <v>5280.33572809031</v>
       </c>
       <c r="H20">
-        <v>17.41328609839178</v>
+        <v>5383.880271778272</v>
       </c>
       <c r="I20">
-        <v>14.42134333187611</v>
+        <v>5240.232935328376</v>
       </c>
       <c r="J20">
         <v>0</v>
@@ -1429,13 +1429,13 @@
         <v>0</v>
       </c>
       <c r="M20">
-        <v>2092312.712906658</v>
+        <v>702284651.8360113</v>
       </c>
       <c r="N20">
-        <v>2315967.051086107</v>
+        <v>716056076.1465101</v>
       </c>
       <c r="O20">
-        <v>1918038.663139523</v>
+        <v>696950980.398674</v>
       </c>
     </row>
     <row r="21">
@@ -1455,22 +1455,22 @@
         </is>
       </c>
       <c r="D21">
-        <v>7860.871411142093</v>
+        <v>5990.296033973489</v>
       </c>
       <c r="E21">
-        <v>8479.565229538392</v>
+        <v>6573.322859446153</v>
       </c>
       <c r="F21">
-        <v>7398.264574458593</v>
+        <v>5541.030202217163</v>
       </c>
       <c r="G21">
-        <v>881.6670539229833</v>
+        <v>4402.289309390806</v>
       </c>
       <c r="H21">
-        <v>952.2597205470934</v>
+        <v>4830.757743389689</v>
       </c>
       <c r="I21">
-        <v>828.7405272942868</v>
+        <v>4072.122293103374</v>
       </c>
       <c r="J21">
         <v>0</v>
@@ -1482,13 +1482,13 @@
         <v>0</v>
       </c>
       <c r="M21">
-        <v>117261718.1717568</v>
+        <v>585504478.1489772</v>
       </c>
       <c r="N21">
-        <v>126650542.8327634</v>
+        <v>642490779.8708287</v>
       </c>
       <c r="O21">
-        <v>110222490.1301402</v>
+        <v>541592264.9827487</v>
       </c>
     </row>
     <row r="22">
@@ -1508,22 +1508,22 @@
         </is>
       </c>
       <c r="D22">
-        <v>1570.382499897635</v>
+        <v>7269.88116884159</v>
       </c>
       <c r="E22">
-        <v>1704.899280945912</v>
+        <v>7255.394201162701</v>
       </c>
       <c r="F22">
-        <v>1468.502702157824</v>
+        <v>7350.903042680936</v>
       </c>
       <c r="G22">
-        <v>205.4873350781146</v>
+        <v>6076.118246232678</v>
       </c>
       <c r="H22">
-        <v>226.0641744118261</v>
+        <v>6064.010135164301</v>
       </c>
       <c r="I22">
-        <v>189.576183094056</v>
+        <v>6143.835788589383</v>
       </c>
       <c r="J22">
         <v>0</v>
@@ -1535,19 +1535,19 @@
         <v>0</v>
       </c>
       <c r="M22">
-        <v>27329815.56538925</v>
+        <v>808123726.7489462</v>
       </c>
       <c r="N22">
-        <v>30066535.19677287</v>
+        <v>806513347.9768519</v>
       </c>
       <c r="O22">
-        <v>25213632.35150945</v>
+        <v>817130159.8823879</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>bc</t>
+          <t>cvd</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1561,46 +1561,46 @@
         </is>
       </c>
       <c r="D23">
-        <v>0.02790282175082632</v>
+        <v>70.00621305999313</v>
       </c>
       <c r="E23">
-        <v>0.006081492880741414</v>
+        <v>42.55000000855148</v>
       </c>
       <c r="F23">
-        <v>0.05628055138491281</v>
+        <v>100.5398414677183</v>
       </c>
       <c r="G23">
-        <v>0.01882621556664465</v>
+        <v>261.7454460585686</v>
       </c>
       <c r="H23">
-        <v>0.003085908229237306</v>
+        <v>124.8639004804226</v>
       </c>
       <c r="I23">
-        <v>0.04804208772314022</v>
+        <v>458.2273434492053</v>
       </c>
       <c r="J23">
-        <v>1230.151702528681</v>
+        <v>3899486.07986773</v>
       </c>
       <c r="K23">
-        <v>268.1147766332467</v>
+        <v>2370120.100476335</v>
       </c>
       <c r="L23">
-        <v>2481.240668906651</v>
+        <v>5600270.249434839</v>
       </c>
       <c r="M23">
-        <v>2503.886670363739</v>
+        <v>34812144.32578963</v>
       </c>
       <c r="N23">
-        <v>410.4257944885617</v>
+        <v>16606898.76389621</v>
       </c>
       <c r="O23">
-        <v>6389.597667177649</v>
+        <v>60944236.67874431</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>bc</t>
+          <t>cvd</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1614,46 +1614,46 @@
         </is>
       </c>
       <c r="D24">
-        <v>0.111770641753278</v>
+        <v>43.61042379933474</v>
       </c>
       <c r="E24">
-        <v>0.02436070330694506</v>
+        <v>30.07758701311594</v>
       </c>
       <c r="F24">
-        <v>0.2254436272680476</v>
+        <v>59.1651398586857</v>
       </c>
       <c r="G24">
-        <v>0.07762150364884024</v>
+        <v>162.370949935238</v>
       </c>
       <c r="H24">
-        <v>0.01272336630948389</v>
+        <v>87.89330594817241</v>
       </c>
       <c r="I24">
-        <v>0.1980801225981218</v>
+        <v>268.5246602201175</v>
       </c>
       <c r="J24">
-        <v>4927.632282976766</v>
+        <v>2429187.826470543</v>
       </c>
       <c r="K24">
-        <v>1073.990326693287</v>
+        <v>1675381.751804582</v>
       </c>
       <c r="L24">
-        <v>9939.133195366412</v>
+        <v>3295616.620408511</v>
       </c>
       <c r="M24">
-        <v>10323.65998529575</v>
+        <v>21595336.34138666</v>
       </c>
       <c r="N24">
-        <v>1692.207719161357</v>
+        <v>11689809.69110693</v>
       </c>
       <c r="O24">
-        <v>26344.6563055502</v>
+        <v>35713779.80927563</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>bc</t>
+          <t>cvd</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1667,46 +1667,46 @@
         </is>
       </c>
       <c r="D25">
-        <v>0.9000538536472646</v>
+        <v>108.2570000810117</v>
       </c>
       <c r="E25">
-        <v>0.1961690882778753</v>
+        <v>62.33273135217439</v>
       </c>
       <c r="F25">
-        <v>1.815426683786332</v>
+        <v>158.5567012349194</v>
       </c>
       <c r="G25">
-        <v>0.621924137347224</v>
+        <v>404.1168446633121</v>
       </c>
       <c r="H25">
-        <v>0.1019429957447974</v>
+        <v>182.6257054604304</v>
       </c>
       <c r="I25">
-        <v>1.587070638695494</v>
+        <v>721.4991484265951</v>
       </c>
       <c r="J25">
-        <v>39680.67424574694</v>
+        <v>6030131.418512522</v>
       </c>
       <c r="K25">
-        <v>8648.50659490669</v>
+        <v>3472057.801778818</v>
       </c>
       <c r="L25">
-        <v>80036.71620808808</v>
+        <v>8831925.372187482</v>
       </c>
       <c r="M25">
-        <v>82715.91026718079</v>
+        <v>53747540.3402205</v>
       </c>
       <c r="N25">
-        <v>13558.41843405806</v>
+        <v>24289218.82623724</v>
       </c>
       <c r="O25">
-        <v>211080.3949465007</v>
+        <v>95959386.74073714</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>bc</t>
+          <t>cvd</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1720,46 +1720,46 @@
         </is>
       </c>
       <c r="D26">
-        <v>1.38828549747697</v>
+        <v>177.9779584180429</v>
       </c>
       <c r="E26">
-        <v>0.3025804502762411</v>
+        <v>111.2026332705647</v>
       </c>
       <c r="F26">
-        <v>2.800199706517783</v>
+        <v>252.76300585393</v>
       </c>
       <c r="G26">
-        <v>0.8236107182627403</v>
+        <v>534.9040261075664</v>
       </c>
       <c r="H26">
-        <v>0.1350025491941191</v>
+        <v>262.3128108655166</v>
       </c>
       <c r="I26">
-        <v>2.101748927522201</v>
+        <v>926.0264962946965</v>
       </c>
       <c r="J26">
-        <v>61205.34272726711</v>
+        <v>9913728.23980183</v>
       </c>
       <c r="K26">
-        <v>13339.86431132864</v>
+        <v>6194209.078436995</v>
       </c>
       <c r="L26">
-        <v>123452.4044612495</v>
+        <v>14079404.95207561</v>
       </c>
       <c r="M26">
-        <v>109540.2255289445</v>
+        <v>71142235.47230634</v>
       </c>
       <c r="N26">
-        <v>17955.33904281785</v>
+        <v>34887603.8451137</v>
       </c>
       <c r="O26">
-        <v>279532.6073604527</v>
+        <v>123161524.0071946</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>bc</t>
+          <t>cvd</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1773,46 +1773,46 @@
         </is>
       </c>
       <c r="D27">
-        <v>1.36482702760281</v>
+        <v>174.9568389131374</v>
       </c>
       <c r="E27">
-        <v>0.2974676154953403</v>
+        <v>109.887914849103</v>
       </c>
       <c r="F27">
-        <v>2.752883502050935</v>
+        <v>247.9270366353384</v>
       </c>
       <c r="G27">
-        <v>0.8098126024564024</v>
+        <v>526.3357147034422</v>
       </c>
       <c r="H27">
-        <v>0.1327408243687526</v>
+        <v>259.4637157210539</v>
       </c>
       <c r="I27">
-        <v>2.06653790554938</v>
+        <v>909.1929557621427</v>
       </c>
       <c r="J27">
-        <v>60171.12916592506</v>
+        <v>9745445.84113957</v>
       </c>
       <c r="K27">
-        <v>13114.45476434307</v>
+        <v>6120976.632924738</v>
       </c>
       <c r="L27">
-        <v>121366.3749549195</v>
+        <v>13810031.79466163</v>
       </c>
       <c r="M27">
-        <v>107705.0761267015</v>
+        <v>70002650.05555782</v>
       </c>
       <c r="N27">
-        <v>17654.52964104409</v>
+        <v>34508674.19090016</v>
       </c>
       <c r="O27">
-        <v>274849.5414380675</v>
+        <v>120922663.116365</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>bc</t>
+          <t>cvd</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1826,46 +1826,46 @@
         </is>
       </c>
       <c r="D28">
-        <v>15.79275356196611</v>
+        <v>388.5160461216274</v>
       </c>
       <c r="E28">
-        <v>3.334148677319526</v>
+        <v>210.6330192143275</v>
       </c>
       <c r="F28">
-        <v>31.88765903186635</v>
+        <v>571.2030666257795</v>
       </c>
       <c r="G28">
-        <v>9.135057601693974</v>
+        <v>1174.159398368388</v>
       </c>
       <c r="H28">
-        <v>1.451168793465207</v>
+        <v>499.619447844318</v>
       </c>
       <c r="I28">
-        <v>23.33552254227355</v>
+        <v>2104.305956970938</v>
       </c>
       <c r="J28">
-        <v>696255.1262863997</v>
+        <v>21641120.80106686</v>
       </c>
       <c r="K28">
-        <v>146992.612736986</v>
+        <v>11732680.43627646</v>
       </c>
       <c r="L28">
-        <v>1405831.223737892</v>
+        <v>31817153.2171891</v>
       </c>
       <c r="M28">
-        <v>1214962.661025299</v>
+        <v>156163199.9829956</v>
       </c>
       <c r="N28">
-        <v>193005.4495308725</v>
+        <v>66449386.56329429</v>
       </c>
       <c r="O28">
-        <v>3103624.498122382</v>
+        <v>279872692.2771348</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>bc</t>
+          <t>cvd</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1879,46 +1879,46 @@
         </is>
       </c>
       <c r="D29">
-        <v>2.588336746725318</v>
+        <v>792.2167811033304</v>
       </c>
       <c r="E29">
-        <v>0.5641347544968366</v>
+        <v>479.2094093950568</v>
       </c>
       <c r="F29">
-        <v>5.220727157145636</v>
+        <v>1139.872610086353</v>
       </c>
       <c r="G29">
-        <v>1.267926293804</v>
+        <v>1911.043148582584</v>
       </c>
       <c r="H29">
-        <v>0.2078327516364178</v>
+        <v>907.2909438833487</v>
       </c>
       <c r="I29">
-        <v>3.235585294228341</v>
+        <v>3351.838069863777</v>
       </c>
       <c r="J29">
-        <v>114112.0021528791</v>
+        <v>44128059.14101771</v>
       </c>
       <c r="K29">
-        <v>24871.00892150203</v>
+        <v>26692922.52212348</v>
       </c>
       <c r="L29">
-        <v>230166.1981770796</v>
+        <v>63493184.12702997</v>
       </c>
       <c r="M29">
-        <v>168634.1970759321</v>
+        <v>254168738.7614837</v>
       </c>
       <c r="N29">
-        <v>27641.75596764356</v>
+        <v>120669695.5364854</v>
       </c>
       <c r="O29">
-        <v>430332.8441323693</v>
+        <v>445794463.2918823</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>bc</t>
+          <t>cvd</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1932,46 +1932,46 @@
         </is>
       </c>
       <c r="D30">
-        <v>2.679371656997</v>
+        <v>604.2117624746182</v>
       </c>
       <c r="E30">
-        <v>0.5839760509671355</v>
+        <v>393.1530665230368</v>
       </c>
       <c r="F30">
-        <v>5.404346397920608</v>
+        <v>843.030180352562</v>
       </c>
       <c r="G30">
-        <v>1.253445078792849</v>
+        <v>1447.715592106308</v>
       </c>
       <c r="H30">
-        <v>0.2054590562745379</v>
+        <v>739.3507663682607</v>
       </c>
       <c r="I30">
-        <v>3.19863109069016</v>
+        <v>2462.280097098285</v>
       </c>
       <c r="J30">
-        <v>118125.4582420267</v>
+        <v>33655803.59336124</v>
       </c>
       <c r="K30">
-        <v>25745.75215898811</v>
+        <v>21899412.11146619</v>
       </c>
       <c r="L30">
-        <v>238261.4196451259</v>
+        <v>46958467.10599848</v>
       </c>
       <c r="M30">
-        <v>166708.195479449</v>
+        <v>192546173.7501389</v>
       </c>
       <c r="N30">
-        <v>27326.05448451355</v>
+        <v>98333651.92697868</v>
       </c>
       <c r="O30">
-        <v>425417.9350617913</v>
+        <v>327483252.9140719</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>bc</t>
+          <t>cvd</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1985,46 +1985,46 @@
         </is>
       </c>
       <c r="D31">
-        <v>40.54197566391495</v>
+        <v>1205.884254737031</v>
       </c>
       <c r="E31">
-        <v>8.742101788092164</v>
+        <v>651.3997802736689</v>
       </c>
       <c r="F31">
-        <v>81.80307256245679</v>
+        <v>1790.149842915856</v>
       </c>
       <c r="G31">
-        <v>19.35153499910903</v>
+        <v>2893.283258155638</v>
       </c>
       <c r="H31">
-        <v>3.137775317011033</v>
+        <v>1226.669934433826</v>
       </c>
       <c r="I31">
-        <v>49.40043978851573</v>
+        <v>5235.702604451703</v>
       </c>
       <c r="J31">
-        <v>1787374.08109502</v>
+        <v>67170164.75736214</v>
       </c>
       <c r="K31">
-        <v>385413.0415316202</v>
+        <v>36284270.56080392</v>
       </c>
       <c r="L31">
-        <v>3606452.060061037</v>
+        <v>99714926.55009897</v>
       </c>
       <c r="M31">
-        <v>2573754.154881502</v>
+        <v>384806673.3346999</v>
       </c>
       <c r="N31">
-        <v>417324.1171624673</v>
+        <v>163147101.2796989</v>
       </c>
       <c r="O31">
-        <v>6570258.491872593</v>
+        <v>696348446.3920765</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>bc</t>
+          <t>cvd</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2038,46 +2038,46 @@
         </is>
       </c>
       <c r="D32">
-        <v>7.274135123559618</v>
+        <v>1755.218209722901</v>
       </c>
       <c r="E32">
-        <v>1.585416749693733</v>
+        <v>1074.669614308349</v>
       </c>
       <c r="F32">
-        <v>14.67207651104938</v>
+        <v>2513.478354488385</v>
       </c>
       <c r="G32">
-        <v>2.61098467852854</v>
+        <v>3056.184568183188</v>
       </c>
       <c r="H32">
-        <v>0.4279808162910425</v>
+        <v>1468.649683166577</v>
       </c>
       <c r="I32">
-        <v>6.662898049031521</v>
+        <v>5334.870331308373</v>
       </c>
       <c r="J32">
-        <v>320694.7951923728</v>
+        <v>97769164.71798509</v>
       </c>
       <c r="K32">
-        <v>69896.26824374762</v>
+        <v>59861246.85620371</v>
       </c>
       <c r="L32">
-        <v>646847.8371426343</v>
+        <v>140005771.3017119</v>
       </c>
       <c r="M32">
-        <v>347260.9622442959</v>
+        <v>406472547.568364</v>
       </c>
       <c r="N32">
-        <v>56921.44856670866</v>
+        <v>195330407.8611547</v>
       </c>
       <c r="O32">
-        <v>886165.4405211924</v>
+        <v>709537754.0640136</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>bc</t>
+          <t>cvd</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2091,46 +2091,46 @@
         </is>
       </c>
       <c r="D33">
-        <v>13.16613089089249</v>
+        <v>1132.669431595278</v>
       </c>
       <c r="E33">
-        <v>2.869592616649981</v>
+        <v>802.8378668444541</v>
       </c>
       <c r="F33">
-        <v>26.55635020581457</v>
+        <v>1514.890513782947</v>
       </c>
       <c r="G33">
-        <v>4.698125589840422</v>
+        <v>1960.689521002866</v>
       </c>
       <c r="H33">
-        <v>0.7700955281403257</v>
+        <v>1090.757680811027</v>
       </c>
       <c r="I33">
-        <v>11.98901398544176</v>
+        <v>3196.591569181142</v>
       </c>
       <c r="J33">
-        <v>580455.2125867772</v>
+        <v>63091952.67872021</v>
       </c>
       <c r="K33">
-        <v>126511.7296902477</v>
+        <v>44719674.85896967</v>
       </c>
       <c r="L33">
-        <v>1170789.811523748</v>
+        <v>84382431.39873768</v>
       </c>
       <c r="M33">
-        <v>624850.7034487762</v>
+        <v>260771706.2933812</v>
       </c>
       <c r="N33">
-        <v>102422.7052426633</v>
+        <v>145070771.5478666</v>
       </c>
       <c r="O33">
-        <v>1594538.860063754</v>
+        <v>425146678.7010919</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>bc</t>
+          <t>cvd</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2144,46 +2144,46 @@
         </is>
       </c>
       <c r="D34">
-        <v>30.61792606173723</v>
+        <v>2390.930698406949</v>
       </c>
       <c r="E34">
-        <v>6.656483704638181</v>
+        <v>1304.35261358535</v>
       </c>
       <c r="F34">
-        <v>61.76215573937441</v>
+        <v>3552.101658835956</v>
       </c>
       <c r="G34">
-        <v>10.91539722656241</v>
+        <v>4141.047048075145</v>
       </c>
       <c r="H34">
-        <v>1.785220185828523</v>
+        <v>1773.098951580858</v>
       </c>
       <c r="I34">
-        <v>27.85676460098734</v>
+        <v>7499.439724545427</v>
       </c>
       <c r="J34">
-        <v>1349852.506283811</v>
+        <v>133179621.762664</v>
       </c>
       <c r="K34">
-        <v>293464.3970863837</v>
+        <v>72655049.28193112</v>
       </c>
       <c r="L34">
-        <v>2722908.160081804</v>
+        <v>197859166.6004801</v>
       </c>
       <c r="M34">
-        <v>1451747.831132801</v>
+        <v>550759257.3939942</v>
       </c>
       <c r="N34">
-        <v>237434.2847151936</v>
+        <v>235822160.5602542</v>
       </c>
       <c r="O34">
-        <v>3704949.691931316</v>
+        <v>997425483.3645419</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>bc</t>
+          <t>cvd</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2197,46 +2197,46 @@
         </is>
       </c>
       <c r="D35">
-        <v>2.841123371627007</v>
+        <v>4200.625608565784</v>
       </c>
       <c r="E35">
-        <v>0.6192302596545082</v>
+        <v>2624.598198610017</v>
       </c>
       <c r="F35">
-        <v>5.730602852128943</v>
+        <v>5965.698026461033</v>
       </c>
       <c r="G35">
-        <v>0.7105907489903832</v>
+        <v>4647.574052847465</v>
       </c>
       <c r="H35">
-        <v>0.1164768262727451</v>
+        <v>2279.134487693877</v>
       </c>
       <c r="I35">
-        <v>1.813336460394753</v>
+        <v>8045.885815716421</v>
       </c>
       <c r="J35">
-        <v>125256.6060849199</v>
+        <v>233983247.6483311</v>
       </c>
       <c r="K35">
-        <v>27300.0044573883</v>
+        <v>146195368.8589753</v>
       </c>
       <c r="L35">
-        <v>252645.0879418087</v>
+        <v>332301311.4699321</v>
       </c>
       <c r="M35">
-        <v>94508.56961572096</v>
+        <v>618127349.0287129</v>
       </c>
       <c r="N35">
-        <v>15491.41789427509</v>
+        <v>303124886.8632857</v>
       </c>
       <c r="O35">
-        <v>241173.7492325022</v>
+        <v>1070102813.490284</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>bc</t>
+          <t>cvd</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2250,46 +2250,46 @@
         </is>
       </c>
       <c r="D36">
-        <v>16.48809356394024</v>
+        <v>3145.698222028302</v>
       </c>
       <c r="E36">
-        <v>3.593623057966529</v>
+        <v>2222.851492998685</v>
       </c>
       <c r="F36">
-        <v>33.25681557769737</v>
+        <v>4214.109353940224</v>
       </c>
       <c r="G36">
-        <v>4.093887622368608</v>
+        <v>3567.291358720153</v>
       </c>
       <c r="H36">
-        <v>0.6710515694839388</v>
+        <v>1978.457645783836</v>
       </c>
       <c r="I36">
-        <v>10.44707618407268</v>
+        <v>5825.424552914758</v>
       </c>
       <c r="J36">
-        <v>726910.5809534334</v>
+        <v>175221682.3634205</v>
       </c>
       <c r="K36">
-        <v>158432.0597565705</v>
+        <v>123817273.8630128</v>
       </c>
       <c r="L36">
-        <v>1466193.228373945</v>
+        <v>234734319.2331786</v>
       </c>
       <c r="M36">
-        <v>544487.0537750248</v>
+        <v>474449750.7097803</v>
       </c>
       <c r="N36">
-        <v>89249.85874136386</v>
+        <v>263134866.8892502</v>
       </c>
       <c r="O36">
-        <v>1389461.132481667</v>
+        <v>774781465.5376629</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>bc</t>
+          <t>cvd</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2303,46 +2303,46 @@
         </is>
       </c>
       <c r="D37">
-        <v>30.87782705918709</v>
+        <v>4403.046671529946</v>
       </c>
       <c r="E37">
-        <v>6.729903058196952</v>
+        <v>2544.926898460312</v>
       </c>
       <c r="F37">
-        <v>62.28119678998307</v>
+        <v>6440.641899327791</v>
       </c>
       <c r="G37">
-        <v>7.671466173958108</v>
+        <v>4981.178497293667</v>
       </c>
       <c r="H37">
-        <v>1.257472087936587</v>
+        <v>2259.690248602242</v>
       </c>
       <c r="I37">
-        <v>19.57659783453151</v>
+        <v>8881.947966393045</v>
       </c>
       <c r="J37">
-        <v>1361310.761558383</v>
+        <v>245258505.6975613</v>
       </c>
       <c r="K37">
-        <v>296701.2361267295</v>
+        <v>141757518.0980366</v>
       </c>
       <c r="L37">
-        <v>2745791.122879981</v>
+        <v>358756635.0763565</v>
       </c>
       <c r="M37">
-        <v>1020305.001136428</v>
+        <v>662496740.1400577</v>
       </c>
       <c r="N37">
-        <v>167243.787695566</v>
+        <v>300538803.0640982</v>
       </c>
       <c r="O37">
-        <v>2603687.511992691</v>
+        <v>1181299079.530275</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>bc</t>
+          <t>cvd</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2356,46 +2356,46 @@
         </is>
       </c>
       <c r="D38">
-        <v>1.387790703034119</v>
+        <v>2935.310386286934</v>
       </c>
       <c r="E38">
-        <v>0.3024726085350585</v>
+        <v>2132.667316913576</v>
       </c>
       <c r="F38">
-        <v>2.799201696197759</v>
+        <v>3872.99892108745</v>
       </c>
       <c r="G38">
-        <v>0.153169629871396</v>
+        <v>1588.149003285525</v>
       </c>
       <c r="H38">
-        <v>0.02510687395542345</v>
+        <v>905.6389911888162</v>
       </c>
       <c r="I38">
-        <v>0.3908692519085025</v>
+        <v>2554.376128700241</v>
       </c>
       <c r="J38">
-        <v>61183.52872466518</v>
+        <v>163502659.1369549</v>
       </c>
       <c r="K38">
-        <v>13335.10989248512</v>
+        <v>118793834.88672</v>
       </c>
       <c r="L38">
-        <v>123408.4051802705</v>
+        <v>215733785.9024132</v>
       </c>
       <c r="M38">
-        <v>20371.56077289567</v>
+        <v>211223817.4369749</v>
       </c>
       <c r="N38">
-        <v>3339.214236071319</v>
+        <v>120449985.8281126</v>
       </c>
       <c r="O38">
-        <v>51985.61050383083</v>
+        <v>339732025.1171321</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>bc</t>
+          <t>cvd</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2409,46 +2409,46 @@
         </is>
       </c>
       <c r="D39">
-        <v>15.25813914808517</v>
+        <v>2584.99744319498</v>
       </c>
       <c r="E39">
-        <v>3.325551280479079</v>
+        <v>1956.483112457012</v>
       </c>
       <c r="F39">
-        <v>30.77597283996993</v>
+        <v>3330.661076694787</v>
       </c>
       <c r="G39">
-        <v>1.977604313826408</v>
+        <v>1405.18859287163</v>
       </c>
       <c r="H39">
-        <v>0.3241599674989619</v>
+        <v>834.7287753484065</v>
       </c>
       <c r="I39">
-        <v>5.046592587351401</v>
+        <v>2207.01454507019</v>
       </c>
       <c r="J39">
-        <v>672685.5806216304</v>
+        <v>143989527.5808468</v>
       </c>
       <c r="K39">
-        <v>146613.5793024812</v>
+        <v>108980022.3300804</v>
       </c>
       <c r="L39">
-        <v>1356820.314595755</v>
+        <v>185524483.2940527</v>
       </c>
       <c r="M39">
-        <v>263021.3737389122</v>
+        <v>186890082.8519267</v>
       </c>
       <c r="N39">
-        <v>43113.27567736193</v>
+        <v>111018927.1213381</v>
       </c>
       <c r="O39">
-        <v>671196.8141177363</v>
+        <v>293532934.4943352</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>bc</t>
+          <t>cvd</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2462,46 +2462,46 @@
         </is>
       </c>
       <c r="D40">
-        <v>9.163185896165492</v>
+        <v>3584.305208420943</v>
       </c>
       <c r="E40">
-        <v>1.997140299646943</v>
+        <v>2345.434171683544</v>
       </c>
       <c r="F40">
-        <v>18.48232982613592</v>
+        <v>4988.153768682373</v>
       </c>
       <c r="G40">
-        <v>1.17093994454516</v>
+        <v>2011.850735461718</v>
       </c>
       <c r="H40">
-        <v>0.1919351872936503</v>
+        <v>1033.258067407192</v>
       </c>
       <c r="I40">
-        <v>2.988088569114038</v>
+        <v>3412.957353263679</v>
       </c>
       <c r="J40">
-        <v>403977.3766042479</v>
+        <v>199652968.7194633</v>
       </c>
       <c r="K40">
-        <v>88047.92439053471</v>
+        <v>130645374.2311167</v>
       </c>
       <c r="L40">
-        <v>814830.4750448549</v>
+        <v>277850141.2231459</v>
       </c>
       <c r="M40">
-        <v>155735.0126245063</v>
+        <v>267576147.8164085</v>
       </c>
       <c r="N40">
-        <v>25527.37991005549</v>
+        <v>137423322.9651565</v>
       </c>
       <c r="O40">
-        <v>397415.7796921671</v>
+        <v>453923327.9840693</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>bc</t>
+          <t>cvd</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2515,46 +2515,46 @@
         </is>
       </c>
       <c r="D41">
-        <v>0.6830970727554841</v>
+        <v>1765.412999126128</v>
       </c>
       <c r="E41">
-        <v>0.1488827912071262</v>
+        <v>1315.229777784805</v>
       </c>
       <c r="F41">
-        <v>1.377820503152524</v>
+        <v>2296.143442023591</v>
       </c>
       <c r="G41">
-        <v>0.008184143411637189</v>
+        <v>134.1376454167832</v>
       </c>
       <c r="H41">
-        <v>0.00134150782528895</v>
+        <v>78.43335192755967</v>
       </c>
       <c r="I41">
-        <v>0.02088488439584526</v>
+        <v>212.6687261859293</v>
       </c>
       <c r="J41">
-        <v>30115.70064657103</v>
+        <v>98337034.87732355</v>
       </c>
       <c r="K41">
-        <v>6563.795615948577</v>
+        <v>73260929.08216923</v>
       </c>
       <c r="L41">
-        <v>60743.97252248535</v>
+        <v>127899782.007598</v>
       </c>
       <c r="M41">
-        <v>1088.491073747746</v>
+        <v>17840306.84043217</v>
       </c>
       <c r="N41">
-        <v>178.4205407634304</v>
+        <v>10431635.80636544</v>
       </c>
       <c r="O41">
-        <v>2777.689624647419</v>
+        <v>28284940.58272859</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>bc</t>
+          <t>cvd</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2568,46 +2568,46 @@
         </is>
       </c>
       <c r="D42">
-        <v>20.89811682553058</v>
+        <v>1404.611622313837</v>
       </c>
       <c r="E42">
-        <v>4.554799146491564</v>
+        <v>1158.870362535014</v>
       </c>
       <c r="F42">
-        <v>42.15192099029731</v>
+        <v>1710.488659429885</v>
       </c>
       <c r="G42">
-        <v>0.4632004967363499</v>
+        <v>105.9826592872361</v>
       </c>
       <c r="H42">
-        <v>0.0759257334330153</v>
+        <v>68.62908280537954</v>
       </c>
       <c r="I42">
-        <v>1.182028263664246</v>
+        <v>157.3254598773042</v>
       </c>
       <c r="J42">
-        <v>921335.2764871659</v>
+        <v>78239676.58612531</v>
       </c>
       <c r="K42">
-        <v>200807.4299713736</v>
+        <v>64551396.93392535</v>
       </c>
       <c r="L42">
-        <v>1858351.740699238</v>
+        <v>95277639.30756336</v>
       </c>
       <c r="M42">
-        <v>61605.66606593454</v>
+        <v>14095693.6852024</v>
       </c>
       <c r="N42">
-        <v>10098.12254659104</v>
+        <v>9127668.013115479</v>
       </c>
       <c r="O42">
-        <v>157209.7590673447</v>
+        <v>20924286.16368145</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>bc</t>
+          <t>cvd</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2621,46 +2621,46 @@
         </is>
       </c>
       <c r="D43">
-        <v>4.340614759550004</v>
+        <v>1879.473172314717</v>
       </c>
       <c r="E43">
-        <v>0.9460483242152123</v>
+        <v>1361.299476280961</v>
       </c>
       <c r="F43">
-        <v>8.755107071195429</v>
+        <v>2484.188118681925</v>
       </c>
       <c r="G43">
-        <v>0.08807024766175804</v>
+        <v>148.7896140775257</v>
       </c>
       <c r="H43">
-        <v>0.01443607723752585</v>
+        <v>84.58336280820055</v>
       </c>
       <c r="I43">
-        <v>0.22474397730053</v>
+        <v>239.7293581172962</v>
       </c>
       <c r="J43">
-        <v>191364.6829042811</v>
+        <v>104690414.6442744</v>
       </c>
       <c r="K43">
-        <v>41708.43246967609</v>
+        <v>75827103.42780209</v>
       </c>
       <c r="L43">
-        <v>385986.4054477925</v>
+        <v>138374246.5868205</v>
       </c>
       <c r="M43">
-        <v>11713.34293901382</v>
+        <v>19789018.67231091</v>
       </c>
       <c r="N43">
-        <v>1919.998272590938</v>
+        <v>11249587.25349067</v>
       </c>
       <c r="O43">
-        <v>29890.94898097049</v>
+        <v>31884004.62960039</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>cvd</t>
+          <t>cancer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2674,46 +2674,46 @@
         </is>
       </c>
       <c r="D44">
-        <v>1.636590347282142</v>
+        <v>415.7631793452108</v>
       </c>
       <c r="E44">
-        <v>1.214249537968284</v>
+        <v>90.61667088159106</v>
       </c>
       <c r="F44">
-        <v>2.132033754316275</v>
+        <v>838.6026756738304</v>
       </c>
       <c r="G44">
-        <v>1.047052259999343</v>
+        <v>1394.524053625258</v>
       </c>
       <c r="H44">
-        <v>0.6104463968713932</v>
+        <v>240.4646212187864</v>
       </c>
       <c r="I44">
-        <v>1.661561282127186</v>
+        <v>3247.947240199149</v>
       </c>
       <c r="J44">
-        <v>91161.35552430987</v>
+        <v>6156205.396564541</v>
       </c>
       <c r="K44">
-        <v>67636.12776390932</v>
+        <v>1341761.045743719</v>
       </c>
       <c r="L44">
-        <v>118758.5441829252</v>
+        <v>12417189.81870241</v>
       </c>
       <c r="M44">
-        <v>139257.9505799126</v>
+        <v>185471699.1321593</v>
       </c>
       <c r="N44">
-        <v>81189.3707838953</v>
+        <v>31981794.62209859</v>
       </c>
       <c r="O44">
-        <v>220987.6505229158</v>
+        <v>431976982.9464868</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>cvd</t>
+          <t>cancer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2727,46 +2727,46 @@
         </is>
       </c>
       <c r="D45">
-        <v>8.03818337989715</v>
+        <v>248.365211849006</v>
       </c>
       <c r="E45">
-        <v>5.601540791196293</v>
+        <v>54.13184663442956</v>
       </c>
       <c r="F45">
-        <v>10.84518085627937</v>
+        <v>500.9576161335326</v>
       </c>
       <c r="G45">
-        <v>5.019441387319739</v>
+        <v>832.3653417998213</v>
       </c>
       <c r="H45">
-        <v>2.745147614455639</v>
+        <v>143.5288377502046</v>
       </c>
       <c r="I45">
-        <v>8.255721906470495</v>
+        <v>1938.638998522897</v>
       </c>
       <c r="J45">
-        <v>447742.8906270309</v>
+        <v>3677543.691848233</v>
       </c>
       <c r="K45">
-        <v>312017.0251512156</v>
+        <v>801530.2531159978</v>
       </c>
       <c r="L45">
-        <v>604098.2640564744</v>
+        <v>7417679.422089224</v>
       </c>
       <c r="M45">
-        <v>667585.7045135252</v>
+        <v>110704590.4593762</v>
       </c>
       <c r="N45">
-        <v>365104.6327226</v>
+        <v>19089335.42077721</v>
       </c>
       <c r="O45">
-        <v>1098011.013560576</v>
+        <v>257838986.8035453</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>cvd</t>
+          <t>cancer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2780,46 +2780,46 @@
         </is>
       </c>
       <c r="D46">
-        <v>63.61605802342081</v>
+        <v>654.9995713225958</v>
       </c>
       <c r="E46">
-        <v>41.53241771057156</v>
+        <v>142.7588673811825</v>
       </c>
       <c r="F46">
-        <v>88.46058548652977</v>
+        <v>1321.147278942339</v>
       </c>
       <c r="G46">
-        <v>39.53129609277384</v>
+        <v>2192.688594533249</v>
       </c>
       <c r="H46">
-        <v>20.26057850498445</v>
+        <v>378.09604715278</v>
       </c>
       <c r="I46">
-        <v>67.0006400930733</v>
+        <v>5106.930103296875</v>
       </c>
       <c r="J46">
-        <v>3543541.664020591</v>
+        <v>9698578.652573671</v>
       </c>
       <c r="K46">
-        <v>2313438.731314257</v>
+        <v>2113830.549313169</v>
       </c>
       <c r="L46">
-        <v>4927431.532770677</v>
+        <v>19562227.75929919</v>
       </c>
       <c r="M46">
-        <v>5257662.380338921</v>
+        <v>291627583.0729222</v>
       </c>
       <c r="N46">
-        <v>2694656.941162932</v>
+        <v>50286774.27131974</v>
       </c>
       <c r="O46">
-        <v>8911085.13237875</v>
+        <v>679221703.7384844</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>cvd</t>
+          <t>cancer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2833,46 +2833,46 @@
         </is>
       </c>
       <c r="D47">
-        <v>11.90361771475063</v>
+        <v>746.1845492332919</v>
       </c>
       <c r="E47">
-        <v>8.880376658410286</v>
+        <v>162.6328714853769</v>
       </c>
       <c r="F47">
-        <v>15.45603843130427</v>
+        <v>1505.069209156552</v>
       </c>
       <c r="G47">
-        <v>6.157105152131916</v>
+        <v>2047.59133026688</v>
       </c>
       <c r="H47">
-        <v>3.600237789708793</v>
+        <v>353.0762143281082</v>
       </c>
       <c r="I47">
-        <v>9.753207372169012</v>
+        <v>4768.988095190759</v>
       </c>
       <c r="J47">
-        <v>663055.3139470399</v>
+        <v>11048754.62049736</v>
       </c>
       <c r="K47">
-        <v>494654.74062677</v>
+        <v>2408104.928083976</v>
       </c>
       <c r="L47">
-        <v>860932.2527005102</v>
+        <v>22285559.77998104</v>
       </c>
       <c r="M47">
-        <v>818894.9852335447</v>
+        <v>272329646.925495</v>
       </c>
       <c r="N47">
-        <v>478831.6260312694</v>
+        <v>46959136.50563839</v>
       </c>
       <c r="O47">
-        <v>1297176.580498479</v>
+        <v>634275416.6603709</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>cvd</t>
+          <t>cancer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2886,46 +2886,46 @@
         </is>
       </c>
       <c r="D48">
-        <v>13.25503473826549</v>
+        <v>753.8125070842248</v>
       </c>
       <c r="E48">
-        <v>9.215720526768932</v>
+        <v>164.2954048226606</v>
       </c>
       <c r="F48">
-        <v>17.89162590982862</v>
+        <v>1520.454953208712</v>
       </c>
       <c r="G48">
-        <v>6.942022223036908</v>
+        <v>2077.852995048254</v>
       </c>
       <c r="H48">
-        <v>3.789054743201171</v>
+        <v>358.2943815875295</v>
       </c>
       <c r="I48">
-        <v>11.4211172005436</v>
+        <v>4839.469698111096</v>
       </c>
       <c r="J48">
-        <v>738331.9449908647</v>
+        <v>11161701.79239611</v>
       </c>
       <c r="K48">
-        <v>513334.064782083</v>
+        <v>2432722.059209138</v>
       </c>
       <c r="L48">
-        <v>996599.3464292747</v>
+        <v>22513376.49216139</v>
       </c>
       <c r="M48">
-        <v>923288.9556639087</v>
+        <v>276354448.3414178</v>
       </c>
       <c r="N48">
-        <v>503944.2808457557</v>
+        <v>47653152.75114143</v>
       </c>
       <c r="O48">
-        <v>1519008.587672299</v>
+        <v>643649469.8487759</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>cvd</t>
+          <t>cancer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2939,46 +2939,46 @@
         </is>
       </c>
       <c r="D49">
-        <v>134.6662699392924</v>
+        <v>1776.005053872611</v>
       </c>
       <c r="E49">
-        <v>83.77601438173841</v>
+        <v>244.6663584106245</v>
       </c>
       <c r="F49">
-        <v>190.9350298040215</v>
+        <v>3626.258263185735</v>
       </c>
       <c r="G49">
-        <v>68.66409802636427</v>
+        <v>4927.644067524714</v>
       </c>
       <c r="H49">
-        <v>33.58050635222839</v>
+        <v>537.0719770264043</v>
       </c>
       <c r="I49">
-        <v>118.5927397521785</v>
+        <v>11617.87239247016</v>
       </c>
       <c r="J49">
-        <v>7501180.568158448</v>
+        <v>26297306.83269177</v>
       </c>
       <c r="K49">
-        <v>4666491.553091603</v>
+        <v>3622774.76898612</v>
       </c>
       <c r="L49">
-        <v>10635463.03014361</v>
+        <v>53694006.10299103</v>
       </c>
       <c r="M49">
-        <v>9132325.037506448</v>
+        <v>655376660.9807869</v>
       </c>
       <c r="N49">
-        <v>4466207.344846376</v>
+        <v>71430572.94451177</v>
       </c>
       <c r="O49">
-        <v>15772834.38703974</v>
+        <v>1545177028.198532</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>cvd</t>
+          <t>cancer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2992,46 +2992,46 @@
         </is>
       </c>
       <c r="D50">
-        <v>58.5613338414753</v>
+        <v>1565.680789785276</v>
       </c>
       <c r="E50">
-        <v>43.20401281426481</v>
+        <v>341.2442175784907</v>
       </c>
       <c r="F50">
-        <v>76.55487476842055</v>
+        <v>3158.009570815964</v>
       </c>
       <c r="G50">
-        <v>21.94290946533851</v>
+        <v>3497.648624255389</v>
       </c>
       <c r="H50">
-        <v>12.74631764859977</v>
+        <v>603.1167045140086</v>
       </c>
       <c r="I50">
-        <v>34.90125780819539</v>
+        <v>8146.276263076486</v>
       </c>
       <c r="J50">
-        <v>3261983.417637861</v>
+        <v>23183035.45435058</v>
       </c>
       <c r="K50">
-        <v>2406549.921780178</v>
+        <v>5052803.129684715</v>
       </c>
       <c r="L50">
-        <v>4264259.634350562</v>
+        <v>46760647.71507194</v>
       </c>
       <c r="M50">
-        <v>2918406.958890021</v>
+        <v>465187267.0259668</v>
       </c>
       <c r="N50">
-        <v>1695260.24726377</v>
+        <v>80214521.70036314</v>
       </c>
       <c r="O50">
-        <v>4641867.288489987</v>
+        <v>1083454742.989172</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>cvd</t>
+          <t>cancer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3045,46 +3045,46 @@
         </is>
       </c>
       <c r="D51">
-        <v>57.85103415896698</v>
+        <v>1123.06755299157</v>
       </c>
       <c r="E51">
-        <v>41.23334138195948</v>
+        <v>244.7755065455924</v>
       </c>
       <c r="F51">
-        <v>77.09486608515724</v>
+        <v>2265.249790480363</v>
       </c>
       <c r="G51">
-        <v>23.29323254923291</v>
+        <v>2496.069326314544</v>
       </c>
       <c r="H51">
-        <v>13.03189825714377</v>
+        <v>430.4094744925389</v>
       </c>
       <c r="I51">
-        <v>37.83774738415063</v>
+        <v>5813.525739246659</v>
       </c>
       <c r="J51">
-        <v>3222418.304722783</v>
+        <v>16629261.25714616</v>
       </c>
       <c r="K51">
-        <v>2296779.581657907</v>
+        <v>3624390.92542059</v>
       </c>
       <c r="L51">
-        <v>4294338.230675429</v>
+        <v>33541553.64764274</v>
       </c>
       <c r="M51">
-        <v>3097999.929047977</v>
+        <v>331977220.3998344</v>
       </c>
       <c r="N51">
-        <v>1733242.468200121</v>
+        <v>57244460.10750768</v>
       </c>
       <c r="O51">
-        <v>5032420.402092034</v>
+        <v>773198923.3198056</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>cvd</t>
+          <t>cancer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3098,46 +3098,46 @@
         </is>
       </c>
       <c r="D52">
-        <v>363.9810704110671</v>
+        <v>2426.364145698882</v>
       </c>
       <c r="E52">
-        <v>228.2755863536125</v>
+        <v>438.7725611118991</v>
       </c>
       <c r="F52">
-        <v>514.5901108589602</v>
+        <v>4921.861939029323</v>
       </c>
       <c r="G52">
-        <v>151.584343381194</v>
+        <v>5393.084295118209</v>
       </c>
       <c r="H52">
-        <v>74.66470306176544</v>
+        <v>771.585026471576</v>
       </c>
       <c r="I52">
-        <v>261.1697465245784</v>
+        <v>12632.32799297079</v>
       </c>
       <c r="J52">
-        <v>20274473.58403726</v>
+        <v>35927173.90536334</v>
       </c>
       <c r="K52">
-        <v>12715406.71106892</v>
+        <v>6496905.312383899</v>
       </c>
       <c r="L52">
-        <v>28663698.3550658</v>
+        <v>72878009.73120718</v>
       </c>
       <c r="M52">
-        <v>20160717.6696988</v>
+        <v>717280211.2507217</v>
       </c>
       <c r="N52">
-        <v>9930405.507214803</v>
+        <v>102620808.5207196</v>
       </c>
       <c r="O52">
-        <v>34735576.28776892</v>
+        <v>1680099623.065115</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>cvd</t>
+          <t>cancer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3151,46 +3151,46 @@
         </is>
       </c>
       <c r="D53">
-        <v>144.3211799540095</v>
+        <v>1818.546735454858</v>
       </c>
       <c r="E53">
-        <v>105.5225888805154</v>
+        <v>396.3570109047056</v>
       </c>
       <c r="F53">
-        <v>189.6002776909467</v>
+        <v>3668.045257379818</v>
       </c>
       <c r="G53">
-        <v>44.40825369031113</v>
+        <v>2940.211187452242</v>
       </c>
       <c r="H53">
-        <v>25.40235655315321</v>
+        <v>506.995033650336</v>
       </c>
       <c r="I53">
-        <v>71.24712385659446</v>
+        <v>6847.964211920572</v>
       </c>
       <c r="J53">
-        <v>8038978.365798237</v>
+        <v>26927221.5118801</v>
       </c>
       <c r="K53">
-        <v>5877819.245822473</v>
+        <v>5868858.26046598</v>
       </c>
       <c r="L53">
-        <v>10561114.6679411</v>
+        <v>54312746.12602305</v>
       </c>
       <c r="M53">
-        <v>5906297.74081138</v>
+        <v>391048087.9311482</v>
       </c>
       <c r="N53">
-        <v>3378513.421569377</v>
+        <v>67430339.47549468</v>
       </c>
       <c r="O53">
-        <v>9475867.472927062</v>
+        <v>910779240.185436</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>cvd</t>
+          <t>cancer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3204,46 +3204,46 @@
         </is>
       </c>
       <c r="D54">
-        <v>280.4582135033697</v>
+        <v>1087.413598272012</v>
       </c>
       <c r="E54">
-        <v>197.4070344445368</v>
+        <v>237.0046339889163</v>
       </c>
       <c r="F54">
-        <v>376.3348940845823</v>
+        <v>2193.335048359</v>
       </c>
       <c r="G54">
-        <v>83.00739198871312</v>
+        <v>1753.907645771968</v>
       </c>
       <c r="H54">
-        <v>45.79941794051278</v>
+        <v>302.4348964056068</v>
       </c>
       <c r="I54">
-        <v>135.867720211921</v>
+        <v>4084.977582738828</v>
       </c>
       <c r="J54">
-        <v>15622083.4085647</v>
+        <v>16101333.14961367</v>
       </c>
       <c r="K54">
-        <v>10995966.6326296</v>
+        <v>3509327.615473886</v>
       </c>
       <c r="L54">
-        <v>20962606.27029941</v>
+        <v>32476712.06105168</v>
       </c>
       <c r="M54">
-        <v>11039983.13449885</v>
+        <v>233269716.8876717</v>
       </c>
       <c r="N54">
-        <v>6091322.586088199</v>
+        <v>40223841.22194571</v>
       </c>
       <c r="O54">
-        <v>18070406.7881855</v>
+        <v>543302018.5042642</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>cvd</t>
+          <t>cancer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3257,46 +3257,46 @@
         </is>
       </c>
       <c r="D55">
-        <v>616.6052649967703</v>
+        <v>2574.976689559453</v>
       </c>
       <c r="E55">
-        <v>412.2364035135577</v>
+        <v>548.0701152644502</v>
       </c>
       <c r="F55">
-        <v>847.9626976101185</v>
+        <v>5197.845071581039</v>
       </c>
       <c r="G55">
-        <v>179.8233783949919</v>
+        <v>4148.983676590965</v>
       </c>
       <c r="H55">
-        <v>94.41673477913551</v>
+        <v>698.6628444005972</v>
       </c>
       <c r="I55">
-        <v>301.3606526724215</v>
+        <v>9670.846552488703</v>
       </c>
       <c r="J55">
-        <v>34346146.47085012</v>
+        <v>38127679.84230685</v>
       </c>
       <c r="K55">
-        <v>22962392.1485122</v>
+        <v>8115274.196720711</v>
       </c>
       <c r="L55">
-        <v>47233218.18227879</v>
+        <v>76964491.97490044</v>
       </c>
       <c r="M55">
-        <v>23916509.32653392</v>
+        <v>551814828.9865984</v>
       </c>
       <c r="N55">
-        <v>12557425.72562502</v>
+        <v>92922158.30527943</v>
       </c>
       <c r="O55">
-        <v>40080966.80543205</v>
+        <v>1286222591.480998</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>cvd</t>
+          <t>cancer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3310,46 +3310,46 @@
         </is>
       </c>
       <c r="D56">
-        <v>321.6683949358534</v>
+        <v>2112.976538808103</v>
       </c>
       <c r="E56">
-        <v>233.5532891091962</v>
+        <v>460.528755574859</v>
       </c>
       <c r="F56">
-        <v>424.4101836840118</v>
+        <v>4261.916078935035</v>
       </c>
       <c r="G56">
-        <v>49.41160905375407</v>
+        <v>2181.732598962326</v>
       </c>
       <c r="H56">
-        <v>28.31714994768715</v>
+        <v>376.2068511090249</v>
       </c>
       <c r="I56">
-        <v>79.21843565794846</v>
+        <v>5081.412798316928</v>
       </c>
       <c r="J56">
-        <v>17917572.9347169</v>
+        <v>31286843.61013157</v>
       </c>
       <c r="K56">
-        <v>13009385.30996044</v>
+        <v>6819049.283796935</v>
       </c>
       <c r="L56">
-        <v>23640496.05156684</v>
+        <v>63106191.38079111</v>
       </c>
       <c r="M56">
-        <v>6571744.004149292</v>
+        <v>290170435.6619893</v>
       </c>
       <c r="N56">
-        <v>3766180.943042391</v>
+        <v>50035511.19750031</v>
       </c>
       <c r="O56">
-        <v>10536051.94250715</v>
+        <v>675827902.1761515</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>cvd</t>
+          <t>cancer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -3363,46 +3363,46 @@
         </is>
       </c>
       <c r="D57">
-        <v>796.5057071976358</v>
+        <v>1557.619498506581</v>
       </c>
       <c r="E57">
-        <v>573.1656311638267</v>
+        <v>339.4872380887841</v>
       </c>
       <c r="F57">
-        <v>1056.359869656419</v>
+        <v>3141.7497845445</v>
       </c>
       <c r="G57">
-        <v>154.2523492278801</v>
+        <v>1645.239646924223</v>
       </c>
       <c r="H57">
-        <v>87.24598621181136</v>
+        <v>283.6967404637321</v>
       </c>
       <c r="I57">
-        <v>249.1757031801612</v>
+        <v>3831.881964891329</v>
       </c>
       <c r="J57">
-        <v>44366960.90232281</v>
+        <v>23063671.91438695</v>
       </c>
       <c r="K57">
-        <v>31926471.98708746</v>
+        <v>5026787.534380618</v>
       </c>
       <c r="L57">
-        <v>58841357.45960189</v>
+        <v>46519889.05975042</v>
       </c>
       <c r="M57">
-        <v>20515562.44730805</v>
+        <v>218816873.0409216</v>
       </c>
       <c r="N57">
-        <v>11603716.16617091</v>
+        <v>37731666.48167637</v>
       </c>
       <c r="O57">
-        <v>33140368.52296144</v>
+        <v>509640301.3305467</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>cvd</t>
+          <t>cancer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -3416,46 +3416,46 @@
         </is>
       </c>
       <c r="D58">
-        <v>1384.86625831875</v>
+        <v>2346.249943076887</v>
       </c>
       <c r="E58">
-        <v>937.6427261527182</v>
+        <v>511.3713033284636</v>
       </c>
       <c r="F58">
-        <v>1893.435965723474</v>
+        <v>4732.433216338684</v>
       </c>
       <c r="G58">
-        <v>259.4504169690492</v>
+        <v>2462.55598636275</v>
       </c>
       <c r="H58">
-        <v>137.1655735990006</v>
+        <v>424.6306049374815</v>
       </c>
       <c r="I58">
-        <v>433.5040596300004</v>
+        <v>5735.470750002643</v>
       </c>
       <c r="J58">
-        <v>77139820.32087086</v>
+        <v>34740922.90713947</v>
       </c>
       <c r="K58">
-        <v>52228575.1321587</v>
+        <v>7571874.888384562</v>
       </c>
       <c r="L58">
-        <v>105468170.1627288</v>
+        <v>70073138.63432689</v>
       </c>
       <c r="M58">
-        <v>34506905.45688355</v>
+        <v>327519946.1862458</v>
       </c>
       <c r="N58">
-        <v>18243021.28866708</v>
+        <v>56475870.45668504</v>
       </c>
       <c r="O58">
-        <v>57656039.93079006</v>
+        <v>762817609.7503515</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>cvd</t>
+          <t>cancer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -3469,46 +3469,46 @@
         </is>
       </c>
       <c r="D59">
-        <v>62.62491179099383</v>
+        <v>835.2436047477086</v>
       </c>
       <c r="E59">
-        <v>52.1827623896593</v>
+        <v>182.0435252505413</v>
       </c>
       <c r="F59">
-        <v>75.70876662651104</v>
+        <v>1684.703111237536</v>
       </c>
       <c r="G59">
-        <v>6.451867292915296</v>
+        <v>407.091252346968</v>
       </c>
       <c r="H59">
-        <v>4.224709121978511</v>
+        <v>70.19674099031242</v>
       </c>
       <c r="I59">
-        <v>9.499387749445114</v>
+        <v>948.1449288251999</v>
       </c>
       <c r="J59">
-        <v>3488332.836581938</v>
+        <v>12367452.05549933</v>
       </c>
       <c r="K59">
-        <v>2906684.230628802</v>
+        <v>2695518.478384761</v>
       </c>
       <c r="L59">
-        <v>4217129.718629917</v>
+        <v>24945398.96809415</v>
       </c>
       <c r="M59">
-        <v>858098.3499577345</v>
+        <v>54143136.56214675</v>
       </c>
       <c r="N59">
-        <v>561886.3132231419</v>
+        <v>9336166.551711552</v>
       </c>
       <c r="O59">
-        <v>1263418.5706762</v>
+        <v>126103275.5337516</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>cvd</t>
+          <t>cancer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -3522,46 +3522,46 @@
         </is>
       </c>
       <c r="D60">
-        <v>944.788850989561</v>
+        <v>718.6130424774171</v>
       </c>
       <c r="E60">
-        <v>731.6971022630355</v>
+        <v>156.6235895731507</v>
       </c>
       <c r="F60">
-        <v>1200.137813332994</v>
+        <v>1449.456926764802</v>
       </c>
       <c r="G60">
-        <v>86.21157891224745</v>
+        <v>348.4411779186865</v>
       </c>
       <c r="H60">
-        <v>52.35957578260737</v>
+        <v>60.08342104062218</v>
       </c>
       <c r="I60">
-        <v>133.5646760601329</v>
+        <v>811.5446694882552</v>
       </c>
       <c r="J60">
-        <v>52626628.57782052</v>
+        <v>10640503.31996315</v>
       </c>
       <c r="K60">
-        <v>40756991.99025565</v>
+        <v>2319125.490809646</v>
       </c>
       <c r="L60">
-        <v>66850076.47827446</v>
+        <v>21462108.71460643</v>
       </c>
       <c r="M60">
-        <v>11466139.99532891</v>
+        <v>46342676.66318531</v>
       </c>
       <c r="N60">
-        <v>6963823.57908678</v>
+        <v>7991094.99840275</v>
       </c>
       <c r="O60">
-        <v>17764101.91599767</v>
+        <v>107935441.0419379</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>cvd</t>
+          <t>cancer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -3575,46 +3575,46 @@
         </is>
       </c>
       <c r="D61">
-        <v>511.3799629456157</v>
+        <v>1056.21548430027</v>
       </c>
       <c r="E61">
-        <v>395.7246102542057</v>
+        <v>230.2049235615637</v>
       </c>
       <c r="F61">
-        <v>649.7338663373233</v>
+        <v>2130.407826439325</v>
       </c>
       <c r="G61">
-        <v>50.61663028910152</v>
+        <v>531.0503557029517</v>
       </c>
       <c r="H61">
-        <v>30.7470278797095</v>
+        <v>91.57161706909251</v>
       </c>
       <c r="I61">
-        <v>78.38969809451466</v>
+        <v>1236.854633470289</v>
       </c>
       <c r="J61">
-        <v>28484886.69599668</v>
+        <v>15639382.67603411</v>
       </c>
       <c r="K61">
-        <v>22042652.24037976</v>
+        <v>3408644.303176075</v>
       </c>
       <c r="L61">
-        <v>36191475.82272157</v>
+        <v>31544948.68608713</v>
       </c>
       <c r="M61">
-        <v>6732011.828450503</v>
+        <v>70629697.30849259</v>
       </c>
       <c r="N61">
-        <v>4089354.708001364</v>
+        <v>12179025.0701893</v>
       </c>
       <c r="O61">
-        <v>10425829.84657045</v>
+        <v>164501666.2515484</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>cvd</t>
+          <t>cancer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -3628,46 +3628,46 @@
         </is>
       </c>
       <c r="D62">
-        <v>71.83601726011547</v>
+        <v>313.5745094393058</v>
       </c>
       <c r="E62">
-        <v>59.06618715181178</v>
+        <v>68.34438336619475</v>
       </c>
       <c r="F62">
-        <v>87.67564402700725</v>
+        <v>632.4860778990954</v>
       </c>
       <c r="G62">
-        <v>0.3919506373264032</v>
+        <v>20.17442418765819</v>
       </c>
       <c r="H62">
-        <v>0.2570241100770838</v>
+        <v>3.47877489669736</v>
       </c>
       <c r="I62">
-        <v>0.5765949452221326</v>
+        <v>46.98769102803838</v>
       </c>
       <c r="J62">
-        <v>4001409.83342295</v>
+        <v>4643097.761267804</v>
       </c>
       <c r="K62">
-        <v>3290104.756730219</v>
+        <v>1011975.284503244</v>
       </c>
       <c r="L62">
-        <v>4883708.723592357</v>
+        <v>9365221.355451906</v>
       </c>
       <c r="M62">
-        <v>52129.43476441163</v>
+        <v>2683198.416958539</v>
       </c>
       <c r="N62">
-        <v>34184.20664025215</v>
+        <v>462677.0612607489</v>
       </c>
       <c r="O62">
-        <v>76687.12771454363</v>
+        <v>6249362.906729105</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>cvd</t>
+          <t>cancer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -3681,46 +3681,46 @@
         </is>
       </c>
       <c r="D63">
-        <v>1794.036842654509</v>
+        <v>236.390661277424</v>
       </c>
       <c r="E63">
-        <v>1444.603262012854</v>
+        <v>51.52196206069619</v>
       </c>
       <c r="F63">
-        <v>2221.756185159352</v>
+        <v>476.8047073426706</v>
       </c>
       <c r="G63">
-        <v>21.79517674584586</v>
+        <v>15.37990590101244</v>
       </c>
       <c r="H63">
-        <v>13.79254054991426</v>
+        <v>2.652032596535927</v>
       </c>
       <c r="I63">
-        <v>32.87267011521953</v>
+        <v>35.82091165502322</v>
       </c>
       <c r="J63">
-        <v>99931440.20954147</v>
+        <v>3500236.521534819</v>
       </c>
       <c r="K63">
-        <v>80467290.90064004</v>
+        <v>762885.6922327289</v>
       </c>
       <c r="L63">
-        <v>123756263.0257464</v>
+        <v>7060047.301622916</v>
       </c>
       <c r="M63">
-        <v>2898758.5071975</v>
+        <v>2045527.484834654</v>
       </c>
       <c r="N63">
-        <v>1834407.893138597</v>
+        <v>352720.3353392783</v>
       </c>
       <c r="O63">
-        <v>4372065.125324198</v>
+        <v>4764181.250118088</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>cvd</t>
+          <t>cancer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -3734,46 +3734,46 @@
         </is>
       </c>
       <c r="D64">
-        <v>345.8224747961253</v>
+        <v>335.1415856107587</v>
       </c>
       <c r="E64">
-        <v>281.2673934708092</v>
+        <v>73.04498394940379</v>
       </c>
       <c r="F64">
-        <v>425.2756344904891</v>
+        <v>675.9873033138297</v>
       </c>
       <c r="G64">
-        <v>4.205216324526533</v>
+        <v>22.60428428871962</v>
       </c>
       <c r="H64">
-        <v>2.734461983759312</v>
+        <v>3.897767589793943</v>
       </c>
       <c r="I64">
-        <v>6.222885079728173</v>
+        <v>52.64701069971866</v>
       </c>
       <c r="J64">
-        <v>19263003.49109377</v>
+        <v>4962441.458138504</v>
       </c>
       <c r="K64">
-        <v>15667156.35111099</v>
+        <v>1081577.077338822</v>
       </c>
       <c r="L64">
-        <v>23688703.3923892</v>
+        <v>10009344.00016788</v>
       </c>
       <c r="M64">
-        <v>559293.7711620289</v>
+        <v>3006369.81039971</v>
       </c>
       <c r="N64">
-        <v>363683.4438399886</v>
+        <v>518403.0894425944</v>
       </c>
       <c r="O64">
-        <v>827643.7156038471</v>
+        <v>7002052.423062582</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>cancer</t>
+          <t>diab2</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -3787,46 +3787,46 @@
         </is>
       </c>
       <c r="D65">
-        <v>8.950795614504893</v>
+        <v>93.4597350949351</v>
       </c>
       <c r="E65">
-        <v>1.950849283011009</v>
+        <v>-7.411104959875187</v>
       </c>
       <c r="F65">
-        <v>18.05393436608531</v>
+        <v>188.355418076562</v>
       </c>
       <c r="G65">
-        <v>4.968567527410945</v>
+        <v>372.9669568139454</v>
       </c>
       <c r="H65">
-        <v>0.8567544642725126</v>
+        <v>-22.00960974391572</v>
       </c>
       <c r="I65">
-        <v>11.57215262543907</v>
+        <v>954.3250788402071</v>
       </c>
       <c r="J65">
-        <v>132534.430663974</v>
+        <v>7028265.538874211</v>
       </c>
       <c r="K65">
-        <v>28886.22533354401</v>
+        <v>-557322.5040875734</v>
       </c>
       <c r="L65">
-        <v>267324.6061586251</v>
+        <v>14164515.79477554</v>
       </c>
       <c r="M65">
-        <v>660819.4811456557</v>
+        <v>49604605.25625475</v>
       </c>
       <c r="N65">
-        <v>113948.3437482442</v>
+        <v>-2927278.095940791</v>
       </c>
       <c r="O65">
-        <v>1539096.299183396</v>
+        <v>126925235.4857475</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>cancer</t>
+          <t>diab2</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -3840,46 +3840,46 @@
         </is>
       </c>
       <c r="D66">
-        <v>45.93607670318785</v>
+        <v>55.59436772459278</v>
       </c>
       <c r="E66">
-        <v>10.01188789916396</v>
+        <v>-4.408483439059063</v>
       </c>
       <c r="F66">
-        <v>92.65398848912142</v>
+        <v>112.0429066574065</v>
       </c>
       <c r="G66">
-        <v>25.93490822411922</v>
+        <v>221.0483303452196</v>
       </c>
       <c r="H66">
-        <v>4.472083408130733</v>
+        <v>-13.04455367039288</v>
       </c>
       <c r="I66">
-        <v>60.40427439911492</v>
+        <v>565.6049723177761</v>
       </c>
       <c r="J66">
-        <v>680175.4877441027</v>
+        <v>4180752.0472571</v>
       </c>
       <c r="K66">
-        <v>148246.0241229205</v>
+        <v>-331522.3631006803</v>
       </c>
       <c r="L66">
-        <v>1371927.607558422</v>
+        <v>8425738.623543626</v>
       </c>
       <c r="M66">
-        <v>3449342.793807857</v>
+        <v>29399427.9359142</v>
       </c>
       <c r="N66">
-        <v>594787.0932813875</v>
+        <v>-1734925.638162253</v>
       </c>
       <c r="O66">
-        <v>8033768.495082284</v>
+        <v>75225461.31826422</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>cancer</t>
+          <t>diab2</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -3893,46 +3893,46 @@
         </is>
       </c>
       <c r="D67">
-        <v>340.3389750666342</v>
+        <v>147.7938649011022</v>
       </c>
       <c r="E67">
-        <v>74.17776855651714</v>
+        <v>-11.71965493049052</v>
       </c>
       <c r="F67">
-        <v>686.4705421400263</v>
+        <v>297.858486163274</v>
       </c>
       <c r="G67">
-        <v>189.9966010302564</v>
+        <v>588.7707292148518</v>
       </c>
       <c r="H67">
-        <v>32.76204564620164</v>
+        <v>-34.74467038409552</v>
       </c>
       <c r="I67">
-        <v>442.515806277565</v>
+        <v>1506.510596479091</v>
       </c>
       <c r="J67">
-        <v>5039399.203811648</v>
+        <v>11114246.43442777</v>
       </c>
       <c r="K67">
-        <v>1098350.219016351</v>
+        <v>-881329.7704278189</v>
       </c>
       <c r="L67">
-        <v>10164569.31746736</v>
+        <v>22399256.01796438</v>
       </c>
       <c r="M67">
-        <v>25269547.93702409</v>
+        <v>78306506.98557529</v>
       </c>
       <c r="N67">
-        <v>4357352.070944819</v>
+        <v>-4621041.161084704</v>
       </c>
       <c r="O67">
-        <v>58854602.23491615</v>
+        <v>200365909.3317192</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>cancer</t>
+          <t>diab2</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -3946,46 +3946,46 @@
         </is>
       </c>
       <c r="D68">
-        <v>69.2188401966349</v>
+        <v>176.7691466145579</v>
       </c>
       <c r="E68">
-        <v>15.08642701545214</v>
+        <v>-14.01731663263693</v>
       </c>
       <c r="F68">
-        <v>139.6157896602488</v>
+        <v>356.2542358995669</v>
       </c>
       <c r="G68">
-        <v>33.11976479527958</v>
+        <v>566.7035752752383</v>
       </c>
       <c r="H68">
-        <v>5.711003460749402</v>
+        <v>-33.44243854425986</v>
       </c>
       <c r="I68">
-        <v>77.13832427861432</v>
+        <v>1450.046510214994</v>
       </c>
       <c r="J68">
-        <v>1024923.366791572</v>
+        <v>13293216.59456136</v>
       </c>
       <c r="K68">
-        <v>223384.7248177998</v>
+        <v>-1054116.22809093</v>
       </c>
       <c r="L68">
-        <v>2067290.997499304</v>
+        <v>26790674.79388333</v>
       </c>
       <c r="M68">
-        <v>4404928.717772184</v>
+        <v>75371575.51160669</v>
       </c>
       <c r="N68">
-        <v>759563.4602796704</v>
+        <v>-4447844.326386562</v>
       </c>
       <c r="O68">
-        <v>10259397.1290557</v>
+        <v>192856185.8585942</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>cancer</t>
+          <t>diab2</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -3999,46 +3999,46 @@
         </is>
       </c>
       <c r="D69">
-        <v>73.95951017444229</v>
+        <v>173.4183679034386</v>
       </c>
       <c r="E69">
-        <v>16.11966841940163</v>
+        <v>-13.7516089169002</v>
       </c>
       <c r="F69">
-        <v>149.1778161343993</v>
+        <v>349.5011959474014</v>
       </c>
       <c r="G69">
-        <v>35.29184459454813</v>
+        <v>556.7241214471828</v>
       </c>
       <c r="H69">
-        <v>6.085545832270493</v>
+        <v>-32.8535287757126</v>
       </c>
       <c r="I69">
-        <v>82.1972550092723</v>
+        <v>1424.511693022079</v>
       </c>
       <c r="J69">
-        <v>1095118.467152968</v>
+        <v>13041234.68470647</v>
       </c>
       <c r="K69">
-        <v>238683.9302860801</v>
+        <v>-1034134.742159813</v>
       </c>
       <c r="L69">
-        <v>2208875.923502051</v>
+        <v>26282839.43644052</v>
       </c>
       <c r="M69">
-        <v>4693815.331074902</v>
+        <v>74044308.15247531</v>
       </c>
       <c r="N69">
-        <v>809377.5956919756</v>
+        <v>-4369519.327169776</v>
       </c>
       <c r="O69">
-        <v>10932234.91623322</v>
+        <v>189460055.1719365</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>cancer</t>
+          <t>diab2</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -4052,46 +4052,46 @@
         </is>
       </c>
       <c r="D70">
-        <v>763.2211304242132</v>
+        <v>434.4318067093736</v>
       </c>
       <c r="E70">
-        <v>161.9130279589</v>
+        <v>-26.40581408005138</v>
       </c>
       <c r="F70">
-        <v>1540.802543080427</v>
+        <v>850.078083122454</v>
       </c>
       <c r="G70">
-        <v>354.876122762386</v>
+        <v>1401.928932099329</v>
       </c>
       <c r="H70">
-        <v>59.5883228914692</v>
+        <v>-63.41434515004669</v>
       </c>
       <c r="I70">
-        <v>827.25604497565</v>
+        <v>3482.856745298585</v>
       </c>
       <c r="J70">
-        <v>11301015.27819134</v>
+        <v>32669706.29635156</v>
       </c>
       <c r="K70">
-        <v>2397446.204987432</v>
+        <v>-1985743.624633945</v>
       </c>
       <c r="L70">
-        <v>22814663.25539189</v>
+        <v>63926721.92889177</v>
       </c>
       <c r="M70">
-        <v>47198524.32739735</v>
+        <v>186456547.9692107</v>
       </c>
       <c r="N70">
-        <v>7925246.944565404</v>
+        <v>-8434107.904956209</v>
       </c>
       <c r="O70">
-        <v>110025053.9817614</v>
+        <v>463219947.1247118</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>cancer</t>
+          <t>diab2</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -4105,46 +4105,46 @@
         </is>
       </c>
       <c r="D71">
-        <v>86.44538873473503</v>
+        <v>372.9115888772673</v>
       </c>
       <c r="E71">
-        <v>18.84099826382769</v>
+        <v>-29.57088336614647</v>
       </c>
       <c r="F71">
-        <v>174.3620837390739</v>
+        <v>751.5527211501685</v>
       </c>
       <c r="G71">
-        <v>31.25430896301283</v>
+        <v>960.9937280867418</v>
       </c>
       <c r="H71">
-        <v>5.389333763521678</v>
+        <v>-56.71037751500126</v>
       </c>
       <c r="I71">
-        <v>72.793542912977</v>
+        <v>2458.932081157039</v>
       </c>
       <c r="J71">
-        <v>1279996.870995223</v>
+        <v>28043324.39515935</v>
       </c>
       <c r="K71">
-        <v>278978.6612924967</v>
+        <v>-2223760.00001758</v>
       </c>
       <c r="L71">
-        <v>2581779.373924466</v>
+        <v>56517516.18321388</v>
       </c>
       <c r="M71">
-        <v>4156823.092080706</v>
+        <v>127812165.8355367</v>
       </c>
       <c r="N71">
-        <v>716781.3905483831</v>
+        <v>-7542480.209495167</v>
       </c>
       <c r="O71">
-        <v>9681541.207425941</v>
+        <v>327037966.7938862</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>cancer</t>
+          <t>diab2</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -4158,46 +4158,46 @@
         </is>
       </c>
       <c r="D72">
-        <v>85.65091096210662</v>
+        <v>271.268580536048</v>
       </c>
       <c r="E72">
-        <v>18.66783975816489</v>
+        <v>-21.51086690569907</v>
       </c>
       <c r="F72">
-        <v>172.7596061292506</v>
+        <v>546.7050259237438</v>
       </c>
       <c r="G72">
-        <v>31.19312998146979</v>
+        <v>694.4691151815515</v>
       </c>
       <c r="H72">
-        <v>5.378784371716575</v>
+        <v>-40.98216725395754</v>
       </c>
       <c r="I72">
-        <v>72.65105264631981</v>
+        <v>1776.965173427772</v>
       </c>
       <c r="J72">
-        <v>1268233.038615913</v>
+        <v>20399668.52489135</v>
       </c>
       <c r="K72">
-        <v>276414.7032991477</v>
+        <v>-1617638.702175478</v>
       </c>
       <c r="L72">
-        <v>2558051.487955814</v>
+        <v>41112764.65449149</v>
       </c>
       <c r="M72">
-        <v>4148686.287535482</v>
+        <v>92364392.31914635</v>
       </c>
       <c r="N72">
-        <v>715378.3214383045</v>
+        <v>-5450628.244776353</v>
       </c>
       <c r="O72">
-        <v>9662590.001960535</v>
+        <v>236336368.0658937</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>cancer</t>
+          <t>diab2</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -4211,46 +4211,46 @@
         </is>
       </c>
       <c r="D73">
-        <v>913.2515621775354</v>
+        <v>604.0082982617715</v>
       </c>
       <c r="E73">
-        <v>196.4412974273078</v>
+        <v>-42.69420801891535</v>
       </c>
       <c r="F73">
-        <v>1842.851684239497</v>
+        <v>1200.830613622297</v>
       </c>
       <c r="G73">
-        <v>347.4370554454907</v>
+        <v>1548.689763535536</v>
       </c>
       <c r="H73">
-        <v>59.13434328091773</v>
+        <v>-81.46556071714882</v>
       </c>
       <c r="I73">
-        <v>809.5560383513604</v>
+        <v>3909.090112850674</v>
       </c>
       <c r="J73">
-        <v>13522515.88116276</v>
+        <v>45422028.03758345</v>
       </c>
       <c r="K73">
-        <v>2908706.291006151</v>
+        <v>-3210647.137230455</v>
       </c>
       <c r="L73">
-        <v>27287104.88853423</v>
+        <v>90303662.97501042</v>
       </c>
       <c r="M73">
-        <v>46209128.37425026</v>
+        <v>205975738.5502263</v>
       </c>
       <c r="N73">
-        <v>7864867.656362059</v>
+        <v>-10834919.57538079</v>
       </c>
       <c r="O73">
-        <v>107670953.1007309</v>
+        <v>519908985.0091397</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>cancer</t>
+          <t>diab2</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -4264,46 +4264,46 @@
         </is>
       </c>
       <c r="D74">
-        <v>158.7843408907523</v>
+        <v>521.9219867141205</v>
       </c>
       <c r="E74">
-        <v>34.60746183033353</v>
+        <v>-41.3870060778146</v>
       </c>
       <c r="F74">
-        <v>320.2712018312939</v>
+        <v>1051.862964420234</v>
       </c>
       <c r="G74">
-        <v>44.28433272727031</v>
+        <v>980.8400800989752</v>
       </c>
       <c r="H74">
-        <v>7.636164659552877</v>
+        <v>-57.88155489318342</v>
       </c>
       <c r="I74">
-        <v>103.1414093515876</v>
+        <v>2509.713715033026</v>
       </c>
       <c r="J74">
-        <v>2351119.735569369</v>
+        <v>39249055.32288864</v>
       </c>
       <c r="K74">
-        <v>512432.6873217486</v>
+        <v>-3112344.244057731</v>
       </c>
       <c r="L74">
-        <v>4742255.685515965</v>
+        <v>79101146.78736587</v>
       </c>
       <c r="M74">
-        <v>5889816.252726952</v>
+        <v>130451730.6531637</v>
       </c>
       <c r="N74">
-        <v>1015609.899720533</v>
+        <v>-7698246.800793394</v>
       </c>
       <c r="O74">
-        <v>13717807.44376115</v>
+        <v>333791924.0993924</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>cancer</t>
+          <t>diab2</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -4317,46 +4317,46 @@
         </is>
       </c>
       <c r="D75">
-        <v>296.1718697810469</v>
+        <v>318.5954544033222</v>
       </c>
       <c r="E75">
-        <v>64.55143259824463</v>
+        <v>-25.26376037684879</v>
       </c>
       <c r="F75">
-        <v>597.3846044973687</v>
+        <v>642.0859202144455</v>
       </c>
       <c r="G75">
-        <v>80.79676447437178</v>
+        <v>595.3645659758121</v>
       </c>
       <c r="H75">
-        <v>13.93218232021549</v>
+        <v>-35.13378735859569</v>
       </c>
       <c r="I75">
-        <v>188.1814999958945</v>
+        <v>1523.382503418291</v>
       </c>
       <c r="J75">
-        <v>4385416.875847962</v>
+        <v>23958696.76658422</v>
       </c>
       <c r="K75">
-        <v>955813.0624822077</v>
+        <v>-1899860.044099406</v>
       </c>
       <c r="L75">
-        <v>8845473.838792544</v>
+        <v>48285503.28604659</v>
       </c>
       <c r="M75">
-        <v>10745969.67509145</v>
+        <v>79183487.274783</v>
       </c>
       <c r="N75">
-        <v>1852980.248588661</v>
+        <v>-4672793.718693227</v>
       </c>
       <c r="O75">
-        <v>25028139.49945396</v>
+        <v>202609872.9546327</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>cancer</t>
+          <t>diab2</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -4370,46 +4370,46 @@
         </is>
       </c>
       <c r="D76">
-        <v>671.9227769581798</v>
+        <v>750.2320052253166</v>
       </c>
       <c r="E76">
-        <v>146.1820420978079</v>
+        <v>-58.59888655784636</v>
       </c>
       <c r="F76">
-        <v>1355.363720866856</v>
+        <v>1509.165805229692</v>
       </c>
       <c r="G76">
-        <v>182.0209904824632</v>
+        <v>1403.175810284757</v>
       </c>
       <c r="H76">
-        <v>31.33309601898063</v>
+        <v>-81.56229408571875</v>
       </c>
       <c r="I76">
-        <v>423.9642478757406</v>
+        <v>3583.652303055574</v>
       </c>
       <c r="J76">
-        <v>9949160.558419764</v>
+        <v>56418197.02494904</v>
       </c>
       <c r="K76">
-        <v>2164517.49734224</v>
+        <v>-4406694.868036607</v>
       </c>
       <c r="L76">
-        <v>20068870.61487554</v>
+        <v>113490777.719078</v>
       </c>
       <c r="M76">
-        <v>24208791.73416761</v>
+        <v>186622382.7678727</v>
       </c>
       <c r="N76">
-        <v>4167301.770524424</v>
+        <v>-10847785.11340059</v>
       </c>
       <c r="O76">
-        <v>56387244.96747349</v>
+        <v>476625756.3063914</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>cancer</t>
+          <t>diab2</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -4423,46 +4423,46 @@
         </is>
       </c>
       <c r="D77">
-        <v>125.8375198184148</v>
+        <v>565.0595741338583</v>
       </c>
       <c r="E77">
-        <v>27.426616122908</v>
+        <v>-44.80770043093585</v>
       </c>
       <c r="F77">
-        <v>253.8168025992053</v>
+        <v>1138.800920161337</v>
       </c>
       <c r="G77">
-        <v>18.12091757151336</v>
+        <v>714.2547167528863</v>
       </c>
       <c r="H77">
-        <v>3.124678680617224</v>
+        <v>-42.14975961348913</v>
       </c>
       <c r="I77">
-        <v>42.20492580480722</v>
+        <v>1827.5913627845</v>
       </c>
       <c r="J77">
-        <v>1863276.155951269</v>
+        <v>42493045.03444033</v>
       </c>
       <c r="K77">
-        <v>406105.9049318989</v>
+        <v>-3369583.880106805</v>
       </c>
       <c r="L77">
-        <v>3758265.396086434</v>
+        <v>85638967.99705264</v>
       </c>
       <c r="M77">
-        <v>2410082.037011277</v>
+        <v>94995877.32813388</v>
       </c>
       <c r="N77">
-        <v>415582.2645220908</v>
+        <v>-5605918.028594054</v>
       </c>
       <c r="O77">
-        <v>5613255.13203936</v>
+        <v>243069651.2503386</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>cancer</t>
+          <t>diab2</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -4476,46 +4476,46 @@
         </is>
       </c>
       <c r="D78">
-        <v>387.9797495216186</v>
+        <v>417.7885341112005</v>
       </c>
       <c r="E78">
-        <v>84.56119978323181</v>
+        <v>-33.12950410340297</v>
       </c>
       <c r="F78">
-        <v>782.562940201936</v>
+        <v>841.9961166182869</v>
       </c>
       <c r="G78">
-        <v>69.03331363332994</v>
+        <v>539.9056050504836</v>
       </c>
       <c r="H78">
-        <v>11.90375280452271</v>
+        <v>-31.86103071227875</v>
       </c>
       <c r="I78">
-        <v>160.7835733735068</v>
+        <v>1381.477500064712</v>
       </c>
       <c r="J78">
-        <v>5744816.151166611</v>
+        <v>31418115.55369638</v>
       </c>
       <c r="K78">
-        <v>1252097.685190313</v>
+        <v>-2491371.838080009</v>
       </c>
       <c r="L78">
-        <v>11587409.45557008</v>
+        <v>63318949.96581168</v>
       </c>
       <c r="M78">
-        <v>9181430.713232882</v>
+        <v>71807445.47171432</v>
       </c>
       <c r="N78">
-        <v>1583199.12300152</v>
+        <v>-4237517.084733074</v>
       </c>
       <c r="O78">
-        <v>21384215.2586764</v>
+        <v>183736507.5086067</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>cancer</t>
+          <t>diab2</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -4529,46 +4529,46 @@
         </is>
       </c>
       <c r="D79">
-        <v>700.5790805836583</v>
+        <v>634.757902256956</v>
       </c>
       <c r="E79">
-        <v>152.6930404750086</v>
+        <v>-50.33458989540249</v>
       </c>
       <c r="F79">
-        <v>1413.082063745614</v>
+        <v>1279.268445770391</v>
       </c>
       <c r="G79">
-        <v>122.5283210164019</v>
+        <v>814.5378109823686</v>
       </c>
       <c r="H79">
-        <v>21.12815926350471</v>
+        <v>-48.06768807224011</v>
       </c>
       <c r="I79">
-        <v>285.3773092381527</v>
+        <v>2084.189621848592</v>
       </c>
       <c r="J79">
-        <v>10373474.44620223</v>
+        <v>47734429.00762533</v>
       </c>
       <c r="K79">
-        <v>2260925.85031345</v>
+        <v>-3785211.494724163</v>
       </c>
       <c r="L79">
-        <v>20923506.11788131</v>
+        <v>96202266.39037931</v>
       </c>
       <c r="M79">
-        <v>16296266.69518145</v>
+        <v>108333528.860655</v>
       </c>
       <c r="N79">
-        <v>2810045.182046126</v>
+        <v>-6393002.513607934</v>
       </c>
       <c r="O79">
-        <v>37955182.12867431</v>
+        <v>277197219.7058628</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>cancer</t>
+          <t>diab2</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -4582,46 +4582,46 @@
         </is>
       </c>
       <c r="D80">
-        <v>14.50756555704248</v>
+        <v>106.6654225461977</v>
       </c>
       <c r="E80">
-        <v>3.161961805867568</v>
+        <v>-8.458280362942812</v>
       </c>
       <c r="F80">
-        <v>29.26205084541126</v>
+        <v>214.9696897556374</v>
       </c>
       <c r="G80">
-        <v>1.289945196023605</v>
+        <v>74.7066357001186</v>
       </c>
       <c r="H80">
-        <v>0.2224315759548479</v>
+        <v>-4.408604749028129</v>
       </c>
       <c r="I80">
-        <v>3.004375527651464</v>
+        <v>191.1547784646442</v>
       </c>
       <c r="J80">
-        <v>214813.5232031279</v>
+        <v>8021346.440896623</v>
       </c>
       <c r="K80">
-        <v>46819.16845948108</v>
+        <v>-636071.1415736622</v>
       </c>
       <c r="L80">
-        <v>433283.1868680046</v>
+        <v>16165935.63931368</v>
       </c>
       <c r="M80">
-        <v>171562.7110711395</v>
+        <v>9935982.548115773</v>
       </c>
       <c r="N80">
-        <v>29583.39960199477</v>
+        <v>-586344.4316207411</v>
       </c>
       <c r="O80">
-        <v>399581.9451776448</v>
+        <v>25423585.53579768</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>cancer</t>
+          <t>diab2</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -4635,46 +4635,46 @@
         </is>
       </c>
       <c r="D81">
-        <v>252.4936881197808</v>
+        <v>90.84520596236823</v>
       </c>
       <c r="E81">
-        <v>55.03165882092467</v>
+        <v>-7.203779850271619</v>
       </c>
       <c r="F81">
-        <v>509.2848356159739</v>
+        <v>183.0861892761822</v>
       </c>
       <c r="G81">
-        <v>20.4689094265097</v>
+        <v>61.83504622700616</v>
       </c>
       <c r="H81">
-        <v>3.529554430568339</v>
+        <v>-3.649023622841647</v>
       </c>
       <c r="I81">
-        <v>47.67356841847872</v>
+        <v>158.2197411528674</v>
       </c>
       <c r="J81">
-        <v>3738674.039989593</v>
+        <v>6831650.33357606</v>
       </c>
       <c r="K81">
-        <v>814853.7721614313</v>
+        <v>-541731.448520276</v>
       </c>
       <c r="L81">
-        <v>7540980.560965745</v>
+        <v>13768264.51975819</v>
       </c>
       <c r="M81">
-        <v>2722364.95372579</v>
+        <v>8224061.148191819</v>
       </c>
       <c r="N81">
-        <v>469430.739265589</v>
+        <v>-485320.1418379391</v>
       </c>
       <c r="O81">
-        <v>6340584.599657671</v>
+        <v>21043225.57333136</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>cancer</t>
+          <t>diab2</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -4688,46 +4688,46 @@
         </is>
       </c>
       <c r="D82">
-        <v>140.3242830683551</v>
+        <v>136.1006334381682</v>
       </c>
       <c r="E82">
-        <v>30.58404401160841</v>
+        <v>-10.79241320865276</v>
       </c>
       <c r="F82">
-        <v>283.0368947737608</v>
+        <v>274.2923643608771</v>
       </c>
       <c r="G82">
-        <v>12.41851265799104</v>
+        <v>96.44114884562255</v>
       </c>
       <c r="H82">
-        <v>2.141385037168351</v>
+        <v>-5.691206715682126</v>
       </c>
       <c r="I82">
-        <v>28.92361290581155</v>
+        <v>246.7677237730493</v>
       </c>
       <c r="J82">
-        <v>2077781.659393134</v>
+        <v>10234903.73518368</v>
       </c>
       <c r="K82">
-        <v>452857.9396798862</v>
+        <v>-811600.2657038979</v>
       </c>
       <c r="L82">
-        <v>4190927.300915076</v>
+        <v>20627060.09230229</v>
       </c>
       <c r="M82">
-        <v>1651662.183512808</v>
+        <v>12826672.7964678</v>
       </c>
       <c r="N82">
-        <v>284804.2099433907</v>
+        <v>-756930.4931857227</v>
       </c>
       <c r="O82">
-        <v>3846840.516472937</v>
+        <v>32820107.26181556</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>cancer</t>
+          <t>diab2</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -4741,46 +4741,46 @@
         </is>
       </c>
       <c r="D83">
-        <v>11.97023672269221</v>
+        <v>3.991716176127684</v>
       </c>
       <c r="E83">
-        <v>2.608944359101869</v>
+        <v>-0.3165323282937225</v>
       </c>
       <c r="F83">
-        <v>24.14420767107901</v>
+        <v>8.044762468391044</v>
       </c>
       <c r="G83">
-        <v>0.05591446066884381</v>
+        <v>0.5115473908538007</v>
       </c>
       <c r="H83">
-        <v>0.009641604653884158</v>
+        <v>-0.03018754941292878</v>
       </c>
       <c r="I83">
-        <v>0.1302288173118866</v>
+        <v>1.308916232894551</v>
       </c>
       <c r="J83">
-        <v>177243.2951529035</v>
+        <v>300181.0481609779</v>
       </c>
       <c r="K83">
-        <v>38630.63912522138</v>
+        <v>-23803.54762001623</v>
       </c>
       <c r="L83">
-        <v>357503.282985667</v>
+        <v>604974.1823854749</v>
       </c>
       <c r="M83">
-        <v>7436.623268956228</v>
+        <v>68035.80298355549</v>
       </c>
       <c r="N83">
-        <v>1282.333418966593</v>
+        <v>-4014.944071919528</v>
       </c>
       <c r="O83">
-        <v>17320.43270248092</v>
+        <v>174085.8589749753</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>cancer</t>
+          <t>diab2</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -4794,46 +4794,46 @@
         </is>
       </c>
       <c r="D84">
-        <v>288.4354640597416</v>
+        <v>2.999099097621881</v>
       </c>
       <c r="E84">
-        <v>62.86526276435698</v>
+        <v>-0.2378204707617101</v>
       </c>
       <c r="F84">
-        <v>581.7801189144842</v>
+        <v>6.044277397232065</v>
       </c>
       <c r="G84">
-        <v>3.175327044223821</v>
+        <v>0.3908539039953398</v>
       </c>
       <c r="H84">
-        <v>0.5475372138258211</v>
+        <v>-0.02306515828455687</v>
       </c>
       <c r="I84">
-        <v>7.395566023551595</v>
+        <v>1.00009310725998</v>
       </c>
       <c r="J84">
-        <v>4270863.916332592</v>
+        <v>225535.2512402629</v>
       </c>
       <c r="K84">
-        <v>930845.9457518338</v>
+        <v>-17884.33722175135</v>
       </c>
       <c r="L84">
-        <v>8614418.220766762</v>
+        <v>454535.7045492484</v>
       </c>
       <c r="M84">
-        <v>422318.4968817682</v>
+        <v>51983.56923138019</v>
       </c>
       <c r="N84">
-        <v>72822.44943883421</v>
+        <v>-3067.666051846064</v>
       </c>
       <c r="O84">
-        <v>983610.2811323621</v>
+        <v>133012.3832655773</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>cancer</t>
+          <t>diab2</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -4847,46 +4847,46 @@
         </is>
       </c>
       <c r="D85">
-        <v>56.01924821916865</v>
+        <v>4.467609444021941</v>
       </c>
       <c r="E85">
-        <v>12.20954146758567</v>
+        <v>-0.3542693810949135</v>
       </c>
       <c r="F85">
-        <v>112.9919477713662</v>
+        <v>9.003860793921204</v>
       </c>
       <c r="G85">
-        <v>0.6014206486424277</v>
+        <v>0.5731216266927552</v>
       </c>
       <c r="H85">
-        <v>0.1037059117718337</v>
+        <v>-0.03382118203462903</v>
       </c>
       <c r="I85">
-        <v>1.400752128210956</v>
+        <v>1.466468628349382</v>
       </c>
       <c r="J85">
-        <v>829477.0083812297</v>
+        <v>335968.6977998942</v>
       </c>
       <c r="K85">
-        <v>180786.680510541</v>
+        <v>-26641.41172771858</v>
       </c>
       <c r="L85">
-        <v>1673071.770650617</v>
+        <v>677099.3355636692</v>
       </c>
       <c r="M85">
-        <v>79988.94626944288</v>
+        <v>76225.17635013645</v>
       </c>
       <c r="N85">
-        <v>13792.88626565389</v>
+        <v>-4498.217210605661</v>
       </c>
       <c r="O85">
-        <v>186300.0330520571</v>
+        <v>195040.3275704678</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>diab2</t>
+          <t>dem</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -4900,46 +4900,46 @@
         </is>
       </c>
       <c r="D86">
-        <v>2.034591855039652</v>
+        <v>0</v>
       </c>
       <c r="E86">
-        <v>-0.1613376474145712</v>
+        <v>0</v>
       </c>
       <c r="F86">
-        <v>4.10044388721928</v>
+        <v>0</v>
       </c>
       <c r="G86">
-        <v>1.38171561230097</v>
+        <v>0</v>
       </c>
       <c r="H86">
-        <v>-0.08153811175017876</v>
+        <v>0</v>
       </c>
       <c r="I86">
-        <v>3.535449552711042</v>
+        <v>0</v>
       </c>
       <c r="J86">
-        <v>153003.3420908368</v>
+        <v>0</v>
       </c>
       <c r="K86">
-        <v>-12132.75242322317</v>
+        <v>0</v>
       </c>
       <c r="L86">
-        <v>308357.4807627773</v>
+        <v>0</v>
       </c>
       <c r="M86">
-        <v>183768.1764360289</v>
+        <v>0</v>
       </c>
       <c r="N86">
-        <v>-10844.56886277378</v>
+        <v>0</v>
       </c>
       <c r="O86">
-        <v>470214.7905105685</v>
+        <v>0</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>diab2</t>
+          <t>dem</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -4953,46 +4953,46 @@
         </is>
       </c>
       <c r="D87">
-        <v>10.32304018140615</v>
+        <v>0</v>
       </c>
       <c r="E87">
-        <v>-0.8185892482115235</v>
+        <v>0</v>
       </c>
       <c r="F87">
-        <v>20.80468714377165</v>
+        <v>0</v>
       </c>
       <c r="G87">
-        <v>6.891997720044627</v>
+        <v>0</v>
       </c>
       <c r="H87">
-        <v>-0.4067121159202645</v>
+        <v>0</v>
       </c>
       <c r="I87">
-        <v>17.63482299808435</v>
+        <v>0</v>
       </c>
       <c r="J87">
-        <v>776302.9446819227</v>
+        <v>0</v>
       </c>
       <c r="K87">
-        <v>-61558.73005475487</v>
+        <v>0</v>
       </c>
       <c r="L87">
-        <v>1564533.277898771</v>
+        <v>0</v>
       </c>
       <c r="M87">
-        <v>916635.6967659353</v>
+        <v>0</v>
       </c>
       <c r="N87">
-        <v>-54092.71141739518</v>
+        <v>0</v>
       </c>
       <c r="O87">
-        <v>2345431.458745218</v>
+        <v>0</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>diab2</t>
+          <t>dem</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -5006,46 +5006,46 @@
         </is>
       </c>
       <c r="D88">
-        <v>82.56752987685582</v>
+        <v>0</v>
       </c>
       <c r="E88">
-        <v>-6.54738245912462</v>
+        <v>0</v>
       </c>
       <c r="F88">
-        <v>166.403656009795</v>
+        <v>0</v>
       </c>
       <c r="G88">
-        <v>54.74178212502667</v>
+        <v>0</v>
       </c>
       <c r="H88">
-        <v>-3.230434330029245</v>
+        <v>0</v>
       </c>
       <c r="I88">
-        <v>140.0699300243374</v>
+        <v>0</v>
       </c>
       <c r="J88">
-        <v>6209160.814269436</v>
+        <v>0</v>
       </c>
       <c r="K88">
-        <v>-492369.7083086311</v>
+        <v>0</v>
       </c>
       <c r="L88">
-        <v>12513721.33559261</v>
+        <v>0</v>
       </c>
       <c r="M88">
-        <v>7280657.022628548</v>
+        <v>0</v>
       </c>
       <c r="N88">
-        <v>-429647.7658938896</v>
+        <v>0</v>
       </c>
       <c r="O88">
-        <v>18629300.69323687</v>
+        <v>0</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>diab2</t>
+          <t>dem</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -5059,46 +5059,46 @@
         </is>
       </c>
       <c r="D89">
-        <v>11.32352231931893</v>
+        <v>0</v>
       </c>
       <c r="E89">
-        <v>-0.8979247837447698</v>
+        <v>0</v>
       </c>
       <c r="F89">
-        <v>22.82102317525379</v>
+        <v>0</v>
       </c>
       <c r="G89">
-        <v>6.282021172745131</v>
+        <v>0</v>
       </c>
       <c r="H89">
-        <v>-0.3707160430410773</v>
+        <v>0</v>
       </c>
       <c r="I89">
-        <v>16.07405224894087</v>
+        <v>0</v>
       </c>
       <c r="J89">
-        <v>851540.2019351025</v>
+        <v>0</v>
       </c>
       <c r="K89">
-        <v>-67524.84166239045</v>
+        <v>0</v>
       </c>
       <c r="L89">
-        <v>1716163.76380226</v>
+        <v>0</v>
       </c>
       <c r="M89">
-        <v>835508.8159751025</v>
+        <v>0</v>
       </c>
       <c r="N89">
-        <v>-49305.23372446328</v>
+        <v>0</v>
       </c>
       <c r="O89">
-        <v>2137848.949109136</v>
+        <v>0</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>diab2</t>
+          <t>dem</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -5112,46 +5112,46 @@
         </is>
       </c>
       <c r="D90">
-        <v>13.30123046683064</v>
+        <v>0</v>
       </c>
       <c r="E90">
-        <v>-1.054751706550849</v>
+        <v>0</v>
       </c>
       <c r="F90">
-        <v>26.80682566634367</v>
+        <v>0</v>
       </c>
       <c r="G90">
-        <v>7.444385890461114</v>
+        <v>0</v>
       </c>
       <c r="H90">
-        <v>-0.4393097705808294</v>
+        <v>0</v>
       </c>
       <c r="I90">
-        <v>19.04824012432616</v>
+        <v>0</v>
       </c>
       <c r="J90">
-        <v>1000265.832336131</v>
+        <v>0</v>
       </c>
       <c r="K90">
-        <v>-79318.38308433043</v>
+        <v>0</v>
       </c>
       <c r="L90">
-        <v>2015900.09693471</v>
+        <v>0</v>
       </c>
       <c r="M90">
-        <v>990103.3234313282</v>
+        <v>0</v>
       </c>
       <c r="N90">
-        <v>-58428.19948725031</v>
+        <v>0</v>
       </c>
       <c r="O90">
-        <v>2533415.93653538</v>
+        <v>0</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>diab2</t>
+          <t>dem</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -5165,46 +5165,46 @@
         </is>
       </c>
       <c r="D91">
-        <v>137.2204174439248</v>
+        <v>0</v>
       </c>
       <c r="E91">
-        <v>-10.72663394413109</v>
+        <v>0</v>
       </c>
       <c r="F91">
-        <v>276.0598540048709</v>
+        <v>0</v>
       </c>
       <c r="G91">
-        <v>74.67002715017858</v>
+        <v>0</v>
       </c>
       <c r="H91">
-        <v>-4.34399838942994</v>
+        <v>0</v>
       </c>
       <c r="I91">
-        <v>190.7238860861294</v>
+        <v>0</v>
       </c>
       <c r="J91">
-        <v>10319112.61220057</v>
+        <v>0</v>
       </c>
       <c r="K91">
-        <v>-806653.5992326026</v>
+        <v>0</v>
       </c>
       <c r="L91">
-        <v>20759977.08102028</v>
+        <v>0</v>
       </c>
       <c r="M91">
-        <v>9931113.610973751</v>
+        <v>0</v>
       </c>
       <c r="N91">
-        <v>-577751.785794182</v>
+        <v>0</v>
       </c>
       <c r="O91">
-        <v>25366276.84945521</v>
+        <v>0</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>diab2</t>
+          <t>dem</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -5218,46 +5218,46 @@
         </is>
       </c>
       <c r="D92">
-        <v>24.3024898317341</v>
+        <v>70.89371061040806</v>
       </c>
       <c r="E92">
-        <v>-1.927121907057949</v>
+        <v>51.72861550672907</v>
       </c>
       <c r="F92">
-        <v>48.97837157261259</v>
+        <v>88.87937326625558</v>
       </c>
       <c r="G92">
-        <v>9.792966687939636</v>
+        <v>551.9102394964336</v>
       </c>
       <c r="H92">
-        <v>-0.5779047475893189</v>
+        <v>322.9349502980362</v>
       </c>
       <c r="I92">
-        <v>25.05764528413598</v>
+        <v>788.0336211011796</v>
       </c>
       <c r="J92">
-        <v>1827571.537836237</v>
+        <v>1193779.192968661</v>
       </c>
       <c r="K92">
-        <v>-144921.4945326648</v>
+        <v>871058.1565178109</v>
       </c>
       <c r="L92">
-        <v>3683222.520632039</v>
+        <v>1496639.766430478</v>
       </c>
       <c r="M92">
-        <v>1302464.569495972</v>
+        <v>73404061.85302567</v>
       </c>
       <c r="N92">
-        <v>-76861.33142937941</v>
+        <v>42950348.38963881</v>
       </c>
       <c r="O92">
-        <v>3332666.822790085</v>
+        <v>104808471.6064569</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>diab2</t>
+          <t>dem</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -5271,46 +5271,46 @@
         </is>
       </c>
       <c r="D93">
-        <v>27.31335587990205</v>
+        <v>54.75868394419028</v>
       </c>
       <c r="E93">
-        <v>-2.165875465265996</v>
+        <v>42.35670012243911</v>
       </c>
       <c r="F93">
-        <v>55.04636366245887</v>
+        <v>66.49867966287569</v>
       </c>
       <c r="G93">
-        <v>11.71660388721152</v>
+        <v>423.9259822044121</v>
       </c>
       <c r="H93">
-        <v>-0.6914228576292235</v>
+        <v>262.9557083743219</v>
       </c>
       <c r="I93">
-        <v>29.97973070837069</v>
+        <v>586.3177952289719</v>
       </c>
       <c r="J93">
-        <v>2053991.675524513</v>
+        <v>922081.4789362205</v>
       </c>
       <c r="K93">
-        <v>-162876.0008634682</v>
+        <v>713244.4733617528</v>
       </c>
       <c r="L93">
-        <v>4139541.593780568</v>
+        <v>1119771.266843164</v>
       </c>
       <c r="M93">
-        <v>1558308.316999133</v>
+        <v>56382155.63318681</v>
       </c>
       <c r="N93">
-        <v>-91959.24006468673</v>
+        <v>34973109.21378481</v>
       </c>
       <c r="O93">
-        <v>3987304.184213302</v>
+        <v>77980266.76545326</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>diab2</t>
+          <t>dem</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -5324,46 +5324,46 @@
         </is>
       </c>
       <c r="D94">
-        <v>167.7846143685232</v>
+        <v>108.9687259484035</v>
       </c>
       <c r="E94">
-        <v>-13.15342675449299</v>
+        <v>72.97205094551195</v>
       </c>
       <c r="F94">
-        <v>337.6677683109382</v>
+        <v>142.4090376913466</v>
       </c>
       <c r="G94">
-        <v>74.55818841420243</v>
+        <v>843.2877083010039</v>
       </c>
       <c r="H94">
-        <v>-4.350752930741296</v>
+        <v>452.8495091014402</v>
       </c>
       <c r="I94">
-        <v>190.5098362956604</v>
+        <v>1255.146642357282</v>
       </c>
       <c r="J94">
-        <v>12617570.7851273</v>
+        <v>1834924.376245168</v>
       </c>
       <c r="K94">
-        <v>-989150.8453646286</v>
+        <v>1228776.365871474</v>
       </c>
       <c r="L94">
-        <v>25392953.84475085</v>
+        <v>2398025.785684585</v>
       </c>
       <c r="M94">
-        <v>9916239.059088923</v>
+        <v>112157265.2040335</v>
       </c>
       <c r="N94">
-        <v>-578650.1397885924</v>
+        <v>60228984.71049154</v>
       </c>
       <c r="O94">
-        <v>25337808.22732283</v>
+        <v>166934503.4335185</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>diab2</t>
+          <t>dem</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -5377,46 +5377,46 @@
         </is>
       </c>
       <c r="D95">
-        <v>42.49565527050481</v>
+        <v>136.1610218936238</v>
       </c>
       <c r="E95">
-        <v>-3.369790864787665</v>
+        <v>100.3072000231572</v>
       </c>
       <c r="F95">
-        <v>85.64422857375669</v>
+        <v>169.8495780447139</v>
       </c>
       <c r="G95">
-        <v>14.02134586441885</v>
+        <v>791.7274804248713</v>
       </c>
       <c r="H95">
-        <v>-0.8274308083390765</v>
+        <v>467.7119611090891</v>
       </c>
       <c r="I95">
-        <v>35.87696377130362</v>
+        <v>1124.787313834789</v>
       </c>
       <c r="J95">
-        <v>3195715.771997234</v>
+        <v>2292815.447666733</v>
       </c>
       <c r="K95">
-        <v>-253411.6428228971</v>
+        <v>1689072.941189943</v>
       </c>
       <c r="L95">
-        <v>6440531.632975081</v>
+        <v>2860097.044694935</v>
       </c>
       <c r="M95">
-        <v>1864838.999967708</v>
+        <v>105299754.8965079</v>
       </c>
       <c r="N95">
-        <v>-110048.2975090972</v>
+        <v>62205690.82750886</v>
       </c>
       <c r="O95">
-        <v>4771636.181583381</v>
+        <v>149596712.7400269</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>diab2</t>
+          <t>dem</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -5430,46 +5430,46 @@
         </is>
       </c>
       <c r="D96">
-        <v>81.25080893635611</v>
+        <v>85.65048800681426</v>
       </c>
       <c r="E96">
-        <v>-6.442970039348376</v>
+        <v>71.09288186277985</v>
       </c>
       <c r="F96">
-        <v>163.7499835701498</v>
+        <v>99.66664873105965</v>
       </c>
       <c r="G96">
-        <v>25.87988917340395</v>
+        <v>495.9247209530446</v>
       </c>
       <c r="H96">
-        <v>-1.527229826975163</v>
+        <v>330.0923708508183</v>
       </c>
       <c r="I96">
-        <v>66.21988040646993</v>
+        <v>657.2321370998264</v>
       </c>
       <c r="J96">
-        <v>6110142.082822916</v>
+        <v>1442268.56754675</v>
       </c>
       <c r="K96">
-        <v>-484517.7899290375</v>
+        <v>1197133.037687348</v>
       </c>
       <c r="L96">
-        <v>12314162.51445884</v>
+        <v>1678286.697982312</v>
       </c>
       <c r="M96">
-        <v>3442025.260062726</v>
+        <v>65957987.88675493</v>
       </c>
       <c r="N96">
-        <v>-203121.5669876967</v>
+        <v>43902285.32315883</v>
       </c>
       <c r="O96">
-        <v>8807244.094060501</v>
+        <v>87411874.23427692</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>diab2</t>
+          <t>dem</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -5483,46 +5483,46 @@
         </is>
       </c>
       <c r="D97">
-        <v>179.6189298042697</v>
+        <v>184.9351656205262</v>
       </c>
       <c r="E97">
-        <v>-14.23037663250373</v>
+        <v>124.6930125106734</v>
       </c>
       <c r="F97">
-        <v>361.9566907335621</v>
+        <v>240.9722314862467</v>
       </c>
       <c r="G97">
-        <v>56.56127990590623</v>
+        <v>1070.702545194627</v>
       </c>
       <c r="H97">
-        <v>-3.334770672309015</v>
+        <v>578.9151346672759</v>
       </c>
       <c r="I97">
-        <v>144.7091534159808</v>
+        <v>1588.910202978805</v>
       </c>
       <c r="J97">
-        <v>13507523.1402109</v>
+        <v>3114123.25388403</v>
       </c>
       <c r="K97">
-        <v>-1070138.553140914</v>
+        <v>2099705.63766723</v>
       </c>
       <c r="L97">
-        <v>27219505.09985463</v>
+        <v>4057731.405996906</v>
       </c>
       <c r="M97">
-        <v>7522650.227485529</v>
+        <v>142403438.5108854</v>
       </c>
       <c r="N97">
-        <v>-443524.4994170991</v>
+        <v>76995712.91074769</v>
       </c>
       <c r="O97">
-        <v>19246317.40432544</v>
+        <v>211325056.996181</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>diab2</t>
+          <t>dem</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -5536,46 +5536,46 @@
         </is>
       </c>
       <c r="D98">
-        <v>31.86783382843173</v>
+        <v>653.9674328166136</v>
       </c>
       <c r="E98">
-        <v>-2.527033284509824</v>
+        <v>489.5953998024117</v>
       </c>
       <c r="F98">
-        <v>64.22529614332223</v>
+        <v>808.7549579707122</v>
       </c>
       <c r="G98">
-        <v>5.644430008567044</v>
+        <v>2340.405437531038</v>
       </c>
       <c r="H98">
-        <v>-0.3330903701943286</v>
+        <v>1405.062870407624</v>
       </c>
       <c r="I98">
-        <v>14.44262290404692</v>
+        <v>3296.362411366938</v>
       </c>
       <c r="J98">
-        <v>2396492.971731894</v>
+        <v>11012157.60119895</v>
       </c>
       <c r="K98">
-        <v>-190035.4300284231</v>
+        <v>8244296.937272817</v>
       </c>
       <c r="L98">
-        <v>4829806.495273972</v>
+        <v>13618624.73726882</v>
       </c>
       <c r="M98">
-        <v>750709.1911394168</v>
+        <v>311273923.191628</v>
       </c>
       <c r="N98">
-        <v>-44301.01923584571</v>
+        <v>186873361.764214</v>
       </c>
       <c r="O98">
-        <v>1920868.846238241</v>
+        <v>438416200.7118027</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>diab2</t>
+          <t>dem</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -5589,46 +5589,46 @@
         </is>
       </c>
       <c r="D99">
-        <v>106.5403932087828</v>
+        <v>482.1464873066591</v>
       </c>
       <c r="E99">
-        <v>-8.448365873652651</v>
+        <v>399.1733210350187</v>
       </c>
       <c r="F99">
-        <v>214.7177100865659</v>
+        <v>561.9677175748649</v>
       </c>
       <c r="G99">
-        <v>23.23852684744799</v>
+        <v>1763.025372097715</v>
       </c>
       <c r="H99">
-        <v>-1.371357160712197</v>
+        <v>1170.481393402903</v>
       </c>
       <c r="I99">
-        <v>59.461323746393</v>
+        <v>2340.312990941033</v>
       </c>
       <c r="J99">
-        <v>8011944.109693679</v>
+        <v>8118864.699756844</v>
       </c>
       <c r="K99">
-        <v>-635325.5620645536</v>
+        <v>6721679.552908679</v>
       </c>
       <c r="L99">
-        <v>16146986.51621985</v>
+        <v>9462974.396243144</v>
       </c>
       <c r="M99">
-        <v>3090724.070710583</v>
+        <v>234482374.4889961</v>
       </c>
       <c r="N99">
-        <v>-182390.5023747222</v>
+        <v>155674025.3225861</v>
       </c>
       <c r="O99">
-        <v>7908356.058270269</v>
+        <v>311261627.7951574</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>diab2</t>
+          <t>dem</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -5642,46 +5642,46 @@
         </is>
       </c>
       <c r="D100">
-        <v>188.4854380505257</v>
+        <v>679.8810634140494</v>
       </c>
       <c r="E100">
-        <v>-14.94638694815023</v>
+        <v>478.8040187043862</v>
       </c>
       <c r="F100">
-        <v>379.8668319494795</v>
+        <v>867.8130378550079</v>
       </c>
       <c r="G100">
-        <v>40.26166477347436</v>
+        <v>2482.023960361387</v>
       </c>
       <c r="H100">
-        <v>-2.375930395749761</v>
+        <v>1401.697385301856</v>
       </c>
       <c r="I100">
-        <v>103.0190897805217</v>
+        <v>3608.13031998833</v>
       </c>
       <c r="J100">
-        <v>14174293.42683759</v>
+        <v>11448517.22682916</v>
       </c>
       <c r="K100">
-        <v>-1123983.244887845</v>
+        <v>8062580.870963153</v>
       </c>
       <c r="L100">
-        <v>28566365.62943282</v>
+        <v>14613103.74444046</v>
       </c>
       <c r="M100">
-        <v>5354801.414872089</v>
+        <v>330109186.7280644</v>
       </c>
       <c r="N100">
-        <v>-315998.7426347182</v>
+        <v>186425752.2451469</v>
       </c>
       <c r="O100">
-        <v>13701538.94080938</v>
+        <v>479881332.5584479</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>diab2</t>
+          <t>dem</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -5695,46 +5695,46 @@
         </is>
       </c>
       <c r="D101">
-        <v>1.411313555989257</v>
+        <v>1073.128536701045</v>
       </c>
       <c r="E101">
-        <v>-0.1119133590963652</v>
+        <v>909.4536814638525</v>
       </c>
       <c r="F101">
-        <v>2.844311024479699</v>
+        <v>1231.91613309592</v>
       </c>
       <c r="G101">
-        <v>0.1580763132462938</v>
+        <v>1893.696670209171</v>
       </c>
       <c r="H101">
-        <v>-0.009328434867336916</v>
+        <v>1286.95306560905</v>
       </c>
       <c r="I101">
-        <v>0.4044760195118123</v>
+        <v>2475.841477910278</v>
       </c>
       <c r="J101">
-        <v>106132.1907239482</v>
+        <v>18070411.42950892</v>
       </c>
       <c r="K101">
-        <v>-8415.99651740576</v>
+        <v>15314290.54216983</v>
       </c>
       <c r="L101">
-        <v>213895.0333518979</v>
+        <v>20744235.76520216</v>
       </c>
       <c r="M101">
-        <v>21024.14966175708</v>
+        <v>251861657.1378197</v>
       </c>
       <c r="N101">
-        <v>-1240.68183735581</v>
+        <v>171164757.7260037</v>
       </c>
       <c r="O101">
-        <v>53795.31059507104</v>
+        <v>329286916.5620669</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>diab2</t>
+          <t>dem</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -5748,46 +5748,46 @@
         </is>
       </c>
       <c r="D102">
-        <v>30.02669399765054</v>
+        <v>935.5499353460502</v>
       </c>
       <c r="E102">
-        <v>-2.381035860936245</v>
+        <v>820.8869766200262</v>
       </c>
       <c r="F102">
-        <v>60.51472856882663</v>
+        <v>1048.782450885886</v>
       </c>
       <c r="G102">
-        <v>3.425785543545082</v>
+        <v>1666.686988397232</v>
       </c>
       <c r="H102">
-        <v>-0.2021632251925974</v>
+        <v>1172.718804747808</v>
       </c>
       <c r="I102">
-        <v>8.765690898896947</v>
+        <v>2127.921014786807</v>
       </c>
       <c r="J102">
-        <v>2258037.415317317</v>
+        <v>15753725.36129215</v>
       </c>
       <c r="K102">
-        <v>-179056.2777782665</v>
+        <v>13822915.79930463</v>
       </c>
       <c r="L102">
-        <v>4550768.103104334</v>
+        <v>17660447.69046745</v>
       </c>
       <c r="M102">
-        <v>455629.4772914959</v>
+        <v>221669369.4568319</v>
       </c>
       <c r="N102">
-        <v>-26887.70895061546</v>
+        <v>155971601.0314584</v>
       </c>
       <c r="O102">
-        <v>1165836.889553294</v>
+        <v>283013494.9666454</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>diab2</t>
+          <t>dem</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -5801,46 +5801,46 @@
         </is>
       </c>
       <c r="D103">
-        <v>18.2159948839801</v>
+        <v>1350.195737800902</v>
       </c>
       <c r="E103">
-        <v>-1.444479271170608</v>
+        <v>1049.186138805141</v>
       </c>
       <c r="F103">
-        <v>36.71186665110206</v>
+        <v>1635.374462628896</v>
       </c>
       <c r="G103">
-        <v>2.213122346954912</v>
+        <v>2483.666506521427</v>
       </c>
       <c r="H103">
-        <v>-0.1306012725312733</v>
+        <v>1547.649258591167</v>
       </c>
       <c r="I103">
-        <v>5.662802346574511</v>
+        <v>3426.074319695068</v>
       </c>
       <c r="J103">
-        <v>1369861.031270188</v>
+        <v>22735946.0288294</v>
       </c>
       <c r="K103">
-        <v>-108626.2856713007</v>
+        <v>17667245.39133975</v>
       </c>
       <c r="L103">
-        <v>2760769.084029526</v>
+        <v>27538070.57620797</v>
       </c>
       <c r="M103">
-        <v>294345.2721450033</v>
+        <v>330327645.3673499</v>
       </c>
       <c r="N103">
-        <v>-17369.96924665935</v>
+        <v>205837351.3926252</v>
       </c>
       <c r="O103">
-        <v>753152.7120944099</v>
+        <v>455667884.5194441</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>diab2</t>
+          <t>dem</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -5854,46 +5854,46 @@
         </is>
       </c>
       <c r="D104">
-        <v>0.1406431463369601</v>
+        <v>1222.063244749208</v>
       </c>
       <c r="E104">
-        <v>-0.0111526222317186</v>
+        <v>1057.91985798275</v>
       </c>
       <c r="F104">
-        <v>0.2834471829070787</v>
+        <v>1382.889267372711</v>
       </c>
       <c r="G104">
-        <v>0.00139430618284655</v>
+        <v>329.5158705084067</v>
       </c>
       <c r="H104">
-        <v>-8.228110932435989E-05</v>
+        <v>228.7488266565694</v>
       </c>
       <c r="I104">
-        <v>0.003567665535947739</v>
+        <v>424.6714647733252</v>
       </c>
       <c r="J104">
-        <v>10576.50524768573</v>
+        <v>20578322.97833193</v>
       </c>
       <c r="K104">
-        <v>-838.6883444474699</v>
+        <v>17814312.48857155</v>
       </c>
       <c r="L104">
-        <v>21315.51160179522</v>
+        <v>23286472.37328907</v>
       </c>
       <c r="M104">
-        <v>185.4427223185912</v>
+        <v>43825610.77761809</v>
       </c>
       <c r="N104">
-        <v>-10.94338754013986</v>
+        <v>30423593.94532374</v>
       </c>
       <c r="O104">
-        <v>474.4995162810492</v>
+        <v>56481304.81485225</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>diab2</t>
+          <t>dem</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -5907,46 +5907,46 @@
         </is>
       </c>
       <c r="D105">
-        <v>3.614396239296559</v>
+        <v>981.1317786361486</v>
       </c>
       <c r="E105">
-        <v>-0.2866118748228435</v>
+        <v>927.8342946252344</v>
       </c>
       <c r="F105">
-        <v>7.284325319941455</v>
+        <v>1039.654283722999</v>
       </c>
       <c r="G105">
-        <v>0.0801303052775468</v>
+        <v>257.6487104796974</v>
       </c>
       <c r="H105">
-        <v>-0.004728667555124655</v>
+        <v>195.3864773983815</v>
       </c>
       <c r="I105">
-        <v>0.2050325330552858</v>
+        <v>310.9371387289203</v>
       </c>
       <c r="J105">
-        <v>271806.2115913403</v>
+        <v>16521278.0204541</v>
       </c>
       <c r="K105">
-        <v>-21553.49959855265</v>
+        <v>15623801.68719432</v>
       </c>
       <c r="L105">
-        <v>547788.5483849173</v>
+        <v>17506738.48361158</v>
       </c>
       <c r="M105">
-        <v>10657.33060191373</v>
+        <v>34267278.49379975</v>
       </c>
       <c r="N105">
-        <v>-628.9127848315792</v>
+        <v>25986401.49398474</v>
       </c>
       <c r="O105">
-        <v>27269.32689635302</v>
+        <v>41354639.45094641</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>diab2</t>
+          <t>dem</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -5960,46 +5960,46 @@
         </is>
       </c>
       <c r="D106">
-        <v>0.7602355454450265</v>
+        <v>1324.494077059028</v>
       </c>
       <c r="E106">
-        <v>-0.06028462862427381</v>
+        <v>1119.53690502002</v>
       </c>
       <c r="F106">
-        <v>1.532151614312904</v>
+        <v>1523.121317426594</v>
       </c>
       <c r="G106">
-        <v>0.01497252756601041</v>
+        <v>366.4214814021191</v>
       </c>
       <c r="H106">
-        <v>-0.000883562156344872</v>
+        <v>248.3663596461094</v>
       </c>
       <c r="I106">
-        <v>0.03831078943810551</v>
+        <v>479.8974277265941</v>
       </c>
       <c r="J106">
-        <v>57170.47325301147</v>
+        <v>22303155.76359696</v>
       </c>
       <c r="K106">
-        <v>-4533.464357174014</v>
+        <v>18851881.94363211</v>
       </c>
       <c r="L106">
-        <v>115219.3335479446</v>
+        <v>25647839.86414644</v>
       </c>
       <c r="M106">
-        <v>1991.346166279384</v>
+        <v>48734057.02648184</v>
       </c>
       <c r="N106">
-        <v>-117.513766793868</v>
+        <v>33032725.83293255</v>
       </c>
       <c r="O106">
-        <v>5095.334995268033</v>
+        <v>63826357.88763702</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>dem</t>
+          <t>dep</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -6013,22 +6013,22 @@
         </is>
       </c>
       <c r="D107">
-        <v>0</v>
+        <v>5646.474344533598</v>
       </c>
       <c r="E107">
-        <v>0</v>
+        <v>4010.85457503764</v>
       </c>
       <c r="F107">
-        <v>0</v>
+        <v>6972.852977765641</v>
       </c>
       <c r="G107">
-        <v>0</v>
+        <v>28503.11545069014</v>
       </c>
       <c r="H107">
-        <v>0</v>
+        <v>12524.50171933484</v>
       </c>
       <c r="I107">
-        <v>0</v>
+        <v>53785.90221072586</v>
       </c>
       <c r="J107">
         <v>0</v>
@@ -6040,19 +6040,19 @@
         <v>0</v>
       </c>
       <c r="M107">
-        <v>0</v>
+        <v>3790914354.941788</v>
       </c>
       <c r="N107">
-        <v>0</v>
+        <v>1665758728.671534</v>
       </c>
       <c r="O107">
-        <v>0</v>
+        <v>7153524994.02654</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>dem</t>
+          <t>dep</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -6066,22 +6066,22 @@
         </is>
       </c>
       <c r="D108">
-        <v>0</v>
+        <v>3359.212760402233</v>
       </c>
       <c r="E108">
-        <v>0</v>
+        <v>2386.146300589806</v>
       </c>
       <c r="F108">
-        <v>0</v>
+        <v>4148.304812895383</v>
       </c>
       <c r="G108">
-        <v>0</v>
+        <v>16932.50715958917</v>
       </c>
       <c r="H108">
-        <v>0</v>
+        <v>7440.281936892262</v>
       </c>
       <c r="I108">
-        <v>0</v>
+        <v>31951.95191359431</v>
       </c>
       <c r="J108">
         <v>0</v>
@@ -6093,19 +6093,19 @@
         <v>0</v>
       </c>
       <c r="M108">
-        <v>0</v>
+        <v>2252023452.22536</v>
       </c>
       <c r="N108">
-        <v>0</v>
+        <v>989557497.6066709</v>
       </c>
       <c r="O108">
-        <v>0</v>
+        <v>4249609604.508043</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>dem</t>
+          <t>dep</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -6119,22 +6119,22 @@
         </is>
       </c>
       <c r="D109">
-        <v>0</v>
+        <v>8905.877206228399</v>
       </c>
       <c r="E109">
-        <v>0</v>
+        <v>6326.103008314508</v>
       </c>
       <c r="F109">
-        <v>0</v>
+        <v>10997.90216122807</v>
       </c>
       <c r="G109">
-        <v>0</v>
+        <v>44857.22473711741</v>
       </c>
       <c r="H109">
-        <v>0</v>
+        <v>19710.63090687565</v>
       </c>
       <c r="I109">
-        <v>0</v>
+        <v>84646.40671750616</v>
       </c>
       <c r="J109">
         <v>0</v>
@@ -6146,19 +6146,19 @@
         <v>0</v>
       </c>
       <c r="M109">
-        <v>0</v>
+        <v>5966010890.036615</v>
       </c>
       <c r="N109">
-        <v>0</v>
+        <v>2621513910.614461</v>
       </c>
       <c r="O109">
-        <v>0</v>
+        <v>11257972093.42832</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>dem</t>
+          <t>dep</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -6172,22 +6172,22 @@
         </is>
       </c>
       <c r="D110">
-        <v>0</v>
+        <v>6364.080663668506</v>
       </c>
       <c r="E110">
-        <v>0</v>
+        <v>4520.591166857031</v>
       </c>
       <c r="F110">
-        <v>0</v>
+        <v>7859.027793044395</v>
       </c>
       <c r="G110">
-        <v>0</v>
+        <v>26162.80152357957</v>
       </c>
       <c r="H110">
-        <v>0</v>
+        <v>11496.14866597874</v>
       </c>
       <c r="I110">
-        <v>0</v>
+        <v>49369.68685897848</v>
       </c>
       <c r="J110">
         <v>0</v>
@@ -6199,19 +6199,19 @@
         <v>0</v>
       </c>
       <c r="M110">
-        <v>0</v>
+        <v>3479652602.636083</v>
       </c>
       <c r="N110">
-        <v>0</v>
+        <v>1528987772.575173</v>
       </c>
       <c r="O110">
-        <v>0</v>
+        <v>6566168352.244138</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>dem</t>
+          <t>dep</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -6225,22 +6225,22 @@
         </is>
       </c>
       <c r="D111">
-        <v>0</v>
+        <v>6370.941034319718</v>
       </c>
       <c r="E111">
-        <v>0</v>
+        <v>4525.464287203258</v>
       </c>
       <c r="F111">
-        <v>0</v>
+        <v>7867.499691259993</v>
       </c>
       <c r="G111">
-        <v>0</v>
+        <v>26299.71849753301</v>
       </c>
       <c r="H111">
-        <v>0</v>
+        <v>11556.31110256052</v>
       </c>
       <c r="I111">
-        <v>0</v>
+        <v>49628.05170280701</v>
       </c>
       <c r="J111">
         <v>0</v>
@@ -6252,19 +6252,19 @@
         <v>0</v>
       </c>
       <c r="M111">
-        <v>0</v>
+        <v>3497862560.17189</v>
       </c>
       <c r="N111">
-        <v>0</v>
+        <v>1536989376.640549</v>
       </c>
       <c r="O111">
-        <v>0</v>
+        <v>6600530876.473332</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>dem</t>
+          <t>dep</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -6278,22 +6278,22 @@
         </is>
       </c>
       <c r="D112">
-        <v>0</v>
+        <v>15104.03933926087</v>
       </c>
       <c r="E112">
-        <v>0</v>
+        <v>10909.10973564213</v>
       </c>
       <c r="F112">
-        <v>0</v>
+        <v>18597.59953447181</v>
       </c>
       <c r="G112">
-        <v>0</v>
+        <v>62734.26554557034</v>
       </c>
       <c r="H112">
-        <v>0</v>
+        <v>28029.12810701377</v>
       </c>
       <c r="I112">
-        <v>0</v>
+        <v>118035.2104105808</v>
       </c>
       <c r="J112">
         <v>0</v>
@@ -6305,19 +6305,19 @@
         <v>0</v>
       </c>
       <c r="M112">
-        <v>0</v>
+        <v>8343657317.560856</v>
       </c>
       <c r="N112">
-        <v>0</v>
+        <v>3727874038.232832</v>
       </c>
       <c r="O112">
-        <v>0</v>
+        <v>15698682984.60725</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>dem</t>
+          <t>dep</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -6331,46 +6331,46 @@
         </is>
       </c>
       <c r="D113">
-        <v>4.837846688359742</v>
+        <v>9631.002719211361</v>
       </c>
       <c r="E113">
-        <v>4.187015358957903</v>
+        <v>6841.18070171443</v>
       </c>
       <c r="F113">
-        <v>5.475311514618383</v>
+        <v>11893.36245803295</v>
       </c>
       <c r="G113">
-        <v>5.836379991578271</v>
+        <v>32278.32955656146</v>
       </c>
       <c r="H113">
-        <v>4.066053689849757</v>
+        <v>14183.36163033796</v>
       </c>
       <c r="I113">
-        <v>7.503125684015216</v>
+        <v>60909.80054647896</v>
       </c>
       <c r="J113">
-        <v>81464.50038528968</v>
+        <v>0</v>
       </c>
       <c r="K113">
-        <v>70505.15162949213</v>
+        <v>0</v>
       </c>
       <c r="L113">
-        <v>92198.77059465894</v>
+        <v>0</v>
       </c>
       <c r="M113">
-        <v>776238.53887991</v>
+        <v>4293017831.022674</v>
       </c>
       <c r="N113">
-        <v>540785.1407500177</v>
+        <v>1886387096.834948</v>
       </c>
       <c r="O113">
-        <v>997915.7159740237</v>
+        <v>8101003472.681702</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>dem</t>
+          <t>dep</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -6384,46 +6384,46 @@
         </is>
       </c>
       <c r="D114">
-        <v>4.388514742685438</v>
+        <v>6864.769883456749</v>
       </c>
       <c r="E114">
-        <v>3.638343594688184</v>
+        <v>4876.245248559148</v>
       </c>
       <c r="F114">
-        <v>5.110371799300389</v>
+        <v>8477.330844490209</v>
       </c>
       <c r="G114">
-        <v>5.655592823094606</v>
+        <v>22889.22099023566</v>
       </c>
       <c r="H114">
-        <v>3.759730717631365</v>
+        <v>10057.71064367989</v>
       </c>
       <c r="I114">
-        <v>7.500948438596639</v>
+        <v>43192.38028524711</v>
       </c>
       <c r="J114">
-        <v>73898.19975208007</v>
+        <v>0</v>
       </c>
       <c r="K114">
-        <v>61266.06779095435</v>
+        <v>0</v>
       </c>
       <c r="L114">
-        <v>86053.55072841926</v>
+        <v>0</v>
       </c>
       <c r="M114">
-        <v>752193.8454715826</v>
+        <v>3044266391.701343</v>
       </c>
       <c r="N114">
-        <v>500044.1854449715</v>
+        <v>1337675515.609425</v>
       </c>
       <c r="O114">
-        <v>997626.1423333531</v>
+        <v>5744586577.937865</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>dem</t>
+          <t>dep</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -6437,46 +6437,46 @@
         </is>
       </c>
       <c r="D115">
-        <v>37.42807238086389</v>
+        <v>14803.76568130983</v>
       </c>
       <c r="E115">
-        <v>28.13304330516083</v>
+        <v>10596.16312199098</v>
       </c>
       <c r="F115">
-        <v>46.18073489850033</v>
+        <v>18256.88289490419</v>
       </c>
       <c r="G115">
-        <v>50.20673766373768</v>
+        <v>49363.17229453719</v>
       </c>
       <c r="H115">
-        <v>30.27622420261154</v>
+        <v>21856.87472106608</v>
       </c>
       <c r="I115">
-        <v>70.53443258547868</v>
+        <v>93025.16867090882</v>
       </c>
       <c r="J115">
-        <v>630251.3108213663</v>
+        <v>0</v>
       </c>
       <c r="K115">
-        <v>473732.3162156024</v>
+        <v>0</v>
       </c>
       <c r="L115">
-        <v>777637.3949558482</v>
+        <v>0</v>
       </c>
       <c r="M115">
-        <v>6677496.109277112</v>
+        <v>6565301915.173446</v>
       </c>
       <c r="N115">
-        <v>4026737.818947334</v>
+        <v>2906964337.901789</v>
       </c>
       <c r="O115">
-        <v>9381079.533868665</v>
+        <v>12372347433.23087</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>dem</t>
+          <t>dep</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -6490,46 +6490,46 @@
         </is>
       </c>
       <c r="D116">
-        <v>11.95842713596549</v>
+        <v>8010.434213225634</v>
       </c>
       <c r="E116">
-        <v>10.13740742900164</v>
+        <v>5690.043866622397</v>
       </c>
       <c r="F116">
-        <v>13.72481614132636</v>
+        <v>9892.116150489635</v>
       </c>
       <c r="G116">
-        <v>12.10075517398357</v>
+        <v>19809.34553162937</v>
       </c>
       <c r="H116">
-        <v>8.205234475181014</v>
+        <v>8704.388213246468</v>
       </c>
       <c r="I116">
-        <v>15.84365274494939</v>
+        <v>37380.59874422952</v>
       </c>
       <c r="J116">
-        <v>201367.9545425228</v>
+        <v>0</v>
       </c>
       <c r="K116">
-        <v>170703.8036969586</v>
+        <v>0</v>
       </c>
       <c r="L116">
-        <v>231112.1790037945</v>
+        <v>0</v>
       </c>
       <c r="M116">
-        <v>1609400.438139815</v>
+        <v>2634642955.706706</v>
       </c>
       <c r="N116">
-        <v>1091296.185199075</v>
+        <v>1157683632.36178</v>
       </c>
       <c r="O116">
-        <v>2107205.815078269</v>
+        <v>4971619632.982527</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>dem</t>
+          <t>dep</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -6543,46 +6543,46 @@
         </is>
       </c>
       <c r="D117">
-        <v>22.51151063013679</v>
+        <v>4809.182103887862</v>
       </c>
       <c r="E117">
-        <v>18.56065782724281</v>
+        <v>3416.101600150112</v>
       </c>
       <c r="F117">
-        <v>26.30694731448451</v>
+        <v>5938.877555722187</v>
       </c>
       <c r="G117">
-        <v>22.13448028364467</v>
+        <v>11861.5517274533</v>
       </c>
       <c r="H117">
-        <v>14.6224957873275</v>
+        <v>5212.06270456557</v>
       </c>
       <c r="I117">
-        <v>29.47449234009693</v>
+        <v>22382.96590363859</v>
       </c>
       <c r="J117">
-        <v>379071.327500873</v>
+        <v>0</v>
       </c>
       <c r="K117">
-        <v>312542.9171529418</v>
+        <v>0</v>
       </c>
       <c r="L117">
-        <v>442982.6858286053</v>
+        <v>0</v>
       </c>
       <c r="M117">
-        <v>2943885.877724741</v>
+        <v>1577586379.751289</v>
       </c>
       <c r="N117">
-        <v>1944791.939714557</v>
+        <v>693204339.7072208</v>
       </c>
       <c r="O117">
-        <v>3920107.481232892</v>
+        <v>2976934465.183933</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>dem</t>
+          <t>dep</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -6596,46 +6596,46 @@
         </is>
       </c>
       <c r="D118">
-        <v>49.73252106882055</v>
+        <v>11295.0041930892</v>
       </c>
       <c r="E118">
-        <v>39.32533946929043</v>
+        <v>8031.545508316425</v>
       </c>
       <c r="F118">
-        <v>59.62153168801525</v>
+        <v>13945.71491461562</v>
       </c>
       <c r="G118">
-        <v>48.51726604756686</v>
+        <v>27853.25872659043</v>
       </c>
       <c r="H118">
-        <v>30.77180563796683</v>
+        <v>12251.72696068801</v>
       </c>
       <c r="I118">
-        <v>66.23418898495093</v>
+        <v>52550.07941946424</v>
       </c>
       <c r="J118">
-        <v>837445.9222778701</v>
+        <v>0</v>
       </c>
       <c r="K118">
-        <v>662199.3913233803</v>
+        <v>0</v>
       </c>
       <c r="L118">
-        <v>1003966.972094489</v>
+        <v>0</v>
       </c>
       <c r="M118">
-        <v>6452796.384326392</v>
+        <v>3704483410.636528</v>
       </c>
       <c r="N118">
-        <v>4092650.149849589</v>
+        <v>1629479685.771506</v>
       </c>
       <c r="O118">
-        <v>8809147.134998474</v>
+        <v>6989160562.788745</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>dem</t>
+          <t>dep</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -6649,46 +6649,46 @@
         </is>
       </c>
       <c r="D119">
-        <v>48.17171995440645</v>
+        <v>7663.070146594271</v>
       </c>
       <c r="E119">
-        <v>40.99578296567429</v>
+        <v>5443.301090362211</v>
       </c>
       <c r="F119">
-        <v>55.14451022851332</v>
+        <v>9463.154922900922</v>
       </c>
       <c r="G119">
-        <v>23.94762241936628</v>
+        <v>12595.47227241151</v>
       </c>
       <c r="H119">
-        <v>16.44442803494296</v>
+        <v>5534.553386087244</v>
       </c>
       <c r="I119">
-        <v>31.09217937535782</v>
+        <v>23767.88744773622</v>
       </c>
       <c r="J119">
-        <v>811163.5923122499</v>
+        <v>0</v>
       </c>
       <c r="K119">
-        <v>690327.9893589902</v>
+        <v>0</v>
       </c>
       <c r="L119">
-        <v>928578.4077379359</v>
+        <v>0</v>
       </c>
       <c r="M119">
-        <v>3185033.781775715</v>
+        <v>1675197812.230731</v>
       </c>
       <c r="N119">
-        <v>2187108.928647413</v>
+        <v>736095600.3496034</v>
       </c>
       <c r="O119">
-        <v>4135259.856922591</v>
+        <v>3161129030.548918</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>dem</t>
+          <t>dep</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -6702,46 +6702,46 @@
         </is>
       </c>
       <c r="D120">
-        <v>120.21907116839</v>
+        <v>5730.884853566849</v>
       </c>
       <c r="E120">
-        <v>100.8730296019931</v>
+        <v>4070.813809009029</v>
       </c>
       <c r="F120">
-        <v>138.9140053551935</v>
+        <v>7077.091841409316</v>
       </c>
       <c r="G120">
-        <v>74.98882619924819</v>
+        <v>9592.396575617324</v>
       </c>
       <c r="H120">
-        <v>50.49377850641017</v>
+        <v>4214.977398232179</v>
       </c>
       <c r="I120">
-        <v>98.63832231359039</v>
+        <v>18101.02846740442</v>
       </c>
       <c r="J120">
-        <v>2024368.939404521</v>
+        <v>0</v>
       </c>
       <c r="K120">
-        <v>1698600.945467964</v>
+        <v>0</v>
       </c>
       <c r="L120">
-        <v>2339172.936176104</v>
+        <v>0</v>
       </c>
       <c r="M120">
-        <v>9973513.88450001</v>
+        <v>1275788744.557104</v>
       </c>
       <c r="N120">
-        <v>6715672.541352552</v>
+        <v>560591993.9648799</v>
       </c>
       <c r="O120">
-        <v>13118896.86770752</v>
+        <v>2407436786.164788</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>dem</t>
+          <t>dep</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -6755,46 +6755,46 @@
         </is>
       </c>
       <c r="D121">
-        <v>213.6340701904733</v>
+        <v>8607.659084033854</v>
       </c>
       <c r="E121">
-        <v>170.7575334477544</v>
+        <v>6114.270022493695</v>
       </c>
       <c r="F121">
-        <v>254.4770083552099</v>
+        <v>10629.63145025229</v>
       </c>
       <c r="G121">
-        <v>129.8280205824493</v>
+        <v>14298.32846879784</v>
       </c>
       <c r="H121">
-        <v>82.89604822447539</v>
+        <v>6282.80230632604</v>
       </c>
       <c r="I121">
-        <v>176.5352073248865</v>
+        <v>26981.2083570317</v>
       </c>
       <c r="J121">
-        <v>3597384.107937383</v>
+        <v>0</v>
       </c>
       <c r="K121">
-        <v>2875386.105726742</v>
+        <v>0</v>
       </c>
       <c r="L121">
-        <v>4285138.343693377</v>
+        <v>0</v>
       </c>
       <c r="M121">
-        <v>17267126.73746576</v>
+        <v>1901677686.350113</v>
       </c>
       <c r="N121">
-        <v>11025174.41385523</v>
+        <v>835612706.7413633</v>
       </c>
       <c r="O121">
-        <v>23479182.5742099</v>
+        <v>3588500711.485216</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>dem</t>
+          <t>dep</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -6808,46 +6808,46 @@
         </is>
       </c>
       <c r="D122">
-        <v>32.06311381754342</v>
+        <v>3035.142459374827</v>
       </c>
       <c r="E122">
-        <v>30.54037933859831</v>
+        <v>2155.949761971351</v>
       </c>
       <c r="F122">
-        <v>33.7782082857282</v>
+        <v>3748.109146423978</v>
       </c>
       <c r="G122">
-        <v>10.48623004444169</v>
+        <v>2598.867380480646</v>
       </c>
       <c r="H122">
-        <v>8.017438869431315</v>
+        <v>1141.963552421604</v>
       </c>
       <c r="I122">
-        <v>12.57152208819143</v>
+        <v>4904.110465643605</v>
       </c>
       <c r="J122">
-        <v>539910.7735736136</v>
+        <v>0</v>
       </c>
       <c r="K122">
-        <v>514269.447682657</v>
+        <v>0</v>
       </c>
       <c r="L122">
-        <v>568791.2493233773</v>
+        <v>0</v>
       </c>
       <c r="M122">
-        <v>1394668.595910744</v>
+        <v>345649361.6039259</v>
       </c>
       <c r="N122">
-        <v>1066319.369634365</v>
+        <v>151881152.4720733</v>
       </c>
       <c r="O122">
-        <v>1672012.43772946</v>
+        <v>652246691.9305995</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>dem</t>
+          <t>dep</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -6861,46 +6861,46 @@
         </is>
       </c>
       <c r="D123">
-        <v>386.2556026722297</v>
+        <v>2561.140775695088</v>
       </c>
       <c r="E123">
-        <v>345.3599478193721</v>
+        <v>1819.252611579982</v>
       </c>
       <c r="F123">
-        <v>427.2088987631682</v>
+        <v>3162.762636400084</v>
       </c>
       <c r="G123">
-        <v>116.0811294408525</v>
+        <v>2161.176337499466</v>
       </c>
       <c r="H123">
-        <v>83.18811770286038</v>
+        <v>949.6385334306519</v>
       </c>
       <c r="I123">
-        <v>146.2752331129985</v>
+        <v>4078.179430945911</v>
       </c>
       <c r="J123">
-        <v>6504158.093397677</v>
+        <v>0</v>
       </c>
       <c r="K123">
-        <v>5815516.161330404</v>
+        <v>0</v>
       </c>
       <c r="L123">
-        <v>7193770.646272988</v>
+        <v>0</v>
       </c>
       <c r="M123">
-        <v>15438790.21563338</v>
+        <v>287436452.8874289</v>
       </c>
       <c r="N123">
-        <v>11064019.65448043</v>
+        <v>126301924.9462767</v>
       </c>
       <c r="O123">
-        <v>19454606.0040288</v>
+        <v>542397864.3158063</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>dem</t>
+          <t>dep</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -6914,46 +6914,46 @@
         </is>
       </c>
       <c r="D124">
-        <v>206.1424763099495</v>
+        <v>3981.096065912365</v>
       </c>
       <c r="E124">
-        <v>184.4141709380568</v>
+        <v>2827.88805816276</v>
       </c>
       <c r="F124">
-        <v>227.9084347743518</v>
+        <v>4916.270908915475</v>
       </c>
       <c r="G124">
-        <v>65.00376949675106</v>
+        <v>3473.541204035408</v>
       </c>
       <c r="H124">
-        <v>46.65609982595232</v>
+        <v>1526.302374117094</v>
       </c>
       <c r="I124">
-        <v>81.81919672954757</v>
+        <v>6554.636030871216</v>
       </c>
       <c r="J124">
-        <v>3471233.158583241</v>
+        <v>0</v>
       </c>
       <c r="K124">
-        <v>3105350.224425938</v>
+        <v>0</v>
       </c>
       <c r="L124">
-        <v>3837750.13316531</v>
+        <v>0</v>
       </c>
       <c r="M124">
-        <v>8645501.343067892</v>
+        <v>461980980.1367093</v>
       </c>
       <c r="N124">
-        <v>6205261.276851658</v>
+        <v>202998215.7575735</v>
       </c>
       <c r="O124">
-        <v>10881953.16502983</v>
+        <v>871766592.1058718</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>dem</t>
+          <t>dep</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -6967,46 +6967,46 @@
         </is>
       </c>
       <c r="D125">
-        <v>50.79453964486814</v>
+        <v>1243.917789006613</v>
       </c>
       <c r="E125">
-        <v>48.10628858286766</v>
+        <v>883.5909012564545</v>
       </c>
       <c r="F125">
-        <v>53.76009135750757</v>
+        <v>1536.118882319452</v>
       </c>
       <c r="G125">
-        <v>0.9596613887129849</v>
+        <v>189.9463980517847</v>
       </c>
       <c r="H125">
-        <v>0.7358843907340861</v>
+        <v>83.46399863189156</v>
       </c>
       <c r="I125">
-        <v>1.147752152502642</v>
+        <v>358.4323407933128</v>
       </c>
       <c r="J125">
-        <v>855329.2530799342</v>
+        <v>0</v>
       </c>
       <c r="K125">
-        <v>810061.7934469084</v>
+        <v>0</v>
       </c>
       <c r="L125">
-        <v>905266.1783690695</v>
+        <v>0</v>
       </c>
       <c r="M125">
-        <v>127634.964698827</v>
+        <v>25262870.94088736</v>
       </c>
       <c r="N125">
-        <v>97872.62396763345</v>
+        <v>11100711.81804158</v>
       </c>
       <c r="O125">
-        <v>152651.0362828514</v>
+        <v>47671501.3255106</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>dem</t>
+          <t>dep</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -7020,46 +7020,46 @@
         </is>
       </c>
       <c r="D126">
-        <v>1330.498080105364</v>
+        <v>967.9019229665148</v>
       </c>
       <c r="E126">
-        <v>1231.81870542208</v>
+        <v>687.5288222422002</v>
       </c>
       <c r="F126">
-        <v>1433.615594536312</v>
+        <v>1195.265823225775</v>
       </c>
       <c r="G126">
-        <v>53.26927291484402</v>
+        <v>144.776892092941</v>
       </c>
       <c r="H126">
-        <v>39.58979426475607</v>
+        <v>63.61614880572994</v>
       </c>
       <c r="I126">
-        <v>65.31749939078419</v>
+        <v>273.1966536765094</v>
       </c>
       <c r="J126">
-        <v>22404257.17089421</v>
+        <v>0</v>
       </c>
       <c r="K126">
-        <v>20742595.18060241</v>
+        <v>0</v>
       </c>
       <c r="L126">
-        <v>24140652.99639693</v>
+        <v>0</v>
       </c>
       <c r="M126">
-        <v>7084813.297674255</v>
+        <v>19255326.64836115</v>
       </c>
       <c r="N126">
-        <v>5265442.637212558</v>
+        <v>8460947.791162083</v>
       </c>
       <c r="O126">
-        <v>8687227.418974297</v>
+        <v>36335154.93897575</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>dem</t>
+          <t>dep</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -7073,1153 +7073,40 @@
         </is>
       </c>
       <c r="D127">
-        <v>256.520964495994</v>
+        <v>1403.586145772859</v>
       </c>
       <c r="E127">
-        <v>239.8059541272263</v>
+        <v>997.0079682877816</v>
       </c>
       <c r="F127">
-        <v>274.3212112045761</v>
+        <v>1733.293952814603</v>
       </c>
       <c r="G127">
-        <v>10.31231651764437</v>
+        <v>212.825249455226</v>
       </c>
       <c r="H127">
-        <v>7.849392037550997</v>
+        <v>93.51715279444343</v>
       </c>
       <c r="I127">
-        <v>12.40788429075045</v>
+        <v>401.6051534778794</v>
       </c>
       <c r="J127">
-        <v>4319556.521148044</v>
+        <v>0</v>
       </c>
       <c r="K127">
-        <v>4038092.461548369</v>
+        <v>0</v>
       </c>
       <c r="L127">
-        <v>4619294.875473856</v>
+        <v>0</v>
       </c>
       <c r="M127">
-        <v>1371538.096846702</v>
+        <v>28305758.17754506</v>
       </c>
       <c r="N127">
-        <v>1043969.140994283</v>
+        <v>12437781.32166098</v>
       </c>
       <c r="O127">
-        <v>1650248.61066981</v>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="inlineStr">
-        <is>
-          <t>dep</t>
-        </is>
-      </c>
-      <c r="B128" t="inlineStr">
-        <is>
-          <t>20-29</t>
-        </is>
-      </c>
-      <c r="C128" t="inlineStr">
-        <is>
-          <t>periurban</t>
-        </is>
-      </c>
-      <c r="D128">
-        <v>125.8660474719037</v>
-      </c>
-      <c r="E128">
-        <v>89.40630587179078</v>
-      </c>
-      <c r="F128">
-        <v>155.4324681849854</v>
-      </c>
-      <c r="G128">
-        <v>211.6730534018891</v>
-      </c>
-      <c r="H128">
-        <v>93.01086843840545</v>
-      </c>
-      <c r="I128">
-        <v>399.4309383693734</v>
-      </c>
-      <c r="J128">
-        <v>0</v>
-      </c>
-      <c r="K128">
-        <v>0</v>
-      </c>
-      <c r="L128">
-        <v>0</v>
-      </c>
-      <c r="M128">
-        <v>28152516.10245125</v>
-      </c>
-      <c r="N128">
-        <v>12370445.50230793</v>
-      </c>
-      <c r="O128">
-        <v>53124314.80312666</v>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="inlineStr">
-        <is>
-          <t>dep</t>
-        </is>
-      </c>
-      <c r="B129" t="inlineStr">
-        <is>
-          <t>20-29</t>
-        </is>
-      </c>
-      <c r="C129" t="inlineStr">
-        <is>
-          <t>rural</t>
-        </is>
-      </c>
-      <c r="D129">
-        <v>650.2622954716347</v>
-      </c>
-      <c r="E129">
-        <v>461.9001776377175</v>
-      </c>
-      <c r="F129">
-        <v>803.0114203383748</v>
-      </c>
-      <c r="G129">
-        <v>1101.933298140785</v>
-      </c>
-      <c r="H129">
-        <v>484.1984908994372</v>
-      </c>
-      <c r="I129">
-        <v>2079.368366558956</v>
-      </c>
-      <c r="J129">
-        <v>0</v>
-      </c>
-      <c r="K129">
-        <v>0</v>
-      </c>
-      <c r="L129">
-        <v>0</v>
-      </c>
-      <c r="M129">
-        <v>146557128.6527244</v>
-      </c>
-      <c r="N129">
-        <v>64398399.28962515</v>
-      </c>
-      <c r="O129">
-        <v>276555992.7523412</v>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="inlineStr">
-        <is>
-          <t>dep</t>
-        </is>
-      </c>
-      <c r="B130" t="inlineStr">
-        <is>
-          <t>20-29</t>
-        </is>
-      </c>
-      <c r="C130" t="inlineStr">
-        <is>
-          <t>urban</t>
-        </is>
-      </c>
-      <c r="D130">
-        <v>4844.431452014195</v>
-      </c>
-      <c r="E130">
-        <v>3441.14023498185</v>
-      </c>
-      <c r="F130">
-        <v>5982.407111875213</v>
-      </c>
-      <c r="G130">
-        <v>8121.350668859894</v>
-      </c>
-      <c r="H130">
-        <v>3568.587812494529</v>
-      </c>
-      <c r="I130">
-        <v>15325.1378309853</v>
-      </c>
-      <c r="J130">
-        <v>0</v>
-      </c>
-      <c r="K130">
-        <v>0</v>
-      </c>
-      <c r="L130">
-        <v>0</v>
-      </c>
-      <c r="M130">
-        <v>1080139638.958366</v>
-      </c>
-      <c r="N130">
-        <v>474622179.0617724</v>
-      </c>
-      <c r="O130">
-        <v>2038243331.521045</v>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="inlineStr">
-        <is>
-          <t>dep</t>
-        </is>
-      </c>
-      <c r="B131" t="inlineStr">
-        <is>
-          <t>30-39</t>
-        </is>
-      </c>
-      <c r="C131" t="inlineStr">
-        <is>
-          <t>periurban</t>
-        </is>
-      </c>
-      <c r="D131">
-        <v>537.9165658941712</v>
-      </c>
-      <c r="E131">
-        <v>382.0977458958744</v>
-      </c>
-      <c r="F131">
-        <v>664.2752449439242</v>
-      </c>
-      <c r="G131">
-        <v>775.0009891791619</v>
-      </c>
-      <c r="H131">
-        <v>340.541764224079</v>
-      </c>
-      <c r="I131">
-        <v>1462.441096634471</v>
-      </c>
-      <c r="J131">
-        <v>0</v>
-      </c>
-      <c r="K131">
-        <v>0</v>
-      </c>
-      <c r="L131">
-        <v>0</v>
-      </c>
-      <c r="M131">
-        <v>103075131.5608285</v>
-      </c>
-      <c r="N131">
-        <v>45292054.64180251</v>
-      </c>
-      <c r="O131">
-        <v>194504665.8523846</v>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="inlineStr">
-        <is>
-          <t>dep</t>
-        </is>
-      </c>
-      <c r="B132" t="inlineStr">
-        <is>
-          <t>30-39</t>
-        </is>
-      </c>
-      <c r="C132" t="inlineStr">
-        <is>
-          <t>rural</t>
-        </is>
-      </c>
-      <c r="D132">
-        <v>607.3256430357609</v>
-      </c>
-      <c r="E132">
-        <v>431.4010274864482</v>
-      </c>
-      <c r="F132">
-        <v>749.9887824010195</v>
-      </c>
-      <c r="G132">
-        <v>871.6982119732033</v>
-      </c>
-      <c r="H132">
-        <v>383.0313136641757</v>
-      </c>
-      <c r="I132">
-        <v>1644.910531537005</v>
-      </c>
-      <c r="J132">
-        <v>0</v>
-      </c>
-      <c r="K132">
-        <v>0</v>
-      </c>
-      <c r="L132">
-        <v>0</v>
-      </c>
-      <c r="M132">
-        <v>115935862.192436</v>
-      </c>
-      <c r="N132">
-        <v>50943164.71733537</v>
-      </c>
-      <c r="O132">
-        <v>218773100.6944216</v>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="inlineStr">
-        <is>
-          <t>dep</t>
-        </is>
-      </c>
-      <c r="B133" t="inlineStr">
-        <is>
-          <t>30-39</t>
-        </is>
-      </c>
-      <c r="C133" t="inlineStr">
-        <is>
-          <t>urban</t>
-        </is>
-      </c>
-      <c r="D133">
-        <v>5990.554782669715</v>
-      </c>
-      <c r="E133">
-        <v>4259.893540237262</v>
-      </c>
-      <c r="F133">
-        <v>7396.361523721891</v>
-      </c>
-      <c r="G133">
-        <v>8375.603719194654</v>
-      </c>
-      <c r="H133">
-        <v>3684.25405697945</v>
-      </c>
-      <c r="I133">
-        <v>15801.97502047102</v>
-      </c>
-      <c r="J133">
-        <v>0</v>
-      </c>
-      <c r="K133">
-        <v>0</v>
-      </c>
-      <c r="L133">
-        <v>0</v>
-      </c>
-      <c r="M133">
-        <v>1113955294.652889</v>
-      </c>
-      <c r="N133">
-        <v>490005789.5782669</v>
-      </c>
-      <c r="O133">
-        <v>2101662677.722646</v>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="inlineStr">
-        <is>
-          <t>dep</t>
-        </is>
-      </c>
-      <c r="B134" t="inlineStr">
-        <is>
-          <t>40-49</t>
-        </is>
-      </c>
-      <c r="C134" t="inlineStr">
-        <is>
-          <t>periurban</t>
-        </is>
-      </c>
-      <c r="D134">
-        <v>544.7261638476588</v>
-      </c>
-      <c r="E134">
-        <v>386.9348009216099</v>
-      </c>
-      <c r="F134">
-        <v>672.6844437589918</v>
-      </c>
-      <c r="G134">
-        <v>588.3262257105168</v>
-      </c>
-      <c r="H134">
-        <v>258.5153485480744</v>
-      </c>
-      <c r="I134">
-        <v>1110.182390371125</v>
-      </c>
-      <c r="J134">
-        <v>0</v>
-      </c>
-      <c r="K134">
-        <v>0</v>
-      </c>
-      <c r="L134">
-        <v>0</v>
-      </c>
-      <c r="M134">
-        <v>78247388.01949874</v>
-      </c>
-      <c r="N134">
-        <v>34382541.35689389</v>
-      </c>
-      <c r="O134">
-        <v>147654257.9193596</v>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="inlineStr">
-        <is>
-          <t>dep</t>
-        </is>
-      </c>
-      <c r="B135" t="inlineStr">
-        <is>
-          <t>40-49</t>
-        </is>
-      </c>
-      <c r="C135" t="inlineStr">
-        <is>
-          <t>rural</t>
-        </is>
-      </c>
-      <c r="D135">
-        <v>582.2766481289584</v>
-      </c>
-      <c r="E135">
-        <v>413.6079995380767</v>
-      </c>
-      <c r="F135">
-        <v>719.0556818380037</v>
-      </c>
-      <c r="G135">
-        <v>636.4108061101193</v>
-      </c>
-      <c r="H135">
-        <v>279.644105891466</v>
-      </c>
-      <c r="I135">
-        <v>1200.918876482301</v>
-      </c>
-      <c r="J135">
-        <v>0</v>
-      </c>
-      <c r="K135">
-        <v>0</v>
-      </c>
-      <c r="L135">
-        <v>0</v>
-      </c>
-      <c r="M135">
-        <v>84642637.21264587</v>
-      </c>
-      <c r="N135">
-        <v>37192666.08356498</v>
-      </c>
-      <c r="O135">
-        <v>159722210.572146</v>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="inlineStr">
-        <is>
-          <t>dep</t>
-        </is>
-      </c>
-      <c r="B136" t="inlineStr">
-        <is>
-          <t>40-49</t>
-        </is>
-      </c>
-      <c r="C136" t="inlineStr">
-        <is>
-          <t>urban</t>
-        </is>
-      </c>
-      <c r="D136">
-        <v>5276.722736850737</v>
-      </c>
-      <c r="E136">
-        <v>3750.560172365405</v>
-      </c>
-      <c r="F136">
-        <v>6515.535387864549</v>
-      </c>
-      <c r="G136">
-        <v>6052.388098484555</v>
-      </c>
-      <c r="H136">
-        <v>2661.116456329898</v>
-      </c>
-      <c r="I136">
-        <v>11419.73840282208</v>
-      </c>
-      <c r="J136">
-        <v>0</v>
-      </c>
-      <c r="K136">
-        <v>0</v>
-      </c>
-      <c r="L136">
-        <v>0</v>
-      </c>
-      <c r="M136">
-        <v>804967617.0984459</v>
-      </c>
-      <c r="N136">
-        <v>353928488.6918764</v>
-      </c>
-      <c r="O136">
-        <v>1518825207.575337</v>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="inlineStr">
-        <is>
-          <t>dep</t>
-        </is>
-      </c>
-      <c r="B137" t="inlineStr">
-        <is>
-          <t>50-59</t>
-        </is>
-      </c>
-      <c r="C137" t="inlineStr">
-        <is>
-          <t>periurban</t>
-        </is>
-      </c>
-      <c r="D137">
-        <v>724.8065691842462</v>
-      </c>
-      <c r="E137">
-        <v>514.8511383646601</v>
-      </c>
-      <c r="F137">
-        <v>895.066431875896</v>
-      </c>
-      <c r="G137">
-        <v>614.986527303465</v>
-      </c>
-      <c r="H137">
-        <v>270.23010280771</v>
-      </c>
-      <c r="I137">
-        <v>1160.490868995767</v>
-      </c>
-      <c r="J137">
-        <v>0</v>
-      </c>
-      <c r="K137">
-        <v>0</v>
-      </c>
-      <c r="L137">
-        <v>0</v>
-      </c>
-      <c r="M137">
-        <v>81793208.13136084</v>
-      </c>
-      <c r="N137">
-        <v>35940603.67342542</v>
-      </c>
-      <c r="O137">
-        <v>154345285.576437</v>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" t="inlineStr">
-        <is>
-          <t>dep</t>
-        </is>
-      </c>
-      <c r="B138" t="inlineStr">
-        <is>
-          <t>50-59</t>
-        </is>
-      </c>
-      <c r="C138" t="inlineStr">
-        <is>
-          <t>rural</t>
-        </is>
-      </c>
-      <c r="D138">
-        <v>1321.002722642593</v>
-      </c>
-      <c r="E138">
-        <v>938.3465664512601</v>
-      </c>
-      <c r="F138">
-        <v>1631.311364609729</v>
-      </c>
-      <c r="G138">
-        <v>1100.074482928139</v>
-      </c>
-      <c r="H138">
-        <v>483.381712313708</v>
-      </c>
-      <c r="I138">
-        <v>2075.860748122363</v>
-      </c>
-      <c r="J138">
-        <v>0</v>
-      </c>
-      <c r="K138">
-        <v>0</v>
-      </c>
-      <c r="L138">
-        <v>0</v>
-      </c>
-      <c r="M138">
-        <v>146309906.2294425</v>
-      </c>
-      <c r="N138">
-        <v>64289767.73772316</v>
-      </c>
-      <c r="O138">
-        <v>276089479.5002743</v>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" t="inlineStr">
-        <is>
-          <t>dep</t>
-        </is>
-      </c>
-      <c r="B139" t="inlineStr">
-        <is>
-          <t>50-59</t>
-        </is>
-      </c>
-      <c r="C139" t="inlineStr">
-        <is>
-          <t>urban</t>
-        </is>
-      </c>
-      <c r="D139">
-        <v>2935.718004909213</v>
-      </c>
-      <c r="E139">
-        <v>2085.492182811953</v>
-      </c>
-      <c r="F139">
-        <v>3625.279226655072</v>
-      </c>
-      <c r="G139">
-        <v>2431.672515648101</v>
-      </c>
-      <c r="H139">
-        <v>1068.576642067892</v>
-      </c>
-      <c r="I139">
-        <v>4588.551101625951</v>
-      </c>
-      <c r="J139">
-        <v>0</v>
-      </c>
-      <c r="K139">
-        <v>0</v>
-      </c>
-      <c r="L139">
-        <v>0</v>
-      </c>
-      <c r="M139">
-        <v>323412444.5811974</v>
-      </c>
-      <c r="N139">
-        <v>142120693.3950296</v>
-      </c>
-      <c r="O139">
-        <v>610277296.5162514</v>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" t="inlineStr">
-        <is>
-          <t>dep</t>
-        </is>
-      </c>
-      <c r="B140" t="inlineStr">
-        <is>
-          <t>60-69</t>
-        </is>
-      </c>
-      <c r="C140" t="inlineStr">
-        <is>
-          <t>periurban</t>
-        </is>
-      </c>
-      <c r="D140">
-        <v>381.8825384029423</v>
-      </c>
-      <c r="E140">
-        <v>271.2622484087365</v>
-      </c>
-      <c r="F140">
-        <v>471.5882217082156</v>
-      </c>
-      <c r="G140">
-        <v>180.5594372635156</v>
-      </c>
-      <c r="H140">
-        <v>79.33929139645268</v>
-      </c>
-      <c r="I140">
-        <v>340.7189734287103</v>
-      </c>
-      <c r="J140">
-        <v>0</v>
-      </c>
-      <c r="K140">
-        <v>0</v>
-      </c>
-      <c r="L140">
-        <v>0</v>
-      </c>
-      <c r="M140">
-        <v>24014405.15604758</v>
-      </c>
-      <c r="N140">
-        <v>10552125.75572821</v>
-      </c>
-      <c r="O140">
-        <v>45315623.46601848</v>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" t="inlineStr">
-        <is>
-          <t>dep</t>
-        </is>
-      </c>
-      <c r="B141" t="inlineStr">
-        <is>
-          <t>60-69</t>
-        </is>
-      </c>
-      <c r="C141" t="inlineStr">
-        <is>
-          <t>rural</t>
-        </is>
-      </c>
-      <c r="D141">
-        <v>1423.461358611975</v>
-      </c>
-      <c r="E141">
-        <v>1011.125908701834</v>
-      </c>
-      <c r="F141">
-        <v>1757.837929918317</v>
-      </c>
-      <c r="G141">
-        <v>798.6550394144645</v>
-      </c>
-      <c r="H141">
-        <v>350.9355470845457</v>
-      </c>
-      <c r="I141">
-        <v>1507.076723748444</v>
-      </c>
-      <c r="J141">
-        <v>0</v>
-      </c>
-      <c r="K141">
-        <v>0</v>
-      </c>
-      <c r="L141">
-        <v>0</v>
-      </c>
-      <c r="M141">
-        <v>106221120.2421238</v>
-      </c>
-      <c r="N141">
-        <v>46674427.76224458</v>
-      </c>
-      <c r="O141">
-        <v>200441204.2585431</v>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" t="inlineStr">
-        <is>
-          <t>dep</t>
-        </is>
-      </c>
-      <c r="B142" t="inlineStr">
-        <is>
-          <t>60-69</t>
-        </is>
-      </c>
-      <c r="C142" t="inlineStr">
-        <is>
-          <t>urban</t>
-        </is>
-      </c>
-      <c r="D142">
-        <v>2586.110968289174</v>
-      </c>
-      <c r="E142">
-        <v>1836.989663958958</v>
-      </c>
-      <c r="F142">
-        <v>3193.598423682746</v>
-      </c>
-      <c r="G142">
-        <v>1435.899519454086</v>
-      </c>
-      <c r="H142">
-        <v>630.9459761094065</v>
-      </c>
-      <c r="I142">
-        <v>2709.568758243086</v>
-      </c>
-      <c r="J142">
-        <v>0</v>
-      </c>
-      <c r="K142">
-        <v>0</v>
-      </c>
-      <c r="L142">
-        <v>0</v>
-      </c>
-      <c r="M142">
-        <v>190974636.0873934</v>
-      </c>
-      <c r="N142">
-        <v>83915814.82255107</v>
-      </c>
-      <c r="O142">
-        <v>360372644.8463305</v>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="inlineStr">
-        <is>
-          <t>dep</t>
-        </is>
-      </c>
-      <c r="B143" t="inlineStr">
-        <is>
-          <t>70-79</t>
-        </is>
-      </c>
-      <c r="C143" t="inlineStr">
-        <is>
-          <t>periurban</t>
-        </is>
-      </c>
-      <c r="D143">
-        <v>80.16591261426292</v>
-      </c>
-      <c r="E143">
-        <v>56.94417396623137</v>
-      </c>
-      <c r="F143">
-        <v>98.99719513094433</v>
-      </c>
-      <c r="G143">
-        <v>21.63280642764433</v>
-      </c>
-      <c r="H143">
-        <v>9.505631823503316</v>
-      </c>
-      <c r="I143">
-        <v>40.82150293618761</v>
-      </c>
-      <c r="J143">
-        <v>0</v>
-      </c>
-      <c r="K143">
-        <v>0</v>
-      </c>
-      <c r="L143">
-        <v>0</v>
-      </c>
-      <c r="M143">
-        <v>2877163.254876696</v>
-      </c>
-      <c r="N143">
-        <v>1264249.032525941</v>
-      </c>
-      <c r="O143">
-        <v>5429259.890512953</v>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="inlineStr">
-        <is>
-          <t>dep</t>
-        </is>
-      </c>
-      <c r="B144" t="inlineStr">
-        <is>
-          <t>70-79</t>
-        </is>
-      </c>
-      <c r="C144" t="inlineStr">
-        <is>
-          <t>rural</t>
-        </is>
-      </c>
-      <c r="D144">
-        <v>1042.186650094989</v>
-      </c>
-      <c r="E144">
-        <v>740.2954194989635</v>
-      </c>
-      <c r="F144">
-        <v>1287.000319684038</v>
-      </c>
-      <c r="G144">
-        <v>289.8443526585154</v>
-      </c>
-      <c r="H144">
-        <v>127.3599757714616</v>
-      </c>
-      <c r="I144">
-        <v>546.9416153961021</v>
-      </c>
-      <c r="J144">
-        <v>0</v>
-      </c>
-      <c r="K144">
-        <v>0</v>
-      </c>
-      <c r="L144">
-        <v>0</v>
-      </c>
-      <c r="M144">
-        <v>38549298.90358256</v>
-      </c>
-      <c r="N144">
-        <v>16938876.77760439</v>
-      </c>
-      <c r="O144">
-        <v>72743234.84768158</v>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="inlineStr">
-        <is>
-          <t>dep</t>
-        </is>
-      </c>
-      <c r="B145" t="inlineStr">
-        <is>
-          <t>70-79</t>
-        </is>
-      </c>
-      <c r="C145" t="inlineStr">
-        <is>
-          <t>urban</t>
-        </is>
-      </c>
-      <c r="D145">
-        <v>597.2206318970154</v>
-      </c>
-      <c r="E145">
-        <v>424.2231448496694</v>
-      </c>
-      <c r="F145">
-        <v>737.5100651148285</v>
-      </c>
-      <c r="G145">
-        <v>171.6012316299011</v>
-      </c>
-      <c r="H145">
-        <v>75.40298267769322</v>
-      </c>
-      <c r="I145">
-        <v>323.8146749134576</v>
-      </c>
-      <c r="J145">
-        <v>0</v>
-      </c>
-      <c r="K145">
-        <v>0</v>
-      </c>
-      <c r="L145">
-        <v>0</v>
-      </c>
-      <c r="M145">
-        <v>22822963.80677684</v>
-      </c>
-      <c r="N145">
-        <v>10028596.6961332</v>
-      </c>
-      <c r="O145">
-        <v>43067351.76348986</v>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" t="inlineStr">
-        <is>
-          <t>dep</t>
-        </is>
-      </c>
-      <c r="B146" t="inlineStr">
-        <is>
-          <t>80-89</t>
-        </is>
-      </c>
-      <c r="C146" t="inlineStr">
-        <is>
-          <t>periurban</t>
-        </is>
-      </c>
-      <c r="D146">
-        <v>48.05773429137659</v>
-      </c>
-      <c r="E146">
-        <v>34.13680319562891</v>
-      </c>
-      <c r="F146">
-        <v>59.34668170107042</v>
-      </c>
-      <c r="G146">
-        <v>1.054397099275154</v>
-      </c>
-      <c r="H146">
-        <v>0.4633106968808078</v>
-      </c>
-      <c r="I146">
-        <v>1.989666686471402</v>
-      </c>
-      <c r="J146">
-        <v>0</v>
-      </c>
-      <c r="K146">
-        <v>0</v>
-      </c>
-      <c r="L146">
-        <v>0</v>
-      </c>
-      <c r="M146">
-        <v>140234.8142035955</v>
-      </c>
-      <c r="N146">
-        <v>61620.32268514744</v>
-      </c>
-      <c r="O146">
-        <v>264625.6693006965</v>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" t="inlineStr">
-        <is>
-          <t>dep</t>
-        </is>
-      </c>
-      <c r="B147" t="inlineStr">
-        <is>
-          <t>80-89</t>
-        </is>
-      </c>
-      <c r="C147" t="inlineStr">
-        <is>
-          <t>rural</t>
-        </is>
-      </c>
-      <c r="D147">
-        <v>1309.027711323072</v>
-      </c>
-      <c r="E147">
-        <v>929.8403684228346</v>
-      </c>
-      <c r="F147">
-        <v>1616.523376877364</v>
-      </c>
-      <c r="G147">
-        <v>59.81734263151537</v>
-      </c>
-      <c r="H147">
-        <v>26.284228891769</v>
-      </c>
-      <c r="I147">
-        <v>112.8764238719832</v>
-      </c>
-      <c r="J147">
-        <v>0</v>
-      </c>
-      <c r="K147">
-        <v>0</v>
-      </c>
-      <c r="L147">
-        <v>0</v>
-      </c>
-      <c r="M147">
-        <v>7955706.569991545</v>
-      </c>
-      <c r="N147">
-        <v>3495802.442605278</v>
-      </c>
-      <c r="O147">
-        <v>15012564.37497377</v>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" t="inlineStr">
-        <is>
-          <t>dep</t>
-        </is>
-      </c>
-      <c r="B148" t="inlineStr">
-        <is>
-          <t>80-89</t>
-        </is>
-      </c>
-      <c r="C148" t="inlineStr">
-        <is>
-          <t>urban</t>
-        </is>
-      </c>
-      <c r="D148">
-        <v>264.7870037486658</v>
-      </c>
-      <c r="E148">
-        <v>188.0858922920637</v>
-      </c>
-      <c r="F148">
-        <v>326.9864936781246</v>
-      </c>
-      <c r="G148">
-        <v>11.34277017894188</v>
-      </c>
-      <c r="H148">
-        <v>4.984105855163228</v>
-      </c>
-      <c r="I148">
-        <v>21.4040155960753</v>
-      </c>
-      <c r="J148">
-        <v>0</v>
-      </c>
-      <c r="K148">
-        <v>0</v>
-      </c>
-      <c r="L148">
-        <v>0</v>
-      </c>
-      <c r="M148">
-        <v>1508588.43379927</v>
-      </c>
-      <c r="N148">
-        <v>662886.0787367093</v>
-      </c>
-      <c r="O148">
-        <v>2846734.074278015</v>
+        <v>53413485.41255796</v>
       </c>
     </row>
   </sheetData>

--- a/output/Tables/Best practice/cases_prev_target_area_age.xlsx
+++ b/output/Tables/Best practice/cases_prev_target_area_age.xlsx
@@ -448,22 +448,22 @@
         </is>
       </c>
       <c r="D2">
-        <v>184.0297908221409</v>
+        <v>440.0899736899075</v>
       </c>
       <c r="E2">
-        <v>158.468138051187</v>
+        <v>307.1470133506409</v>
       </c>
       <c r="F2">
-        <v>207.9507005595431</v>
+        <v>571.2054629104746</v>
       </c>
       <c r="G2">
-        <v>10497.97547768416</v>
+        <v>25104.92312756283</v>
       </c>
       <c r="H2">
-        <v>9039.811542596595</v>
+        <v>17521.19480109209</v>
       </c>
       <c r="I2">
-        <v>11862.54326154825</v>
+        <v>32584.40340319039</v>
       </c>
       <c r="J2">
         <v>0</v>
@@ -475,13 +475,13 @@
         <v>0</v>
       </c>
       <c r="M2">
-        <v>1396230738.531993</v>
+        <v>3338954775.965857</v>
       </c>
       <c r="N2">
-        <v>1202294935.165347</v>
+        <v>2330318908.545248</v>
       </c>
       <c r="O2">
-        <v>1577718253.785918</v>
+        <v>4333725652.624322</v>
       </c>
     </row>
     <row r="3">
@@ -501,22 +501,22 @@
         </is>
       </c>
       <c r="D3">
-        <v>125.6772031842816</v>
+        <v>281.7419045976529</v>
       </c>
       <c r="E3">
-        <v>120.6843500203786</v>
+        <v>219.9357972412059</v>
       </c>
       <c r="F3">
-        <v>131.1925729230239</v>
+        <v>344.6074983604731</v>
       </c>
       <c r="G3">
-        <v>7134.554233129396</v>
+        <v>15994.17274706293</v>
       </c>
       <c r="H3">
-        <v>6851.115544382604</v>
+        <v>12485.50917323552</v>
       </c>
       <c r="I3">
-        <v>7447.655603304865</v>
+        <v>19562.98217896168</v>
       </c>
       <c r="J3">
         <v>0</v>
@@ -528,13 +528,13 @@
         <v>0</v>
       </c>
       <c r="M3">
-        <v>948895713.0062097</v>
+        <v>2127224975.35937</v>
       </c>
       <c r="N3">
-        <v>911198367.4028863</v>
+        <v>1660572720.040325</v>
       </c>
       <c r="O3">
-        <v>990538195.239547</v>
+        <v>2601876629.801903</v>
       </c>
     </row>
     <row r="4">
@@ -554,22 +554,22 @@
         </is>
       </c>
       <c r="D4">
-        <v>272.2016759993704</v>
+        <v>673.8196233079146</v>
       </c>
       <c r="E4">
-        <v>222.4626736210622</v>
+        <v>447.1162967713043</v>
       </c>
       <c r="F4">
-        <v>317.9538950406766</v>
+        <v>895.316420400437</v>
       </c>
       <c r="G4">
-        <v>15503.52272221162</v>
+        <v>38378.0805253032</v>
       </c>
       <c r="H4">
-        <v>12670.58736014563</v>
+        <v>25465.96247438637</v>
       </c>
       <c r="I4">
-        <v>18109.38679301233</v>
+        <v>50993.65540746869</v>
       </c>
       <c r="J4">
         <v>0</v>
@@ -581,13 +581,13 @@
         <v>0</v>
       </c>
       <c r="M4">
-        <v>2061968522.054146</v>
+        <v>5104284709.865326</v>
       </c>
       <c r="N4">
-        <v>1685188118.899369</v>
+        <v>3386973009.093387</v>
       </c>
       <c r="O4">
-        <v>2408548443.470641</v>
+        <v>6782156169.193336</v>
       </c>
     </row>
     <row r="5">
@@ -607,22 +607,22 @@
         </is>
       </c>
       <c r="D5">
-        <v>423.6560280423507</v>
+        <v>997.6201715929786</v>
       </c>
       <c r="E5">
-        <v>374.1107619285679</v>
+        <v>713.9045192864993</v>
       </c>
       <c r="F5">
-        <v>470.646258824306</v>
+        <v>1278.940247173525</v>
       </c>
       <c r="G5">
-        <v>19460.46263922942</v>
+        <v>45825.2657636825</v>
       </c>
       <c r="H5">
-        <v>17184.62154093741</v>
+        <v>32792.90581500513</v>
       </c>
       <c r="I5">
-        <v>21618.93925708036</v>
+        <v>58747.58589635649</v>
       </c>
       <c r="J5">
         <v>0</v>
@@ -634,13 +634,13 @@
         <v>0</v>
       </c>
       <c r="M5">
-        <v>2588241531.017513</v>
+        <v>6094760346.569773</v>
       </c>
       <c r="N5">
-        <v>2285554664.944675</v>
+        <v>4361456473.395682</v>
       </c>
       <c r="O5">
-        <v>2875318921.191688</v>
+        <v>7813428924.215413</v>
       </c>
     </row>
     <row r="6">
@@ -660,22 +660,22 @@
         </is>
       </c>
       <c r="D6">
-        <v>416.5691614117125</v>
+        <v>978.1767355233018</v>
       </c>
       <c r="E6">
-        <v>369.5751040134195</v>
+        <v>703.2870569219421</v>
       </c>
       <c r="F6">
-        <v>461.2775696290753</v>
+        <v>1251.039275624142</v>
       </c>
       <c r="G6">
-        <v>19125.54070477013</v>
+        <v>44910.09105981329</v>
       </c>
       <c r="H6">
-        <v>16967.94758240013</v>
+        <v>32289.34467620049</v>
       </c>
       <c r="I6">
-        <v>21178.19500666059</v>
+        <v>57437.76737608238</v>
       </c>
       <c r="J6">
         <v>0</v>
@@ -687,13 +687,13 @@
         <v>0</v>
       </c>
       <c r="M6">
-        <v>2543696913.734427</v>
+        <v>5973042110.955168</v>
       </c>
       <c r="N6">
-        <v>2256737028.459217</v>
+        <v>4294482841.934665</v>
       </c>
       <c r="O6">
-        <v>2816699935.885859</v>
+        <v>7639223061.018957</v>
       </c>
     </row>
     <row r="7">
@@ -713,22 +713,22 @@
         </is>
       </c>
       <c r="D7">
-        <v>726.8503517840966</v>
+        <v>2011.407627386185</v>
       </c>
       <c r="E7">
-        <v>556.0948523070297</v>
+        <v>1242.732716260226</v>
       </c>
       <c r="F7">
-        <v>882.3809962541134</v>
+        <v>2741.861513312861</v>
       </c>
       <c r="G7">
-        <v>33509.6114144764</v>
+        <v>92730.9009679695</v>
       </c>
       <c r="H7">
-        <v>25637.35762754975</v>
+        <v>57293.07320512491</v>
       </c>
       <c r="I7">
-        <v>40679.96146857048</v>
+        <v>126406.644280904</v>
       </c>
       <c r="J7">
         <v>0</v>
@@ -740,13 +740,13 @@
         <v>0</v>
       </c>
       <c r="M7">
-        <v>4456778318.125361</v>
+        <v>12333209828.73994</v>
       </c>
       <c r="N7">
-        <v>3409768564.464117</v>
+        <v>7619978736.281613</v>
       </c>
       <c r="O7">
-        <v>5410434875.319874</v>
+        <v>16812083689.36023</v>
       </c>
     </row>
     <row r="8">
@@ -766,22 +766,22 @@
         </is>
       </c>
       <c r="D8">
-        <v>1503.788598607241</v>
+        <v>3606.235638822462</v>
       </c>
       <c r="E8">
-        <v>1289.144674303293</v>
+        <v>2505.836719345886</v>
       </c>
       <c r="F8">
-        <v>1704.268448069612</v>
+        <v>4690.551102939856</v>
       </c>
       <c r="G8">
-        <v>55179.01918704273</v>
+        <v>132324.8132695499</v>
       </c>
       <c r="H8">
-        <v>47303.01771415012</v>
+        <v>91947.50681342056</v>
       </c>
       <c r="I8">
-        <v>62535.29351333099</v>
+        <v>172111.9641062795</v>
       </c>
       <c r="J8">
         <v>0</v>
@@ -793,13 +793,13 @@
         <v>0</v>
       </c>
       <c r="M8">
-        <v>7338809551.876683</v>
+        <v>17599200164.85014</v>
       </c>
       <c r="N8">
-        <v>6291301355.981966</v>
+        <v>12229018406.18493</v>
       </c>
       <c r="O8">
-        <v>8317194037.273023</v>
+        <v>22890891226.13517</v>
       </c>
     </row>
     <row r="9">
@@ -819,22 +819,22 @@
         </is>
       </c>
       <c r="D9">
-        <v>1206.08232659046</v>
+        <v>2780.731842204893</v>
       </c>
       <c r="E9">
-        <v>1103.553010966539</v>
+        <v>2063.192082946152</v>
       </c>
       <c r="F9">
-        <v>1306.412284081256</v>
+        <v>3498.657064361859</v>
       </c>
       <c r="G9">
-        <v>43974.86365754621</v>
+        <v>101388.0237967206</v>
       </c>
       <c r="H9">
-        <v>40236.55112608794</v>
+        <v>75225.8685386523</v>
       </c>
       <c r="I9">
-        <v>47632.98558185762</v>
+        <v>127564.2333842658</v>
       </c>
       <c r="J9">
         <v>0</v>
@@ -846,13 +846,13 @@
         <v>0</v>
       </c>
       <c r="M9">
-        <v>5848656866.453646</v>
+        <v>13484607164.96384</v>
       </c>
       <c r="N9">
-        <v>5351461299.769695</v>
+        <v>10005040515.64076</v>
       </c>
       <c r="O9">
-        <v>6335187082.387063</v>
+        <v>16966043040.10736</v>
       </c>
     </row>
     <row r="10">
@@ -872,22 +872,22 @@
         </is>
       </c>
       <c r="D10">
-        <v>1957.015374270655</v>
+        <v>5220.349811364322</v>
       </c>
       <c r="E10">
-        <v>1492.542659390586</v>
+        <v>3238.090935766625</v>
       </c>
       <c r="F10">
-        <v>2379.322482136924</v>
+        <v>7123.220123375438</v>
       </c>
       <c r="G10">
-        <v>71417.36914009105</v>
+        <v>190506.244570284</v>
       </c>
       <c r="H10">
-        <v>54467.36467400323</v>
+        <v>118167.6642448519</v>
       </c>
       <c r="I10">
-        <v>86828.62395673255</v>
+        <v>259947.6977572651</v>
       </c>
       <c r="J10">
         <v>0</v>
@@ -899,13 +899,13 @@
         <v>0</v>
       </c>
       <c r="M10">
-        <v>9498510095.632109</v>
+        <v>25337330527.84778</v>
       </c>
       <c r="N10">
-        <v>7244159501.64243</v>
+        <v>15716299344.5653</v>
       </c>
       <c r="O10">
-        <v>11548206986.24543</v>
+        <v>34573043801.71626</v>
       </c>
     </row>
     <row r="11">
@@ -925,22 +925,22 @@
         </is>
       </c>
       <c r="D11">
-        <v>2909.842257110345</v>
+        <v>6929.450997483879</v>
       </c>
       <c r="E11">
-        <v>2522.681343039547</v>
+        <v>4868.613930757308</v>
       </c>
       <c r="F11">
-        <v>3273.293882534601</v>
+        <v>8964.753750143735</v>
       </c>
       <c r="G11">
-        <v>77467.68185808836</v>
+        <v>184480.2768990572</v>
       </c>
       <c r="H11">
-        <v>67160.43635505956</v>
+        <v>129615.3542880733</v>
       </c>
       <c r="I11">
-        <v>87143.72351305129</v>
+        <v>238665.4086678568</v>
       </c>
       <c r="J11">
         <v>0</v>
@@ -952,13 +952,13 @@
         <v>0</v>
       </c>
       <c r="M11">
-        <v>10303201687.12575</v>
+        <v>24535876827.57461</v>
       </c>
       <c r="N11">
-        <v>8932338035.222921</v>
+        <v>17238842120.31374</v>
       </c>
       <c r="O11">
-        <v>11590115227.23582</v>
+        <v>31742499352.82495</v>
       </c>
     </row>
     <row r="12">
@@ -978,22 +978,22 @@
         </is>
       </c>
       <c r="D12">
-        <v>2127.507217994631</v>
+        <v>4710.052790127407</v>
       </c>
       <c r="E12">
-        <v>2087.878605485205</v>
+        <v>3764.19073846491</v>
       </c>
       <c r="F12">
-        <v>2181.920916676962</v>
+        <v>5681.656451814916</v>
       </c>
       <c r="G12">
-        <v>56251.37102312798</v>
+        <v>124533.9732786954</v>
       </c>
       <c r="H12">
-        <v>55203.58901489555</v>
+        <v>99525.34498604303</v>
       </c>
       <c r="I12">
-        <v>57690.07126697757</v>
+        <v>150223.2107105348</v>
       </c>
       <c r="J12">
         <v>0</v>
@@ -1005,13 +1005,13 @@
         <v>0</v>
       </c>
       <c r="M12">
-        <v>7481432346.076021</v>
+        <v>16563018446.06648</v>
       </c>
       <c r="N12">
-        <v>7342077338.981109</v>
+        <v>13236870883.14372</v>
       </c>
       <c r="O12">
-        <v>7672779478.508017</v>
+        <v>19979687024.50113</v>
       </c>
     </row>
     <row r="13">
@@ -1031,22 +1031,22 @@
         </is>
       </c>
       <c r="D13">
-        <v>3493.570314426226</v>
+        <v>9106.241830190571</v>
       </c>
       <c r="E13">
-        <v>2695.870864716214</v>
+        <v>5722.041321036823</v>
       </c>
       <c r="F13">
-        <v>4219.674616467965</v>
+        <v>12378.80431748128</v>
       </c>
       <c r="G13">
-        <v>92476.73733384541</v>
+        <v>241047.2548245575</v>
       </c>
       <c r="H13">
-        <v>71361.19196251886</v>
+        <v>151465.5966916873</v>
       </c>
       <c r="I13">
-        <v>111697.1195713551</v>
+        <v>327673.7928095185</v>
       </c>
       <c r="J13">
         <v>0</v>
@@ -1058,13 +1058,13 @@
         <v>0</v>
       </c>
       <c r="M13">
-        <v>12299406065.40144</v>
+        <v>32059284891.66614</v>
       </c>
       <c r="N13">
-        <v>9491038531.015009</v>
+        <v>20144924359.99441</v>
       </c>
       <c r="O13">
-        <v>14855716902.99023</v>
+        <v>43580614443.66596</v>
       </c>
     </row>
     <row r="14">
@@ -1084,22 +1084,22 @@
         </is>
       </c>
       <c r="D14">
-        <v>5483.853455551071</v>
+        <v>12913.31283682508</v>
       </c>
       <c r="E14">
-        <v>4842.53370367655</v>
+        <v>9240.864063974659</v>
       </c>
       <c r="F14">
-        <v>6092.100529578328</v>
+        <v>16554.75298277774</v>
       </c>
       <c r="G14">
-        <v>90651.98160057292</v>
+        <v>213466.2071433252</v>
       </c>
       <c r="H14">
-        <v>80050.51188256592</v>
+        <v>152758.0278887389</v>
       </c>
       <c r="I14">
-        <v>100706.7365297927</v>
+        <v>273661.7918332003</v>
       </c>
       <c r="J14">
         <v>0</v>
@@ -1111,13 +1111,13 @@
         <v>0</v>
       </c>
       <c r="M14">
-        <v>12056713552.8762</v>
+        <v>28391005550.06225</v>
       </c>
       <c r="N14">
-        <v>10646718080.38127</v>
+        <v>20316817709.20227</v>
       </c>
       <c r="O14">
-        <v>13393995958.46243</v>
+        <v>36397018313.81564</v>
       </c>
     </row>
     <row r="15">
@@ -1137,22 +1137,22 @@
         </is>
       </c>
       <c r="D15">
-        <v>4440.597504877544</v>
+        <v>9844.615311575395</v>
       </c>
       <c r="E15">
-        <v>4347.396024316141</v>
+        <v>7847.030046662447</v>
       </c>
       <c r="F15">
-        <v>4563.270681242146</v>
+        <v>11894.11886616469</v>
       </c>
       <c r="G15">
-        <v>75313.91689811682</v>
+        <v>166967.7422138636</v>
       </c>
       <c r="H15">
-        <v>73733.19075617942</v>
+        <v>133088.0738869526</v>
       </c>
       <c r="I15">
-        <v>77394.49218110608</v>
+        <v>201727.9609058726</v>
       </c>
       <c r="J15">
         <v>0</v>
@@ -1164,13 +1164,13 @@
         <v>0</v>
       </c>
       <c r="M15">
-        <v>10016750947.44954</v>
+        <v>22206709714.44386</v>
       </c>
       <c r="N15">
-        <v>9806514370.571863</v>
+        <v>17700713826.96469</v>
       </c>
       <c r="O15">
-        <v>10293467460.08711</v>
+        <v>26829818800.48106</v>
       </c>
     </row>
     <row r="16">
@@ -1190,22 +1190,22 @@
         </is>
       </c>
       <c r="D16">
-        <v>5366.253777700224</v>
+        <v>13247.74297466805</v>
       </c>
       <c r="E16">
-        <v>4402.554627554245</v>
+        <v>8822.75870320693</v>
       </c>
       <c r="F16">
-        <v>6253.552183834168</v>
+        <v>17573.85178285685</v>
       </c>
       <c r="G16">
-        <v>90963.70453714528</v>
+        <v>224563.3225061877</v>
       </c>
       <c r="H16">
-        <v>74627.9797675007</v>
+        <v>149555.136437283</v>
       </c>
       <c r="I16">
-        <v>106004.355500626</v>
+        <v>297895.46439238</v>
       </c>
       <c r="J16">
         <v>0</v>
@@ -1217,13 +1217,13 @@
         <v>0</v>
       </c>
       <c r="M16">
-        <v>12098172703.44032</v>
+        <v>29866921893.32297</v>
       </c>
       <c r="N16">
-        <v>9925521309.077593</v>
+        <v>19890833146.15864</v>
       </c>
       <c r="O16">
-        <v>14098579281.58325</v>
+        <v>39620096764.18655</v>
       </c>
     </row>
     <row r="17">
@@ -1243,22 +1243,22 @@
         </is>
       </c>
       <c r="D17">
-        <v>5677.779648050745</v>
+        <v>12431.73218647077</v>
       </c>
       <c r="E17">
-        <v>5680.032156242519</v>
+        <v>10146.85118449455</v>
       </c>
       <c r="F17">
-        <v>5729.288084721476</v>
+        <v>14803.812594564</v>
       </c>
       <c r="G17">
-        <v>39984.07069352455</v>
+        <v>87546.76817327</v>
       </c>
       <c r="H17">
-        <v>39999.93331101951</v>
+        <v>71456.17481241772</v>
       </c>
       <c r="I17">
-        <v>40346.80350473229</v>
+        <v>104251.4373586066</v>
       </c>
       <c r="J17">
         <v>0</v>
@@ -1270,13 +1270,13 @@
         <v>0</v>
       </c>
       <c r="M17">
-        <v>5317881402.238765</v>
+        <v>11643720167.04491</v>
       </c>
       <c r="N17">
-        <v>5319991130.365595</v>
+        <v>9503671250.051558</v>
       </c>
       <c r="O17">
-        <v>5366124866.129395</v>
+        <v>13865441168.69468</v>
       </c>
     </row>
     <row r="18">
@@ -1296,22 +1296,22 @@
         </is>
       </c>
       <c r="D18">
-        <v>5063.39385099504</v>
+        <v>10891.21354754421</v>
       </c>
       <c r="E18">
-        <v>5223.847843349879</v>
+        <v>9201.192511784431</v>
       </c>
       <c r="F18">
-        <v>4971.88485099111</v>
+        <v>12685.68855870182</v>
       </c>
       <c r="G18">
-        <v>36698.09950871272</v>
+        <v>78936.5493383203</v>
       </c>
       <c r="H18">
-        <v>37861.02634223382</v>
+        <v>66687.73718440464</v>
       </c>
       <c r="I18">
-        <v>36034.86720111192</v>
+        <v>91942.41545565172</v>
       </c>
       <c r="J18">
         <v>0</v>
@@ -1323,13 +1323,13 @@
         <v>0</v>
       </c>
       <c r="M18">
-        <v>4880847234.658792</v>
+        <v>10498561061.9966</v>
       </c>
       <c r="N18">
-        <v>5035516503.517098</v>
+        <v>8869469045.525818</v>
       </c>
       <c r="O18">
-        <v>4792637337.747886</v>
+        <v>12228341255.60168</v>
       </c>
     </row>
     <row r="19">
@@ -1349,22 +1349,22 @@
         </is>
       </c>
       <c r="D19">
-        <v>6277.883809061845</v>
+        <v>14433.5451798688</v>
       </c>
       <c r="E19">
-        <v>5771.856099969797</v>
+        <v>10762.43363184686</v>
       </c>
       <c r="F19">
-        <v>6776.111969480356</v>
+        <v>18111.72051866828</v>
       </c>
       <c r="G19">
-        <v>46646.0997561085</v>
+        <v>107244.512445838</v>
       </c>
       <c r="H19">
-        <v>42886.19917247701</v>
+        <v>79967.32148578081</v>
       </c>
       <c r="I19">
-        <v>50348.04792511377</v>
+        <v>134574.1889725751</v>
       </c>
       <c r="J19">
         <v>0</v>
@@ -1376,13 +1376,13 @@
         <v>0</v>
       </c>
       <c r="M19">
-        <v>6203931267.56243</v>
+        <v>14263520155.29645</v>
       </c>
       <c r="N19">
-        <v>5703864489.939443</v>
+        <v>10635653757.60885</v>
       </c>
       <c r="O19">
-        <v>6696290374.040131</v>
+        <v>17898367133.35249</v>
       </c>
     </row>
     <row r="20">
@@ -1402,22 +1402,22 @@
         </is>
       </c>
       <c r="D20">
-        <v>6914.503982485444</v>
+        <v>14974.44806517447</v>
       </c>
       <c r="E20">
-        <v>7050.093686732139</v>
+        <v>12483.999063581</v>
       </c>
       <c r="F20">
-        <v>6861.990101827048</v>
+        <v>17593.55287676645</v>
       </c>
       <c r="G20">
-        <v>5280.33572809031</v>
+        <v>11435.3991735719</v>
       </c>
       <c r="H20">
-        <v>5383.880271778272</v>
+        <v>9533.540865960651</v>
       </c>
       <c r="I20">
-        <v>5240.232935328376</v>
+        <v>13435.50688155694</v>
       </c>
       <c r="J20">
         <v>0</v>
@@ -1429,13 +1429,13 @@
         <v>0</v>
       </c>
       <c r="M20">
-        <v>702284651.8360113</v>
+        <v>1520908090.085063</v>
       </c>
       <c r="N20">
-        <v>716056076.1465101</v>
+        <v>1267960935.172767</v>
       </c>
       <c r="O20">
-        <v>696950980.398674</v>
+        <v>1786922415.247073</v>
       </c>
     </row>
     <row r="21">
@@ -1455,22 +1455,22 @@
         </is>
       </c>
       <c r="D21">
-        <v>5990.296033973489</v>
+        <v>12429.86471475313</v>
       </c>
       <c r="E21">
-        <v>6573.322859446153</v>
+        <v>11279.03976054728</v>
       </c>
       <c r="F21">
-        <v>5541.030202217163</v>
+        <v>13768.71334513649</v>
       </c>
       <c r="G21">
-        <v>4402.289309390806</v>
+        <v>9134.750643472775</v>
       </c>
       <c r="H21">
-        <v>4830.757743389689</v>
+        <v>8289.005397470302</v>
       </c>
       <c r="I21">
-        <v>4072.122293103374</v>
+        <v>10118.67514052631</v>
       </c>
       <c r="J21">
         <v>0</v>
@@ -1482,13 +1482,13 @@
         <v>0</v>
       </c>
       <c r="M21">
-        <v>585504478.1489772</v>
+        <v>1214921835.581879</v>
       </c>
       <c r="N21">
-        <v>642490779.8708287</v>
+        <v>1102437717.86355</v>
       </c>
       <c r="O21">
-        <v>541592264.9827487</v>
+        <v>1345783793.689999</v>
       </c>
     </row>
     <row r="22">
@@ -1508,22 +1508,22 @@
         </is>
       </c>
       <c r="D22">
-        <v>7269.88116884159</v>
+        <v>15939.64510671805</v>
       </c>
       <c r="E22">
-        <v>7255.394201162701</v>
+        <v>12975.69936150938</v>
       </c>
       <c r="F22">
-        <v>7350.903042680936</v>
+        <v>19012.28355563077</v>
       </c>
       <c r="G22">
-        <v>6076.118246232678</v>
+        <v>13322.24918427869</v>
       </c>
       <c r="H22">
-        <v>6064.010135164301</v>
+        <v>10845.00307735564</v>
       </c>
       <c r="I22">
-        <v>6143.835788589383</v>
+        <v>15890.3399288059</v>
       </c>
       <c r="J22">
         <v>0</v>
@@ -1535,13 +1535,13 @@
         <v>0</v>
       </c>
       <c r="M22">
-        <v>808123726.7489462</v>
+        <v>1771859141.509066</v>
       </c>
       <c r="N22">
-        <v>806513347.9768519</v>
+        <v>1442385409.288301</v>
       </c>
       <c r="O22">
-        <v>817130159.8823879</v>
+        <v>2113415210.531185</v>
       </c>
     </row>
     <row r="23">
@@ -1561,40 +1561,40 @@
         </is>
       </c>
       <c r="D23">
-        <v>70.00621305999313</v>
+        <v>467.2741116055834</v>
       </c>
       <c r="E23">
-        <v>42.55000000855148</v>
+        <v>326.1193309912956</v>
       </c>
       <c r="F23">
-        <v>100.5398414677183</v>
+        <v>606.4885391227202</v>
       </c>
       <c r="G23">
-        <v>261.7454460585686</v>
+        <v>1747.085943200667</v>
       </c>
       <c r="H23">
-        <v>124.8639004804226</v>
+        <v>957.0042698344395</v>
       </c>
       <c r="I23">
-        <v>458.2273434492053</v>
+        <v>2764.174162775325</v>
       </c>
       <c r="J23">
-        <v>3899486.07986773</v>
+        <v>26028102.56465426</v>
       </c>
       <c r="K23">
-        <v>2370120.100476335</v>
+        <v>18165498.97487716</v>
       </c>
       <c r="L23">
-        <v>5600270.249434839</v>
+        <v>33782624.60621376</v>
       </c>
       <c r="M23">
-        <v>34812144.32578963</v>
+        <v>232362430.4456887</v>
       </c>
       <c r="N23">
-        <v>16606898.76389621</v>
+        <v>127281567.8879804</v>
       </c>
       <c r="O23">
-        <v>60944236.67874431</v>
+        <v>367635163.6491182</v>
       </c>
     </row>
     <row r="24">
@@ -1614,40 +1614,40 @@
         </is>
       </c>
       <c r="D24">
-        <v>43.61042379933474</v>
+        <v>299.6393122026481</v>
       </c>
       <c r="E24">
-        <v>30.07758701311594</v>
+        <v>233.907026035789</v>
       </c>
       <c r="F24">
-        <v>59.1651398586857</v>
+        <v>366.4983877214387</v>
       </c>
       <c r="G24">
-        <v>162.370949935238</v>
+        <v>1115.621347413451</v>
       </c>
       <c r="H24">
-        <v>87.89330594817241</v>
+        <v>683.5276311835015</v>
       </c>
       <c r="I24">
-        <v>268.5246602201175</v>
+        <v>1663.37568489112</v>
       </c>
       <c r="J24">
-        <v>2429187.826470543</v>
+        <v>16690508.96831193</v>
       </c>
       <c r="K24">
-        <v>1675381.751804582</v>
+        <v>13029089.16424552</v>
       </c>
       <c r="L24">
-        <v>3295616.620408511</v>
+        <v>20414693.19285966</v>
       </c>
       <c r="M24">
-        <v>21595336.34138666</v>
+        <v>148377639.205989</v>
       </c>
       <c r="N24">
-        <v>11689809.69110693</v>
+        <v>90909174.9474057</v>
       </c>
       <c r="O24">
-        <v>35713779.80927563</v>
+        <v>221228966.090519</v>
       </c>
     </row>
     <row r="25">
@@ -1667,40 +1667,40 @@
         </is>
       </c>
       <c r="D25">
-        <v>108.2570000810117</v>
+        <v>712.3376288779198</v>
       </c>
       <c r="E25">
-        <v>62.33273135217439</v>
+        <v>472.6751071914139</v>
       </c>
       <c r="F25">
-        <v>158.5567012349194</v>
+        <v>946.4959967662919</v>
       </c>
       <c r="G25">
-        <v>404.1168446633121</v>
+        <v>2659.11335711935</v>
       </c>
       <c r="H25">
-        <v>182.6257054604304</v>
+        <v>1384.868319289613</v>
       </c>
       <c r="I25">
-        <v>721.4991484265951</v>
+        <v>4306.95171088526</v>
       </c>
       <c r="J25">
-        <v>6030131.418512522</v>
+        <v>39678630.60375764</v>
       </c>
       <c r="K25">
-        <v>3472057.801778818</v>
+        <v>26328948.82077617</v>
       </c>
       <c r="L25">
-        <v>8831925.372187482</v>
+        <v>52721720.01187593</v>
       </c>
       <c r="M25">
-        <v>53747540.3402205</v>
+        <v>353662076.4968736</v>
       </c>
       <c r="N25">
-        <v>24289218.82623724</v>
+        <v>184187486.4655185</v>
       </c>
       <c r="O25">
-        <v>95959386.74073714</v>
+        <v>572824577.5477395</v>
       </c>
     </row>
     <row r="26">
@@ -1720,40 +1720,40 @@
         </is>
       </c>
       <c r="D26">
-        <v>177.9779584180429</v>
+        <v>1195.879504227557</v>
       </c>
       <c r="E26">
-        <v>111.2026332705647</v>
+        <v>855.780393079776</v>
       </c>
       <c r="F26">
-        <v>252.76300585393</v>
+        <v>1533.106960221485</v>
       </c>
       <c r="G26">
-        <v>534.9040261075664</v>
+        <v>3594.15720483956</v>
       </c>
       <c r="H26">
-        <v>262.3128108655166</v>
+        <v>2018.676660706139</v>
       </c>
       <c r="I26">
-        <v>926.0264962946965</v>
+        <v>5616.714605931479</v>
       </c>
       <c r="J26">
-        <v>9913728.23980183</v>
+        <v>66612880.14448373</v>
       </c>
       <c r="K26">
-        <v>6194209.078436995</v>
+        <v>47668679.45532978</v>
       </c>
       <c r="L26">
-        <v>14079404.95207561</v>
+        <v>85397123.89825705</v>
       </c>
       <c r="M26">
-        <v>71142235.47230634</v>
+        <v>478022908.2436615</v>
       </c>
       <c r="N26">
-        <v>34887603.8451137</v>
+        <v>268483995.8739165</v>
       </c>
       <c r="O26">
-        <v>123161524.0071946</v>
+        <v>747023042.5888867</v>
       </c>
     </row>
     <row r="27">
@@ -1773,40 +1773,40 @@
         </is>
       </c>
       <c r="D27">
-        <v>174.9568389131374</v>
+        <v>1177.025733754077</v>
       </c>
       <c r="E27">
-        <v>109.887914849103</v>
+        <v>846.2550111360468</v>
       </c>
       <c r="F27">
-        <v>247.9270366353384</v>
+        <v>1505.357230315761</v>
       </c>
       <c r="G27">
-        <v>526.3357147034422</v>
+        <v>3540.934350713615</v>
       </c>
       <c r="H27">
-        <v>259.4637157210539</v>
+        <v>1998.149386476524</v>
       </c>
       <c r="I27">
-        <v>909.1929557621427</v>
+        <v>5520.415232977536</v>
       </c>
       <c r="J27">
-        <v>9745445.84113957</v>
+        <v>65562687.42156967</v>
       </c>
       <c r="K27">
-        <v>6120976.632924738</v>
+        <v>47138096.6303</v>
       </c>
       <c r="L27">
-        <v>13810031.79466163</v>
+        <v>83851408.44304882</v>
       </c>
       <c r="M27">
-        <v>70002650.05555782</v>
+        <v>470944268.6449108</v>
       </c>
       <c r="N27">
-        <v>34508674.19090016</v>
+        <v>265753868.4013777</v>
       </c>
       <c r="O27">
-        <v>120922663.116365</v>
+        <v>734215225.9860123</v>
       </c>
     </row>
     <row r="28">
@@ -1826,40 +1826,40 @@
         </is>
       </c>
       <c r="D28">
-        <v>388.5160461216274</v>
+        <v>2442.165736753371</v>
       </c>
       <c r="E28">
-        <v>210.6330192143275</v>
+        <v>1508.873297620476</v>
       </c>
       <c r="F28">
-        <v>571.2030666257795</v>
+        <v>3329.051829954995</v>
       </c>
       <c r="G28">
-        <v>1174.159398368388</v>
+        <v>7380.626568212703</v>
       </c>
       <c r="H28">
-        <v>499.619447844318</v>
+        <v>3579.032606740024</v>
       </c>
       <c r="I28">
-        <v>2104.305956970938</v>
+        <v>12264.19115398205</v>
       </c>
       <c r="J28">
-        <v>21641120.80106686</v>
+        <v>136033515.868636</v>
       </c>
       <c r="K28">
-        <v>11732680.43627646</v>
+        <v>84047260.42405576</v>
       </c>
       <c r="L28">
-        <v>31817153.2171891</v>
+        <v>185434845.0321532</v>
       </c>
       <c r="M28">
-        <v>156163199.9829956</v>
+        <v>981623333.5722895</v>
       </c>
       <c r="N28">
-        <v>66449386.56329429</v>
+        <v>476011336.6964232</v>
       </c>
       <c r="O28">
-        <v>279872692.2771348</v>
+        <v>1631137423.479613</v>
       </c>
     </row>
     <row r="29">
@@ -1879,40 +1879,40 @@
         </is>
       </c>
       <c r="D29">
-        <v>792.2167811033304</v>
+        <v>5281.581303228867</v>
       </c>
       <c r="E29">
-        <v>479.2094093950568</v>
+        <v>3669.971042203785</v>
       </c>
       <c r="F29">
-        <v>1139.872610086353</v>
+        <v>6869.636232427654</v>
       </c>
       <c r="G29">
-        <v>1911.043148582584</v>
+        <v>12740.61595761741</v>
       </c>
       <c r="H29">
-        <v>907.2909438833487</v>
+        <v>6948.385039244115</v>
       </c>
       <c r="I29">
-        <v>3351.838069863777</v>
+        <v>20200.42243862863</v>
       </c>
       <c r="J29">
-        <v>44128059.14101771</v>
+        <v>294194641.7524543</v>
       </c>
       <c r="K29">
-        <v>26692922.52212348</v>
+        <v>204424726.9928345</v>
       </c>
       <c r="L29">
-        <v>63493184.12702997</v>
+        <v>382652477.4186854</v>
       </c>
       <c r="M29">
-        <v>254168738.7614837</v>
+        <v>1694501922.363115</v>
       </c>
       <c r="N29">
-        <v>120669695.5364854</v>
+        <v>924135210.2194673</v>
       </c>
       <c r="O29">
-        <v>445794463.2918823</v>
+        <v>2686656184.337608</v>
       </c>
     </row>
     <row r="30">
@@ -1932,40 +1932,40 @@
         </is>
       </c>
       <c r="D30">
-        <v>604.2117624746182</v>
+        <v>4098.044276638107</v>
       </c>
       <c r="E30">
-        <v>393.1530665230368</v>
+        <v>3040.585351954805</v>
       </c>
       <c r="F30">
-        <v>843.030180352562</v>
+        <v>5156.071269050872</v>
       </c>
       <c r="G30">
-        <v>1447.715592106308</v>
+        <v>9819.078284958432</v>
       </c>
       <c r="H30">
-        <v>739.3507663682607</v>
+        <v>5718.025119471314</v>
       </c>
       <c r="I30">
-        <v>2462.280097098285</v>
+        <v>15059.59331099487</v>
       </c>
       <c r="J30">
-        <v>33655803.59336124</v>
+        <v>228269262.2972952</v>
       </c>
       <c r="K30">
-        <v>21899412.11146619</v>
+        <v>169366685.2745869</v>
       </c>
       <c r="L30">
-        <v>46958467.10599848</v>
+        <v>287203481.8286714</v>
       </c>
       <c r="M30">
-        <v>192546173.7501389</v>
+        <v>1305937411.899472</v>
       </c>
       <c r="N30">
-        <v>98333651.92697868</v>
+        <v>760497340.8896847</v>
       </c>
       <c r="O30">
-        <v>327483252.9140719</v>
+        <v>2002925910.362318</v>
       </c>
     </row>
     <row r="31">
@@ -1985,40 +1985,40 @@
         </is>
       </c>
       <c r="D31">
-        <v>1205.884254737031</v>
+        <v>7695.570163788887</v>
       </c>
       <c r="E31">
-        <v>651.3997802736689</v>
+        <v>4773.426473964298</v>
       </c>
       <c r="F31">
-        <v>1790.149842915856</v>
+        <v>10500.68333202801</v>
       </c>
       <c r="G31">
-        <v>2893.283258155638</v>
+        <v>18464.01446025014</v>
       </c>
       <c r="H31">
-        <v>1226.669934433826</v>
+        <v>8988.978684307322</v>
       </c>
       <c r="I31">
-        <v>5235.702604451703</v>
+        <v>30711.64980271751</v>
       </c>
       <c r="J31">
-        <v>67170164.75736214</v>
+        <v>428658649.2633689</v>
       </c>
       <c r="K31">
-        <v>36284270.56080392</v>
+        <v>265889401.4527585</v>
       </c>
       <c r="L31">
-        <v>99714926.55009897</v>
+        <v>584909062.9606224</v>
       </c>
       <c r="M31">
-        <v>384806673.3346999</v>
+        <v>2455713923.213269</v>
       </c>
       <c r="N31">
-        <v>163147101.2796989</v>
+        <v>1195534165.012874</v>
       </c>
       <c r="O31">
-        <v>696348446.3920765</v>
+        <v>4084649423.761428</v>
       </c>
     </row>
     <row r="32">
@@ -2038,40 +2038,40 @@
         </is>
       </c>
       <c r="D32">
-        <v>1755.218209722901</v>
+        <v>11736.66461188222</v>
       </c>
       <c r="E32">
-        <v>1074.669614308349</v>
+        <v>8246.149493052824</v>
       </c>
       <c r="F32">
-        <v>2513.478354488385</v>
+        <v>15183.93132901223</v>
       </c>
       <c r="G32">
-        <v>3056.184568183188</v>
+        <v>20435.87120397931</v>
       </c>
       <c r="H32">
-        <v>1468.649683166577</v>
+        <v>11269.23538087623</v>
       </c>
       <c r="I32">
-        <v>5334.870331308373</v>
+        <v>32227.96990279203</v>
       </c>
       <c r="J32">
-        <v>97769164.71798509</v>
+        <v>653755692.2110626</v>
       </c>
       <c r="K32">
-        <v>59861246.85620371</v>
+        <v>459327019.0620284</v>
       </c>
       <c r="L32">
-        <v>140005771.3017119</v>
+        <v>845775342.888639</v>
       </c>
       <c r="M32">
-        <v>406472547.568364</v>
+        <v>2717970870.129249</v>
       </c>
       <c r="N32">
-        <v>195330407.8611547</v>
+        <v>1498808305.656538</v>
       </c>
       <c r="O32">
-        <v>709537754.0640136</v>
+        <v>4286319997.07134</v>
       </c>
     </row>
     <row r="33">
@@ -2091,40 +2091,40 @@
         </is>
       </c>
       <c r="D33">
-        <v>1132.669431595278</v>
+        <v>7828.946623487883</v>
       </c>
       <c r="E33">
-        <v>802.8378668444541</v>
+        <v>6256.755430393395</v>
       </c>
       <c r="F33">
-        <v>1514.890513782947</v>
+        <v>9443.924957166228</v>
       </c>
       <c r="G33">
-        <v>1960.689521002866</v>
+        <v>13552.17433876007</v>
       </c>
       <c r="H33">
-        <v>1090.757680811027</v>
+        <v>8500.600587615219</v>
       </c>
       <c r="I33">
-        <v>3196.591569181142</v>
+        <v>19927.75756623582</v>
       </c>
       <c r="J33">
-        <v>63091952.67872021</v>
+        <v>436087984.8215225</v>
       </c>
       <c r="K33">
-        <v>44719674.85896967</v>
+        <v>348513790.9837724</v>
       </c>
       <c r="L33">
-        <v>84382431.39873768</v>
+        <v>526045507.964071</v>
       </c>
       <c r="M33">
-        <v>260771706.2933812</v>
+        <v>1802439187.05509</v>
       </c>
       <c r="N33">
-        <v>145070771.5478666</v>
+        <v>1130579878.152824</v>
       </c>
       <c r="O33">
-        <v>425146678.7010919</v>
+        <v>2650391756.309364</v>
       </c>
     </row>
     <row r="34">
@@ -2144,40 +2144,40 @@
         </is>
       </c>
       <c r="D34">
-        <v>2390.930698406949</v>
+        <v>15417.65191711654</v>
       </c>
       <c r="E34">
-        <v>1304.35261358535</v>
+        <v>9687.908907780198</v>
       </c>
       <c r="F34">
-        <v>3552.101658835956</v>
+        <v>20958.38213787395</v>
       </c>
       <c r="G34">
-        <v>4141.047048075145</v>
+        <v>26703.08344870267</v>
       </c>
       <c r="H34">
-        <v>1773.098951580858</v>
+        <v>13169.46119360989</v>
       </c>
       <c r="I34">
-        <v>7499.439724545427</v>
+        <v>44248.76838082463</v>
       </c>
       <c r="J34">
-        <v>133179621.762664</v>
+        <v>858794047.0872285</v>
       </c>
       <c r="K34">
-        <v>72655049.28193112</v>
+        <v>539635901.9811721</v>
       </c>
       <c r="L34">
-        <v>197859166.6004801</v>
+        <v>1167423801.843851</v>
       </c>
       <c r="M34">
-        <v>550759257.3939942</v>
+        <v>3551510098.677454</v>
       </c>
       <c r="N34">
-        <v>235822160.5602542</v>
+        <v>1751538338.750115</v>
       </c>
       <c r="O34">
-        <v>997425483.3645419</v>
+        <v>5885086194.649675</v>
       </c>
     </row>
     <row r="35">
@@ -2197,40 +2197,40 @@
         </is>
       </c>
       <c r="D35">
-        <v>4200.625608565784</v>
+        <v>28225.07975070693</v>
       </c>
       <c r="E35">
-        <v>2624.598198610017</v>
+        <v>20198.07995569726</v>
       </c>
       <c r="F35">
-        <v>5965.698026461033</v>
+        <v>36184.30290480256</v>
       </c>
       <c r="G35">
-        <v>4647.574052847465</v>
+        <v>31228.24086522757</v>
       </c>
       <c r="H35">
-        <v>2279.134487693877</v>
+        <v>17539.50019344203</v>
       </c>
       <c r="I35">
-        <v>8045.885815716421</v>
+        <v>48801.45930987468</v>
       </c>
       <c r="J35">
-        <v>233983247.6483311</v>
+        <v>1572193392.273875</v>
       </c>
       <c r="K35">
-        <v>146195368.8589753</v>
+        <v>1125073449.692255</v>
       </c>
       <c r="L35">
-        <v>332301311.4699321</v>
+        <v>2015538040.403312</v>
       </c>
       <c r="M35">
-        <v>618127349.0287129</v>
+        <v>4153356035.075267</v>
       </c>
       <c r="N35">
-        <v>303124886.8632857</v>
+        <v>2332753525.727789</v>
       </c>
       <c r="O35">
-        <v>1070102813.490284</v>
+        <v>6490594088.213333</v>
       </c>
     </row>
     <row r="36">
@@ -2250,40 +2250,40 @@
         </is>
       </c>
       <c r="D36">
-        <v>3145.698222028302</v>
+        <v>21728.390963775</v>
       </c>
       <c r="E36">
-        <v>2222.851492998685</v>
+        <v>17319.45143228619</v>
       </c>
       <c r="F36">
-        <v>4214.109353940224</v>
+        <v>26251.92114817963</v>
       </c>
       <c r="G36">
-        <v>3567.291358720153</v>
+        <v>24640.47593032931</v>
       </c>
       <c r="H36">
-        <v>1978.457645783836</v>
+        <v>15415.2453346143</v>
       </c>
       <c r="I36">
-        <v>5825.424552914758</v>
+        <v>36289.65771255986</v>
       </c>
       <c r="J36">
-        <v>175221682.3634205</v>
+        <v>1210314833.464206</v>
       </c>
       <c r="K36">
-        <v>123817273.8630128</v>
+        <v>964728083.6812047</v>
       </c>
       <c r="L36">
-        <v>234734319.2331786</v>
+        <v>1462284511.795904</v>
       </c>
       <c r="M36">
-        <v>474449750.7097803</v>
+        <v>3277183298.733799</v>
       </c>
       <c r="N36">
-        <v>263134866.8892502</v>
+        <v>2050227629.503703</v>
       </c>
       <c r="O36">
-        <v>774781465.5376629</v>
+        <v>4826524475.770461</v>
       </c>
     </row>
     <row r="37">
@@ -2303,40 +2303,40 @@
         </is>
       </c>
       <c r="D37">
-        <v>4403.046671529946</v>
+        <v>29004.12003332089</v>
       </c>
       <c r="E37">
-        <v>2544.926898460312</v>
+        <v>19316.2226155926</v>
       </c>
       <c r="F37">
-        <v>6440.641899327791</v>
+        <v>38475.54315723289</v>
       </c>
       <c r="G37">
-        <v>4981.178497293667</v>
+        <v>32812.43870910444</v>
       </c>
       <c r="H37">
-        <v>2259.690248602242</v>
+        <v>17151.25094975893</v>
       </c>
       <c r="I37">
-        <v>8881.947966393045</v>
+        <v>53059.58282464386</v>
       </c>
       <c r="J37">
-        <v>245258505.6975613</v>
+        <v>1615587494.096039</v>
       </c>
       <c r="K37">
-        <v>141757518.0980366</v>
+        <v>1075952232.133734</v>
       </c>
       <c r="L37">
-        <v>358756635.0763565</v>
+        <v>2143164704.944192</v>
       </c>
       <c r="M37">
-        <v>662496740.1400577</v>
+        <v>4364054348.31089</v>
       </c>
       <c r="N37">
-        <v>300538803.0640982</v>
+        <v>2281116376.317938</v>
       </c>
       <c r="O37">
-        <v>1181299079.530275</v>
+        <v>7056924515.677633</v>
       </c>
     </row>
     <row r="38">
@@ -2356,40 +2356,40 @@
         </is>
       </c>
       <c r="D38">
-        <v>2935.310386286934</v>
+        <v>20397.88909256496</v>
       </c>
       <c r="E38">
-        <v>2132.667316913576</v>
+        <v>16648.87418708442</v>
       </c>
       <c r="F38">
-        <v>3872.99892108745</v>
+        <v>24289.98010266483</v>
       </c>
       <c r="G38">
-        <v>1588.149003285525</v>
+        <v>11036.27315967224</v>
       </c>
       <c r="H38">
-        <v>905.6389911888162</v>
+        <v>7069.958592998751</v>
       </c>
       <c r="I38">
-        <v>2554.376128700241</v>
+        <v>16020.07813713251</v>
       </c>
       <c r="J38">
-        <v>163502659.1369549</v>
+        <v>1136203218.234051</v>
       </c>
       <c r="K38">
-        <v>118793834.88672</v>
+        <v>927375589.9689797</v>
       </c>
       <c r="L38">
-        <v>215733785.9024132</v>
+        <v>1353000471.678632</v>
       </c>
       <c r="M38">
-        <v>211223817.4369749</v>
+        <v>1467824330.236408</v>
       </c>
       <c r="N38">
-        <v>120449985.8281126</v>
+        <v>940304492.8688338</v>
       </c>
       <c r="O38">
-        <v>339732025.1171321</v>
+        <v>2130670392.238623</v>
       </c>
     </row>
     <row r="39">
@@ -2409,40 +2409,40 @@
         </is>
       </c>
       <c r="D39">
-        <v>2584.99744319498</v>
+        <v>18122.83990797645</v>
       </c>
       <c r="E39">
-        <v>1956.483112457012</v>
+        <v>15310.66654102478</v>
       </c>
       <c r="F39">
-        <v>3330.661076694787</v>
+        <v>21108.82335271453</v>
       </c>
       <c r="G39">
-        <v>1405.18859287163</v>
+        <v>9851.463480618399</v>
       </c>
       <c r="H39">
-        <v>834.7287753484065</v>
+        <v>6532.258750502397</v>
       </c>
       <c r="I39">
-        <v>2207.01454507019</v>
+        <v>13987.45747345445</v>
       </c>
       <c r="J39">
-        <v>143989527.5808468</v>
+        <v>1009478428.554104</v>
       </c>
       <c r="K39">
-        <v>108980022.3300804</v>
+        <v>852834747.6681653</v>
       </c>
       <c r="L39">
-        <v>185524483.2940527</v>
+        <v>1175803678.392905</v>
       </c>
       <c r="M39">
-        <v>186890082.8519267</v>
+        <v>1310244642.922247</v>
       </c>
       <c r="N39">
-        <v>111018927.1213381</v>
+        <v>868790413.8168187</v>
       </c>
       <c r="O39">
-        <v>293532934.4943352</v>
+        <v>1860331843.969441</v>
       </c>
     </row>
     <row r="40">
@@ -2462,40 +2462,40 @@
         </is>
       </c>
       <c r="D40">
-        <v>3584.305208420943</v>
+        <v>24341.36693751122</v>
       </c>
       <c r="E40">
-        <v>2345.434171683544</v>
+        <v>18150.24257095082</v>
       </c>
       <c r="F40">
-        <v>4988.153768682373</v>
+        <v>30544.4039922673</v>
       </c>
       <c r="G40">
-        <v>2011.850735461718</v>
+        <v>13662.67494752479</v>
       </c>
       <c r="H40">
-        <v>1033.258067407192</v>
+        <v>7995.911711464024</v>
       </c>
       <c r="I40">
-        <v>3412.957353263679</v>
+        <v>20898.86419720421</v>
       </c>
       <c r="J40">
-        <v>199652968.7194633</v>
+        <v>1355862821.15325</v>
       </c>
       <c r="K40">
-        <v>130645374.2311167</v>
+        <v>1011004811.687102</v>
       </c>
       <c r="L40">
-        <v>277850141.2231459</v>
+        <v>1701384391.177274</v>
       </c>
       <c r="M40">
-        <v>267576147.8164085</v>
+        <v>1817135768.020797</v>
       </c>
       <c r="N40">
-        <v>137423322.9651565</v>
+        <v>1063456257.624715</v>
       </c>
       <c r="O40">
-        <v>453923327.9840693</v>
+        <v>2779548938.228159</v>
       </c>
     </row>
     <row r="41">
@@ -2515,40 +2515,40 @@
         </is>
       </c>
       <c r="D41">
-        <v>1765.412999126128</v>
+        <v>12334.77388925859</v>
       </c>
       <c r="E41">
-        <v>1315.229777784805</v>
+        <v>10283.33765710603</v>
       </c>
       <c r="F41">
-        <v>2296.143442023591</v>
+        <v>14492.18667019369</v>
       </c>
       <c r="G41">
-        <v>134.1376454167832</v>
+        <v>937.2070598055884</v>
       </c>
       <c r="H41">
-        <v>78.43335192755967</v>
+        <v>613.2439023758853</v>
       </c>
       <c r="I41">
-        <v>212.6687261859293</v>
+        <v>1342.265828167335</v>
       </c>
       <c r="J41">
-        <v>98337034.87732355</v>
+        <v>687071575.1794808</v>
       </c>
       <c r="K41">
-        <v>73260929.08216923</v>
+        <v>572802474.1761196</v>
       </c>
       <c r="L41">
-        <v>127899782.007598</v>
+        <v>807243781.9031283</v>
       </c>
       <c r="M41">
-        <v>17840306.84043217</v>
+        <v>124648538.9541433</v>
       </c>
       <c r="N41">
-        <v>10431635.80636544</v>
+        <v>81561439.01599275</v>
       </c>
       <c r="O41">
-        <v>28284940.58272859</v>
+        <v>178521355.1462556</v>
       </c>
     </row>
     <row r="42">
@@ -2568,40 +2568,40 @@
         </is>
       </c>
       <c r="D42">
-        <v>1404.611622313837</v>
+        <v>10032.89566330082</v>
       </c>
       <c r="E42">
-        <v>1158.870362535014</v>
+        <v>9103.99523218301</v>
       </c>
       <c r="F42">
-        <v>1710.488659429885</v>
+        <v>11113.56137655242</v>
       </c>
       <c r="G42">
-        <v>105.9826592872361</v>
+        <v>757.0156375300299</v>
       </c>
       <c r="H42">
-        <v>68.62908280537954</v>
+        <v>539.1447247667365</v>
       </c>
       <c r="I42">
-        <v>157.3254598773042</v>
+        <v>1022.19102406883</v>
       </c>
       <c r="J42">
-        <v>78239676.58612531</v>
+        <v>558852354.2371812</v>
       </c>
       <c r="K42">
-        <v>64551396.93392535</v>
+        <v>507110742.4230583</v>
       </c>
       <c r="L42">
-        <v>95277639.30756336</v>
+        <v>619047595.7967232</v>
       </c>
       <c r="M42">
-        <v>14095693.6852024</v>
+        <v>100683079.791494</v>
       </c>
       <c r="N42">
-        <v>9127668.013115479</v>
+        <v>71706248.39397596</v>
       </c>
       <c r="O42">
-        <v>20924286.16368145</v>
+        <v>135951406.2011544</v>
       </c>
     </row>
     <row r="43">
@@ -2621,40 +2621,40 @@
         </is>
       </c>
       <c r="D43">
-        <v>1879.473172314717</v>
+        <v>13051.92734702013</v>
       </c>
       <c r="E43">
-        <v>1361.299476280961</v>
+        <v>10624.94705555377</v>
       </c>
       <c r="F43">
-        <v>2484.188118681925</v>
+        <v>15567.90894700989</v>
       </c>
       <c r="G43">
-        <v>148.7896140775257</v>
+        <v>1033.263608939582</v>
       </c>
       <c r="H43">
-        <v>84.58336280820055</v>
+        <v>660.1734352187062</v>
       </c>
       <c r="I43">
-        <v>239.7293581172962</v>
+        <v>1502.335829975463</v>
       </c>
       <c r="J43">
-        <v>104690414.6442744</v>
+        <v>727018457.0837166</v>
       </c>
       <c r="K43">
-        <v>75827103.42780209</v>
+        <v>591830800.888456</v>
       </c>
       <c r="L43">
-        <v>138374246.5868205</v>
+        <v>867163664.1663475</v>
       </c>
       <c r="M43">
-        <v>19789018.67231091</v>
+        <v>137424059.9889644</v>
       </c>
       <c r="N43">
-        <v>11249587.25349067</v>
+        <v>87803066.88408794</v>
       </c>
       <c r="O43">
-        <v>31884004.62960039</v>
+        <v>199810665.3867366</v>
       </c>
     </row>
     <row r="44">
@@ -2674,40 +2674,40 @@
         </is>
       </c>
       <c r="D44">
-        <v>415.7631793452108</v>
+        <v>14240.29420280448</v>
       </c>
       <c r="E44">
-        <v>90.61667088159106</v>
+        <v>9938.56732738868</v>
       </c>
       <c r="F44">
-        <v>838.6026756738304</v>
+        <v>18482.88833734187</v>
       </c>
       <c r="G44">
-        <v>1394.524053625258</v>
+        <v>47763.80830016361</v>
       </c>
       <c r="H44">
-        <v>240.4646212187864</v>
+        <v>26373.44546635108</v>
       </c>
       <c r="I44">
-        <v>3247.947240199149</v>
+        <v>71585.0877985124</v>
       </c>
       <c r="J44">
-        <v>6156205.396564541</v>
+        <v>210856036.2609259</v>
       </c>
       <c r="K44">
-        <v>1341761.045743719</v>
+        <v>147160366.4166442</v>
       </c>
       <c r="L44">
-        <v>12417189.81870241</v>
+        <v>273676127.6110214</v>
       </c>
       <c r="M44">
-        <v>185471699.1321593</v>
+        <v>6352586503.921761</v>
       </c>
       <c r="N44">
-        <v>31981794.62209859</v>
+        <v>3507668247.024694</v>
       </c>
       <c r="O44">
-        <v>431976982.9464868</v>
+        <v>9520816677.202148</v>
       </c>
     </row>
     <row r="45">
@@ -2727,40 +2727,40 @@
         </is>
       </c>
       <c r="D45">
-        <v>248.365211849006</v>
+        <v>9177.08535583585</v>
       </c>
       <c r="E45">
-        <v>54.13184663442956</v>
+        <v>7163.895576587105</v>
       </c>
       <c r="F45">
-        <v>500.9576161335326</v>
+        <v>11224.78543343196</v>
       </c>
       <c r="G45">
-        <v>832.3653417998213</v>
+        <v>30755.86847315946</v>
       </c>
       <c r="H45">
-        <v>143.5288377502046</v>
+        <v>18994.83704694818</v>
       </c>
       <c r="I45">
-        <v>1938.638998522897</v>
+        <v>43438.418921058</v>
       </c>
       <c r="J45">
-        <v>3677543.691848233</v>
+        <v>135885102.8638608</v>
       </c>
       <c r="K45">
-        <v>801530.2531159978</v>
+        <v>106075801.8025251</v>
       </c>
       <c r="L45">
-        <v>7417679.422089224</v>
+        <v>166205397.9128274</v>
       </c>
       <c r="M45">
-        <v>110704590.4593762</v>
+        <v>4090530506.930209</v>
       </c>
       <c r="N45">
-        <v>19089335.42077721</v>
+        <v>2526313327.244108</v>
       </c>
       <c r="O45">
-        <v>257838986.8035453</v>
+        <v>5777309716.500714</v>
       </c>
     </row>
     <row r="46">
@@ -2780,40 +2780,40 @@
         </is>
       </c>
       <c r="D46">
-        <v>654.9995713225958</v>
+        <v>21610.8305366543</v>
       </c>
       <c r="E46">
-        <v>142.7588673811825</v>
+        <v>14339.97198280711</v>
       </c>
       <c r="F46">
-        <v>1321.147278942339</v>
+        <v>28714.70460146577</v>
       </c>
       <c r="G46">
-        <v>2192.688594533249</v>
+        <v>72344.81320412137</v>
       </c>
       <c r="H46">
-        <v>378.09604715278</v>
+        <v>37979.33412082843</v>
       </c>
       <c r="I46">
-        <v>5106.930103296875</v>
+        <v>110997.4577958491</v>
       </c>
       <c r="J46">
-        <v>9698578.652573671</v>
+        <v>319991567.7562401</v>
       </c>
       <c r="K46">
-        <v>2113830.549313169</v>
+        <v>212331965.1494246</v>
       </c>
       <c r="L46">
-        <v>19562227.75929919</v>
+        <v>425178631.0339045</v>
       </c>
       <c r="M46">
-        <v>291627583.0729222</v>
+        <v>9621860156.148142</v>
       </c>
       <c r="N46">
-        <v>50286774.27131974</v>
+        <v>5051251438.070182</v>
       </c>
       <c r="O46">
-        <v>679221703.7384844</v>
+        <v>14762661886.84793</v>
       </c>
     </row>
     <row r="47">
@@ -2833,40 +2833,40 @@
         </is>
       </c>
       <c r="D47">
-        <v>746.1845492332919</v>
+        <v>26005.2324467869</v>
       </c>
       <c r="E47">
-        <v>162.6328714853769</v>
+        <v>18609.54048193758</v>
       </c>
       <c r="F47">
-        <v>1505.069209156552</v>
+        <v>33338.47827093451</v>
       </c>
       <c r="G47">
-        <v>2047.59133026688</v>
+        <v>71360.48120311306</v>
       </c>
       <c r="H47">
-        <v>353.0762143281082</v>
+        <v>40401.3410311026</v>
       </c>
       <c r="I47">
-        <v>4768.988095190759</v>
+        <v>105636.8737188913</v>
       </c>
       <c r="J47">
-        <v>11048754.62049736</v>
+        <v>385059476.839573</v>
       </c>
       <c r="K47">
-        <v>2408104.928083976</v>
+        <v>275551465.9160499</v>
       </c>
       <c r="L47">
-        <v>22285559.77998104</v>
+        <v>493642847.7577259</v>
       </c>
       <c r="M47">
-        <v>272329646.925495</v>
+        <v>9490944000.014036</v>
       </c>
       <c r="N47">
-        <v>46959136.50563839</v>
+        <v>5373378357.136646</v>
       </c>
       <c r="O47">
-        <v>634275416.6603709</v>
+        <v>14049704204.61255</v>
       </c>
     </row>
     <row r="48">
@@ -2886,40 +2886,40 @@
         </is>
       </c>
       <c r="D48">
-        <v>753.8125070842248</v>
+        <v>26355.61666064602</v>
       </c>
       <c r="E48">
-        <v>164.2954048226606</v>
+        <v>18949.09519056652</v>
       </c>
       <c r="F48">
-        <v>1520.454953208712</v>
+        <v>33707.51969287326</v>
       </c>
       <c r="G48">
-        <v>2077.852995048254</v>
+        <v>72648.16715033396</v>
       </c>
       <c r="H48">
-        <v>358.2943815875295</v>
+        <v>41324.06715985542</v>
       </c>
       <c r="I48">
-        <v>4839.469698111096</v>
+        <v>107287.9665444129</v>
       </c>
       <c r="J48">
-        <v>11161701.79239611</v>
+        <v>390247615.8941859</v>
       </c>
       <c r="K48">
-        <v>2432722.059209138</v>
+        <v>280579252.4867178</v>
       </c>
       <c r="L48">
-        <v>22513376.49216139</v>
+        <v>499107244.0923737</v>
       </c>
       <c r="M48">
-        <v>276354448.3414178</v>
+        <v>9662206230.994417</v>
       </c>
       <c r="N48">
-        <v>47653152.75114143</v>
+        <v>5496100932.260771</v>
       </c>
       <c r="O48">
-        <v>643649469.8487759</v>
+        <v>14269299550.40691</v>
       </c>
     </row>
     <row r="49">
@@ -2939,40 +2939,40 @@
         </is>
       </c>
       <c r="D49">
-        <v>1776.005053872611</v>
+        <v>52318.38484635207</v>
       </c>
       <c r="E49">
-        <v>244.6663584106245</v>
+        <v>32324.51126525025</v>
       </c>
       <c r="F49">
-        <v>3626.258263185735</v>
+        <v>71318.09778175905</v>
       </c>
       <c r="G49">
-        <v>4927.644067524714</v>
+        <v>145160.8361972002</v>
       </c>
       <c r="H49">
-        <v>537.0719770264043</v>
+        <v>70956.17593042296</v>
       </c>
       <c r="I49">
-        <v>11617.87239247016</v>
+        <v>228490.2230251733</v>
       </c>
       <c r="J49">
-        <v>26297306.83269177</v>
+        <v>774678324.4199361</v>
       </c>
       <c r="K49">
-        <v>3622774.76898612</v>
+        <v>478629038.3045618</v>
       </c>
       <c r="L49">
-        <v>53694006.10299103</v>
+        <v>1056007073.854506</v>
       </c>
       <c r="M49">
-        <v>655376660.9807869</v>
+        <v>19306391214.22763</v>
       </c>
       <c r="N49">
-        <v>71430572.94451177</v>
+        <v>9437171398.746254</v>
       </c>
       <c r="O49">
-        <v>1545177028.198532</v>
+        <v>30389199662.34805</v>
       </c>
     </row>
     <row r="50">
@@ -2992,40 +2992,40 @@
         </is>
       </c>
       <c r="D50">
-        <v>1565.680789785276</v>
+        <v>53460.10711351698</v>
       </c>
       <c r="E50">
-        <v>341.2442175784907</v>
+        <v>37147.40600504915</v>
       </c>
       <c r="F50">
-        <v>3158.009570815964</v>
+        <v>69534.38141564993</v>
       </c>
       <c r="G50">
-        <v>3497.648624255389</v>
+        <v>119427.0705229659</v>
       </c>
       <c r="H50">
-        <v>603.1167045140086</v>
+        <v>65654.50764262657</v>
       </c>
       <c r="I50">
-        <v>8146.276263076486</v>
+        <v>179368.1330255301</v>
       </c>
       <c r="J50">
-        <v>23183035.45435058</v>
+        <v>791583806.0298457</v>
       </c>
       <c r="K50">
-        <v>5052803.129684715</v>
+        <v>550041640.7167641</v>
       </c>
       <c r="L50">
-        <v>46760647.71507194</v>
+        <v>1029595585.621526</v>
       </c>
       <c r="M50">
-        <v>465187267.0259668</v>
+        <v>15883800379.55446</v>
       </c>
       <c r="N50">
-        <v>80214521.70036314</v>
+        <v>8732049516.469334</v>
       </c>
       <c r="O50">
-        <v>1083454742.989172</v>
+        <v>23855961692.3955</v>
       </c>
     </row>
     <row r="51">
@@ -3045,40 +3045,40 @@
         </is>
       </c>
       <c r="D51">
-        <v>1123.06755299157</v>
+        <v>40110.47961529465</v>
       </c>
       <c r="E51">
-        <v>244.7755065455924</v>
+        <v>29760.37557070962</v>
       </c>
       <c r="F51">
-        <v>2265.249790480363</v>
+        <v>50466.14374355517</v>
       </c>
       <c r="G51">
-        <v>2496.069326314544</v>
+        <v>89147.38705148341</v>
       </c>
       <c r="H51">
-        <v>430.4094744925389</v>
+        <v>52330.18528225931</v>
       </c>
       <c r="I51">
-        <v>5813.525739246659</v>
+        <v>129516.0590441841</v>
       </c>
       <c r="J51">
-        <v>16629261.25714616</v>
+        <v>593915871.6636686</v>
       </c>
       <c r="K51">
-        <v>3624390.92542059</v>
+        <v>440661881.0754976</v>
       </c>
       <c r="L51">
-        <v>33541553.64764274</v>
+        <v>747252190.4108212</v>
       </c>
       <c r="M51">
-        <v>331977220.3998344</v>
+        <v>11856602477.84729</v>
       </c>
       <c r="N51">
-        <v>57244460.10750768</v>
+        <v>6959914642.540487</v>
       </c>
       <c r="O51">
-        <v>773198923.3198056</v>
+        <v>17225635852.87649</v>
       </c>
     </row>
     <row r="52">
@@ -3098,40 +3098,40 @@
         </is>
       </c>
       <c r="D52">
-        <v>2426.364145698882</v>
+        <v>74158.70054085051</v>
       </c>
       <c r="E52">
-        <v>438.7725611118991</v>
+        <v>45999.33427963169</v>
       </c>
       <c r="F52">
-        <v>4921.861939029323</v>
+        <v>101190.2970306698</v>
       </c>
       <c r="G52">
-        <v>5393.084295118209</v>
+        <v>164832.6876005811</v>
       </c>
       <c r="H52">
-        <v>771.585026471576</v>
+        <v>80890.19392617137</v>
       </c>
       <c r="I52">
-        <v>12632.32799297079</v>
+        <v>259712.4904421164</v>
       </c>
       <c r="J52">
-        <v>35927173.90536334</v>
+        <v>1098067878.908372</v>
       </c>
       <c r="K52">
-        <v>6496905.312383899</v>
+        <v>681112142.6785071</v>
       </c>
       <c r="L52">
-        <v>72878009.73120718</v>
+        <v>1498324728.133137</v>
       </c>
       <c r="M52">
-        <v>717280211.2507217</v>
+        <v>21922747450.87729</v>
       </c>
       <c r="N52">
-        <v>102620808.5207196</v>
+        <v>10758395792.18079</v>
       </c>
       <c r="O52">
-        <v>1680099623.065115</v>
+        <v>34541761228.80148</v>
       </c>
     </row>
     <row r="53">
@@ -3151,40 +3151,40 @@
         </is>
       </c>
       <c r="D53">
-        <v>1818.546735454858</v>
+        <v>62579.4093579967</v>
       </c>
       <c r="E53">
-        <v>396.3570109047056</v>
+        <v>43968.12738693651</v>
       </c>
       <c r="F53">
-        <v>3668.045257379818</v>
+        <v>80960.0926433546</v>
       </c>
       <c r="G53">
-        <v>2940.211187452242</v>
+        <v>101177.8668709955</v>
       </c>
       <c r="H53">
-        <v>506.995033650336</v>
+        <v>56241.27140630187</v>
       </c>
       <c r="I53">
-        <v>6847.964211920572</v>
+        <v>151146.3949088496</v>
       </c>
       <c r="J53">
-        <v>26927221.5118801</v>
+        <v>926613314.3638556</v>
       </c>
       <c r="K53">
-        <v>5868858.26046598</v>
+        <v>651036062.2183704</v>
       </c>
       <c r="L53">
-        <v>54312746.12602305</v>
+        <v>1198776091.770147</v>
       </c>
       <c r="M53">
-        <v>391048087.9311482</v>
+        <v>13456656293.8424</v>
       </c>
       <c r="N53">
-        <v>67430339.47549468</v>
+        <v>7480089097.038149</v>
       </c>
       <c r="O53">
-        <v>910779240.185436</v>
+        <v>20102470522.877</v>
       </c>
     </row>
     <row r="54">
@@ -3204,40 +3204,40 @@
         </is>
       </c>
       <c r="D54">
-        <v>1087.413598272012</v>
+        <v>40817.65262655971</v>
       </c>
       <c r="E54">
-        <v>237.0046339889163</v>
+        <v>32620.74478333336</v>
       </c>
       <c r="F54">
-        <v>2193.335048359</v>
+        <v>49237.63909392608</v>
       </c>
       <c r="G54">
-        <v>1753.907645771968</v>
+        <v>65835.47707877676</v>
       </c>
       <c r="H54">
-        <v>302.4348964056068</v>
+        <v>41626.40790256684</v>
       </c>
       <c r="I54">
-        <v>4084.977582738828</v>
+        <v>91702.65713674568</v>
       </c>
       <c r="J54">
-        <v>16101333.14961367</v>
+        <v>604386982.4414687</v>
       </c>
       <c r="K54">
-        <v>3509327.615473886</v>
+        <v>483015368.0068171</v>
       </c>
       <c r="L54">
-        <v>32476712.06105168</v>
+        <v>729061722.0637653</v>
       </c>
       <c r="M54">
-        <v>233269716.8876717</v>
+        <v>8756118451.47731</v>
       </c>
       <c r="N54">
-        <v>40223841.22194571</v>
+        <v>5536312251.041389</v>
       </c>
       <c r="O54">
-        <v>543302018.5042642</v>
+        <v>12196453399.18718</v>
       </c>
     </row>
     <row r="55">
@@ -3257,40 +3257,40 @@
         </is>
       </c>
       <c r="D55">
-        <v>2574.976689559453</v>
+        <v>80578.09124301765</v>
       </c>
       <c r="E55">
-        <v>548.0701152644502</v>
+        <v>50632.43171669338</v>
       </c>
       <c r="F55">
-        <v>5197.845071581039</v>
+        <v>109535.9032160241</v>
       </c>
       <c r="G55">
-        <v>4148.983676590965</v>
+        <v>129833.0919319252</v>
       </c>
       <c r="H55">
-        <v>698.6628444005972</v>
+        <v>64544.65911726523</v>
       </c>
       <c r="I55">
-        <v>9670.846552488703</v>
+        <v>203796.938423986</v>
       </c>
       <c r="J55">
-        <v>38127679.84230685</v>
+        <v>1193119797.035362</v>
       </c>
       <c r="K55">
-        <v>8115274.196720711</v>
+        <v>749714416.4290801</v>
       </c>
       <c r="L55">
-        <v>76964491.97490044</v>
+        <v>1621898118.919663</v>
       </c>
       <c r="M55">
-        <v>551814828.9865984</v>
+        <v>17267801226.94606</v>
       </c>
       <c r="N55">
-        <v>92922158.30527943</v>
+        <v>8584439662.596275</v>
       </c>
       <c r="O55">
-        <v>1286222591.480998</v>
+        <v>27104992810.39014</v>
       </c>
     </row>
     <row r="56">
@@ -3310,40 +3310,40 @@
         </is>
       </c>
       <c r="D56">
-        <v>2112.976538808103</v>
+        <v>73639.21713840304</v>
       </c>
       <c r="E56">
-        <v>460.528755574859</v>
+        <v>52696.77920393395</v>
       </c>
       <c r="F56">
-        <v>4261.916078935035</v>
+        <v>94404.82585498344</v>
       </c>
       <c r="G56">
-        <v>2181.732598962326</v>
+        <v>76035.43041871449</v>
       </c>
       <c r="H56">
-        <v>376.2068511090249</v>
+        <v>43048.10313777904</v>
       </c>
       <c r="I56">
-        <v>5081.412798316928</v>
+        <v>112557.3290129786</v>
       </c>
       <c r="J56">
-        <v>31286843.61013157</v>
+        <v>1090375888.168334</v>
       </c>
       <c r="K56">
-        <v>6819049.283796935</v>
+        <v>780281209.6726511</v>
       </c>
       <c r="L56">
-        <v>63106191.38079111</v>
+        <v>1397852256.434746</v>
       </c>
       <c r="M56">
-        <v>290170435.6619893</v>
+        <v>10112712245.68903</v>
       </c>
       <c r="N56">
-        <v>50035511.19750031</v>
+        <v>5725397717.324612</v>
       </c>
       <c r="O56">
-        <v>675827902.1761515</v>
+        <v>14970124758.72616</v>
       </c>
     </row>
     <row r="57">
@@ -3363,40 +3363,40 @@
         </is>
       </c>
       <c r="D57">
-        <v>1557.619498506581</v>
+        <v>58364.54111235461</v>
       </c>
       <c r="E57">
-        <v>339.4872380887841</v>
+        <v>46521.70686952129</v>
       </c>
       <c r="F57">
-        <v>3141.7497845445</v>
+        <v>70515.17683410758</v>
       </c>
       <c r="G57">
-        <v>1645.239646924223</v>
+        <v>61647.69836577576</v>
       </c>
       <c r="H57">
-        <v>283.6967404637321</v>
+        <v>38876.44399828889</v>
       </c>
       <c r="I57">
-        <v>3831.881964891329</v>
+        <v>86004.88673254254</v>
       </c>
       <c r="J57">
-        <v>23063671.91438695</v>
+        <v>864203760.2506384</v>
       </c>
       <c r="K57">
-        <v>5026787.534380618</v>
+        <v>688846913.6169974</v>
       </c>
       <c r="L57">
-        <v>46519889.05975042</v>
+        <v>1044118223.382631</v>
       </c>
       <c r="M57">
-        <v>218816873.0409216</v>
+        <v>8199143882.648176</v>
       </c>
       <c r="N57">
-        <v>37731666.48167637</v>
+        <v>5170567051.772422</v>
       </c>
       <c r="O57">
-        <v>509640301.3305467</v>
+        <v>11438649935.42816</v>
       </c>
     </row>
     <row r="58">
@@ -3416,40 +3416,40 @@
         </is>
       </c>
       <c r="D58">
-        <v>2346.249943076887</v>
+        <v>77634.62240675329</v>
       </c>
       <c r="E58">
-        <v>511.3713033284636</v>
+        <v>51703.26310067382</v>
       </c>
       <c r="F58">
-        <v>4732.433216338684</v>
+        <v>102986.5502375148</v>
       </c>
       <c r="G58">
-        <v>2462.55598636275</v>
+        <v>81483.05116463738</v>
       </c>
       <c r="H58">
-        <v>424.6306049374815</v>
+        <v>42933.16372033292</v>
       </c>
       <c r="I58">
-        <v>5735.470750002643</v>
+        <v>124814.5128581302</v>
       </c>
       <c r="J58">
-        <v>34740922.90713947</v>
+        <v>1149535853.976794</v>
       </c>
       <c r="K58">
-        <v>7571874.888384562</v>
+        <v>765570216.7316774</v>
       </c>
       <c r="L58">
-        <v>70073138.63432689</v>
+        <v>1524921849.36688</v>
       </c>
       <c r="M58">
-        <v>327519946.1862458</v>
+        <v>10837245804.89677</v>
       </c>
       <c r="N58">
-        <v>56475870.45668504</v>
+        <v>5710110774.804277</v>
       </c>
       <c r="O58">
-        <v>762817609.7503515</v>
+        <v>16600330210.13132</v>
       </c>
     </row>
     <row r="59">
@@ -3469,40 +3469,40 @@
         </is>
       </c>
       <c r="D59">
-        <v>835.2436047477086</v>
+        <v>31800.92859225367</v>
       </c>
       <c r="E59">
-        <v>182.0435252505413</v>
+        <v>25956.10049462783</v>
       </c>
       <c r="F59">
-        <v>1684.703111237536</v>
+        <v>37868.816682294</v>
       </c>
       <c r="G59">
-        <v>407.091252346968</v>
+        <v>15499.52585428946</v>
       </c>
       <c r="H59">
-        <v>70.19674099031242</v>
+        <v>10008.78037838642</v>
       </c>
       <c r="I59">
-        <v>948.1449288251999</v>
+        <v>21312.43556115562</v>
       </c>
       <c r="J59">
-        <v>12367452.05549933</v>
+        <v>470876349.6654986</v>
       </c>
       <c r="K59">
-        <v>2695518.478384761</v>
+        <v>384331980.0239549</v>
       </c>
       <c r="L59">
-        <v>24945398.96809415</v>
+        <v>560723568.6147256</v>
       </c>
       <c r="M59">
-        <v>54143136.56214675</v>
+        <v>2061436938.620498</v>
       </c>
       <c r="N59">
-        <v>9336166.551711552</v>
+        <v>1331167790.325394</v>
       </c>
       <c r="O59">
-        <v>126103275.5337516</v>
+        <v>2834553929.633698</v>
       </c>
     </row>
     <row r="60">
@@ -3522,40 +3522,40 @@
         </is>
       </c>
       <c r="D60">
-        <v>718.6130424774171</v>
+        <v>28011.03732404898</v>
       </c>
       <c r="E60">
-        <v>156.6235895731507</v>
+        <v>23664.48382893649</v>
       </c>
       <c r="F60">
-        <v>1449.456926764802</v>
+        <v>32626.23528111622</v>
       </c>
       <c r="G60">
-        <v>348.4411779186865</v>
+        <v>13581.9951253148</v>
       </c>
       <c r="H60">
-        <v>60.08342104062218</v>
+        <v>9078.090659765629</v>
       </c>
       <c r="I60">
-        <v>811.5446694882552</v>
+        <v>18267.28814008835</v>
       </c>
       <c r="J60">
-        <v>10640503.31996315</v>
+        <v>414759429.6571933</v>
       </c>
       <c r="K60">
-        <v>2319125.490809646</v>
+        <v>350400012.0550625</v>
       </c>
       <c r="L60">
-        <v>21462108.71460643</v>
+        <v>483096665.8074898</v>
       </c>
       <c r="M60">
-        <v>46342676.66318531</v>
+        <v>1806405351.666868</v>
       </c>
       <c r="N60">
-        <v>7991094.99840275</v>
+        <v>1207386057.748829</v>
       </c>
       <c r="O60">
-        <v>107935441.0419379</v>
+        <v>2429549322.63175</v>
       </c>
     </row>
     <row r="61">
@@ -3575,40 +3575,40 @@
         </is>
       </c>
       <c r="D61">
-        <v>1056.21548430027</v>
+        <v>37848.78958717459</v>
       </c>
       <c r="E61">
-        <v>230.2049235615637</v>
+        <v>28222.10904538181</v>
       </c>
       <c r="F61">
-        <v>2130.407826439325</v>
+        <v>47493.99336269069</v>
       </c>
       <c r="G61">
-        <v>531.0503557029517</v>
+        <v>19029.84142152672</v>
       </c>
       <c r="H61">
-        <v>91.57161706909251</v>
+        <v>11226.27666864277</v>
       </c>
       <c r="I61">
-        <v>1236.854633470289</v>
+        <v>27573.67158701822</v>
       </c>
       <c r="J61">
-        <v>15639382.67603411</v>
+        <v>560427027.4172918</v>
       </c>
       <c r="K61">
-        <v>3408644.303176075</v>
+        <v>417884768.6349679</v>
       </c>
       <c r="L61">
-        <v>31544948.68608713</v>
+        <v>703243559.7213621</v>
       </c>
       <c r="M61">
-        <v>70629697.30849259</v>
+        <v>2530968909.063054</v>
       </c>
       <c r="N61">
-        <v>12179025.0701893</v>
+        <v>1493094796.929489</v>
       </c>
       <c r="O61">
-        <v>164501666.2515484</v>
+        <v>3667298321.073423</v>
       </c>
     </row>
     <row r="62">
@@ -3628,40 +3628,40 @@
         </is>
       </c>
       <c r="D62">
-        <v>313.5745094393058</v>
+        <v>12112.23142500211</v>
       </c>
       <c r="E62">
-        <v>68.34438336619475</v>
+        <v>10097.80695151388</v>
       </c>
       <c r="F62">
-        <v>632.4860778990954</v>
+        <v>14230.72043149285</v>
       </c>
       <c r="G62">
-        <v>20.17442418765819</v>
+        <v>779.2638982805222</v>
       </c>
       <c r="H62">
-        <v>3.47877489669736</v>
+        <v>513.9851382725034</v>
       </c>
       <c r="I62">
-        <v>46.98769102803838</v>
+        <v>1057.206977523472</v>
       </c>
       <c r="J62">
-        <v>4643097.761267804</v>
+        <v>179345810.7100062</v>
       </c>
       <c r="K62">
-        <v>1011975.284503244</v>
+        <v>149518227.531066</v>
       </c>
       <c r="L62">
-        <v>9365221.355451906</v>
+        <v>210714277.4291147</v>
       </c>
       <c r="M62">
-        <v>2683198.416958539</v>
+        <v>103642098.4713095</v>
       </c>
       <c r="N62">
-        <v>462677.0612607489</v>
+        <v>68360023.39024295</v>
       </c>
       <c r="O62">
-        <v>6249362.906729105</v>
+        <v>140608528.0106218</v>
       </c>
     </row>
     <row r="63">
@@ -3681,40 +3681,40 @@
         </is>
       </c>
       <c r="D63">
-        <v>236.390661277424</v>
+        <v>9689.033554962107</v>
       </c>
       <c r="E63">
-        <v>51.52196206069619</v>
+        <v>8791.969761182141</v>
       </c>
       <c r="F63">
-        <v>476.8047073426706</v>
+        <v>10732.66110863959</v>
       </c>
       <c r="G63">
-        <v>15.37990590101244</v>
+        <v>630.3820275378226</v>
       </c>
       <c r="H63">
-        <v>2.652032596535927</v>
+        <v>452.5563364016448</v>
       </c>
       <c r="I63">
-        <v>35.82091165502322</v>
+        <v>806.3127302968967</v>
       </c>
       <c r="J63">
-        <v>3500236.521534819</v>
+        <v>143465519.8483239</v>
       </c>
       <c r="K63">
-        <v>762885.6922327289</v>
+        <v>130182696.2538242</v>
       </c>
       <c r="L63">
-        <v>7060047.301622916</v>
+        <v>158918513.0356258</v>
       </c>
       <c r="M63">
-        <v>2045527.484834654</v>
+        <v>83840809.66253041</v>
       </c>
       <c r="N63">
-        <v>352720.3353392783</v>
+        <v>60189992.74141876</v>
       </c>
       <c r="O63">
-        <v>4764181.250118088</v>
+        <v>107239593.1294873</v>
       </c>
     </row>
     <row r="64">
@@ -3734,40 +3734,40 @@
         </is>
       </c>
       <c r="D64">
-        <v>335.1415856107587</v>
+        <v>12737.33674257351</v>
       </c>
       <c r="E64">
-        <v>73.04498394940379</v>
+        <v>10368.85395699826</v>
       </c>
       <c r="F64">
-        <v>675.9873033138297</v>
+        <v>15192.67563813556</v>
       </c>
       <c r="G64">
-        <v>22.60428428871962</v>
+        <v>859.0947622497689</v>
       </c>
       <c r="H64">
-        <v>3.897767589793943</v>
+        <v>553.2944318926683</v>
       </c>
       <c r="I64">
-        <v>52.64701069971866</v>
+        <v>1183.230739626694</v>
       </c>
       <c r="J64">
-        <v>4962441.458138504</v>
+        <v>188601745.1472858</v>
       </c>
       <c r="K64">
-        <v>1081577.077338822</v>
+        <v>153531620.5412729</v>
       </c>
       <c r="L64">
-        <v>10009344.00016788</v>
+        <v>224957948.1738726</v>
       </c>
       <c r="M64">
-        <v>3006369.81039971</v>
+        <v>114259603.3792193</v>
       </c>
       <c r="N64">
-        <v>518403.0894425944</v>
+        <v>73588159.44172488</v>
       </c>
       <c r="O64">
-        <v>7002052.423062582</v>
+        <v>157369688.3703502</v>
       </c>
     </row>
     <row r="65">
@@ -3787,40 +3787,40 @@
         </is>
       </c>
       <c r="D65">
-        <v>93.4597350949351</v>
+        <v>1453.525328788733</v>
       </c>
       <c r="E65">
-        <v>-7.411104959875187</v>
+        <v>1014.442478259093</v>
       </c>
       <c r="F65">
-        <v>188.355418076562</v>
+        <v>1886.57242363781</v>
       </c>
       <c r="G65">
-        <v>372.9669568139454</v>
+        <v>5800.539857936122</v>
       </c>
       <c r="H65">
-        <v>-22.00960974391572</v>
+        <v>3012.706360929666</v>
       </c>
       <c r="I65">
-        <v>954.3250788402071</v>
+        <v>9558.543074105213</v>
       </c>
       <c r="J65">
-        <v>7028265.538874211</v>
+        <v>109306558.2502416</v>
       </c>
       <c r="K65">
-        <v>-557322.5040875734</v>
+        <v>76287088.80756183</v>
       </c>
       <c r="L65">
-        <v>14164515.79477554</v>
+        <v>141872132.829987</v>
       </c>
       <c r="M65">
-        <v>49604605.25625475</v>
+        <v>771471801.1055042</v>
       </c>
       <c r="N65">
-        <v>-2927278.095940791</v>
+        <v>400689946.0036456</v>
       </c>
       <c r="O65">
-        <v>126925235.4857475</v>
+        <v>1271286228.855993</v>
       </c>
     </row>
     <row r="66">
@@ -3840,40 +3840,40 @@
         </is>
       </c>
       <c r="D66">
-        <v>55.59436772459278</v>
+        <v>932.7600199848479</v>
       </c>
       <c r="E66">
-        <v>-4.408483439059063</v>
+        <v>728.1391773192408</v>
       </c>
       <c r="F66">
-        <v>112.0429066574065</v>
+        <v>1140.888493377217</v>
       </c>
       <c r="G66">
-        <v>221.0483303452196</v>
+        <v>3708.739814289071</v>
       </c>
       <c r="H66">
-        <v>-13.04455367039288</v>
+        <v>2154.539244471756</v>
       </c>
       <c r="I66">
-        <v>565.6049723177761</v>
+        <v>5759.331170222137</v>
       </c>
       <c r="J66">
-        <v>4180752.0472571</v>
+        <v>70144486.26288052</v>
       </c>
       <c r="K66">
-        <v>-331522.3631006803</v>
+        <v>54756794.27358425</v>
       </c>
       <c r="L66">
-        <v>8425738.623543626</v>
+        <v>85795955.59045996</v>
       </c>
       <c r="M66">
-        <v>29399427.9359142</v>
+        <v>493262395.3004464</v>
       </c>
       <c r="N66">
-        <v>-1734925.638162253</v>
+        <v>286553719.5147435</v>
       </c>
       <c r="O66">
-        <v>75225461.31826422</v>
+        <v>765991045.6395442</v>
       </c>
     </row>
     <row r="67">
@@ -3893,40 +3893,40 @@
         </is>
       </c>
       <c r="D67">
-        <v>147.7938649011022</v>
+        <v>2214.175137070685</v>
       </c>
       <c r="E67">
-        <v>-11.71965493049052</v>
+        <v>1469.226709115509</v>
       </c>
       <c r="F67">
-        <v>297.858486163274</v>
+        <v>2942.014879486341</v>
       </c>
       <c r="G67">
-        <v>588.7707292148518</v>
+        <v>8820.674057985056</v>
       </c>
       <c r="H67">
-        <v>-34.74467038409552</v>
+        <v>4355.742385803443</v>
       </c>
       <c r="I67">
-        <v>1506.510596479091</v>
+        <v>14880.14207027089</v>
       </c>
       <c r="J67">
-        <v>11114246.43442777</v>
+        <v>166508184.4828523</v>
       </c>
       <c r="K67">
-        <v>-881329.7704278189</v>
+        <v>110487317.7521953</v>
       </c>
       <c r="L67">
-        <v>22399256.01796438</v>
+        <v>221242460.9522528</v>
       </c>
       <c r="M67">
-        <v>78306506.98557529</v>
+        <v>1173149649.712012</v>
       </c>
       <c r="N67">
-        <v>-4621041.161084704</v>
+        <v>579313737.3118578</v>
       </c>
       <c r="O67">
-        <v>200365909.3317192</v>
+        <v>1979058895.346028</v>
       </c>
     </row>
     <row r="68">
@@ -3946,40 +3946,40 @@
         </is>
       </c>
       <c r="D68">
-        <v>176.7691466145579</v>
+        <v>2797.345275965625</v>
       </c>
       <c r="E68">
-        <v>-14.01731663263693</v>
+        <v>2001.801378301898</v>
       </c>
       <c r="F68">
-        <v>356.2542358995669</v>
+        <v>3586.171932510611</v>
       </c>
       <c r="G68">
-        <v>566.7035752752383</v>
+        <v>8967.999221185697</v>
       </c>
       <c r="H68">
-        <v>-33.44243854425986</v>
+        <v>4775.886949418366</v>
       </c>
       <c r="I68">
-        <v>1450.046510214994</v>
+        <v>14596.64355326842</v>
       </c>
       <c r="J68">
-        <v>13293216.59456136</v>
+        <v>210363162.0978909</v>
       </c>
       <c r="K68">
-        <v>-1054116.22809093</v>
+        <v>150537465.4496809</v>
       </c>
       <c r="L68">
-        <v>26790674.79388333</v>
+        <v>269683715.4967304</v>
       </c>
       <c r="M68">
-        <v>75371575.51160669</v>
+        <v>1192743896.417698</v>
       </c>
       <c r="N68">
-        <v>-4447844.326386562</v>
+        <v>635192964.2726427</v>
       </c>
       <c r="O68">
-        <v>192856185.8585942</v>
+        <v>1941353592.584699</v>
       </c>
     </row>
     <row r="69">
@@ -3999,40 +3999,40 @@
         </is>
       </c>
       <c r="D69">
-        <v>173.4183679034386</v>
+        <v>2753.151176300233</v>
       </c>
       <c r="E69">
-        <v>-13.7516089169002</v>
+        <v>1979.453730317482</v>
       </c>
       <c r="F69">
-        <v>349.5011959474014</v>
+        <v>3521.14309020014</v>
       </c>
       <c r="G69">
-        <v>556.7241214471828</v>
+        <v>8838.427488202859</v>
       </c>
       <c r="H69">
-        <v>-32.8535287757126</v>
+        <v>4729.049559375929</v>
       </c>
       <c r="I69">
-        <v>1424.511693022079</v>
+        <v>14351.62329329732</v>
       </c>
       <c r="J69">
-        <v>13041234.68470647</v>
+        <v>207039721.6089541</v>
       </c>
       <c r="K69">
-        <v>-1034134.742159813</v>
+        <v>148856899.9736046</v>
       </c>
       <c r="L69">
-        <v>26282839.43644052</v>
+        <v>264793481.5261407</v>
       </c>
       <c r="M69">
-        <v>74044308.15247531</v>
+        <v>1175510855.93098</v>
       </c>
       <c r="N69">
-        <v>-4369519.327169776</v>
+        <v>628963591.3969985</v>
       </c>
       <c r="O69">
-        <v>189460055.1719365</v>
+        <v>1908765898.008544</v>
       </c>
     </row>
     <row r="70">
@@ -4052,40 +4052,40 @@
         </is>
       </c>
       <c r="D70">
-        <v>434.4318067093736</v>
+        <v>5757.521425241389</v>
       </c>
       <c r="E70">
-        <v>-26.40581408005138</v>
+        <v>3557.240284016741</v>
       </c>
       <c r="F70">
-        <v>850.078083122454</v>
+        <v>7848.397407370795</v>
       </c>
       <c r="G70">
-        <v>1401.928932099329</v>
+        <v>18579.75345858466</v>
       </c>
       <c r="H70">
-        <v>-63.41434515004669</v>
+        <v>8542.817974421212</v>
       </c>
       <c r="I70">
-        <v>3482.856745298585</v>
+        <v>32155.68592198094</v>
       </c>
       <c r="J70">
-        <v>32669706.29635156</v>
+        <v>432971368.6995774</v>
       </c>
       <c r="K70">
-        <v>-1985743.624633945</v>
+        <v>267508026.5983431</v>
       </c>
       <c r="L70">
-        <v>63926721.92889177</v>
+        <v>590207333.4316914</v>
       </c>
       <c r="M70">
-        <v>186456547.9692107</v>
+        <v>2471107209.99176</v>
       </c>
       <c r="N70">
-        <v>-8434107.904956209</v>
+        <v>1136194790.598021</v>
       </c>
       <c r="O70">
-        <v>463219947.1247118</v>
+        <v>4276706227.623466</v>
       </c>
     </row>
     <row r="71">
@@ -4105,40 +4105,40 @@
         </is>
       </c>
       <c r="D71">
-        <v>372.9115888772673</v>
+        <v>5781.727287168341</v>
       </c>
       <c r="E71">
-        <v>-29.57088336614647</v>
+        <v>4017.503565618735</v>
       </c>
       <c r="F71">
-        <v>751.5527211501685</v>
+        <v>7520.1650751198</v>
       </c>
       <c r="G71">
-        <v>960.9937280867418</v>
+        <v>14899.5199564726</v>
       </c>
       <c r="H71">
-        <v>-56.71037751500126</v>
+        <v>7704.678316608301</v>
       </c>
       <c r="I71">
-        <v>2458.932081157039</v>
+        <v>24604.49498540748</v>
       </c>
       <c r="J71">
-        <v>28043324.39515935</v>
+        <v>434791673.7223455</v>
       </c>
       <c r="K71">
-        <v>-2223760.00001758</v>
+        <v>302120285.6380941</v>
       </c>
       <c r="L71">
-        <v>56517516.18321388</v>
+        <v>565523933.8140825</v>
       </c>
       <c r="M71">
-        <v>127812165.8355367</v>
+        <v>1981636154.210856</v>
       </c>
       <c r="N71">
-        <v>-7542480.209495167</v>
+        <v>1024722216.108904</v>
       </c>
       <c r="O71">
-        <v>327037966.7938862</v>
+        <v>3272397833.059195</v>
       </c>
     </row>
     <row r="72">
@@ -4158,40 +4158,40 @@
         </is>
       </c>
       <c r="D72">
-        <v>271.268580536048</v>
+        <v>4399.229219368426</v>
       </c>
       <c r="E72">
-        <v>-21.51086690569907</v>
+        <v>3264.052562964644</v>
       </c>
       <c r="F72">
-        <v>546.7050259237438</v>
+        <v>5535.015693525609</v>
       </c>
       <c r="G72">
-        <v>694.4691151815515</v>
+        <v>11262.37626716091</v>
       </c>
       <c r="H72">
-        <v>-40.98216725395754</v>
+        <v>6218.62190155087</v>
       </c>
       <c r="I72">
-        <v>1776.965173427772</v>
+        <v>17990.5610071034</v>
       </c>
       <c r="J72">
-        <v>20399668.52489135</v>
+        <v>330826436.5257257</v>
       </c>
       <c r="K72">
-        <v>-1617638.702175478</v>
+        <v>245460016.7875048</v>
       </c>
       <c r="L72">
-        <v>41112764.65449149</v>
+        <v>416238715.1688178</v>
       </c>
       <c r="M72">
-        <v>92364392.31914635</v>
+        <v>1497896043.532402</v>
       </c>
       <c r="N72">
-        <v>-5450628.244776353</v>
+        <v>827076712.9062657</v>
       </c>
       <c r="O72">
-        <v>236336368.0658937</v>
+        <v>2392744613.944752</v>
       </c>
     </row>
     <row r="73">
@@ -4211,40 +4211,40 @@
         </is>
       </c>
       <c r="D73">
-        <v>604.0082982617715</v>
+        <v>8346.573351264147</v>
       </c>
       <c r="E73">
-        <v>-42.69420801891535</v>
+        <v>5177.232271792213</v>
       </c>
       <c r="F73">
-        <v>1200.830613622297</v>
+        <v>11388.98376647595</v>
       </c>
       <c r="G73">
-        <v>1548.689763535536</v>
+        <v>21400.78662313203</v>
       </c>
       <c r="H73">
-        <v>-81.46556071714882</v>
+        <v>9878.766923082656</v>
       </c>
       <c r="I73">
-        <v>3909.090112850674</v>
+        <v>37074.80749733046</v>
       </c>
       <c r="J73">
-        <v>45422028.03758345</v>
+        <v>627670662.588416</v>
       </c>
       <c r="K73">
-        <v>-3210647.137230455</v>
+        <v>389333044.071046</v>
       </c>
       <c r="L73">
-        <v>90303662.97501042</v>
+        <v>856462968.2227558</v>
       </c>
       <c r="M73">
-        <v>205975738.5502263</v>
+        <v>2846304620.87656</v>
       </c>
       <c r="N73">
-        <v>-10834919.57538079</v>
+        <v>1313876000.769993</v>
       </c>
       <c r="O73">
-        <v>519908985.0091397</v>
+        <v>4930949397.144951</v>
       </c>
     </row>
     <row r="74">
@@ -4264,40 +4264,40 @@
         </is>
       </c>
       <c r="D74">
-        <v>521.9219867141205</v>
+        <v>8155.258040944197</v>
       </c>
       <c r="E74">
-        <v>-41.3870060778146</v>
+        <v>5729.862715167244</v>
       </c>
       <c r="F74">
-        <v>1051.862964420234</v>
+        <v>10550.60207980269</v>
       </c>
       <c r="G74">
-        <v>980.8400800989752</v>
+        <v>15326.05284645519</v>
       </c>
       <c r="H74">
-        <v>-57.88155489318342</v>
+        <v>8013.465933119043</v>
       </c>
       <c r="I74">
-        <v>2509.713715033026</v>
+        <v>25173.42242972824</v>
       </c>
       <c r="J74">
-        <v>39249055.32288864</v>
+        <v>613283559.9370455</v>
       </c>
       <c r="K74">
-        <v>-3112344.244057731</v>
+        <v>430891406.0432917</v>
       </c>
       <c r="L74">
-        <v>79101146.78736587</v>
+        <v>793415827.0032403</v>
       </c>
       <c r="M74">
-        <v>130451730.6531637</v>
+        <v>2038365028.578541</v>
       </c>
       <c r="N74">
-        <v>-7698246.800793394</v>
+        <v>1065790969.104833</v>
       </c>
       <c r="O74">
-        <v>333791924.0993924</v>
+        <v>3348065183.153856</v>
       </c>
     </row>
     <row r="75">
@@ -4317,40 +4317,40 @@
         </is>
       </c>
       <c r="D75">
-        <v>318.5954544033222</v>
+        <v>5430.226718511087</v>
       </c>
       <c r="E75">
-        <v>-25.26376037684879</v>
+        <v>4339.740982187855</v>
       </c>
       <c r="F75">
-        <v>642.0859202144455</v>
+        <v>6550.389994506142</v>
       </c>
       <c r="G75">
-        <v>595.3645659758121</v>
+        <v>10147.55398651697</v>
       </c>
       <c r="H75">
-        <v>-35.13378735859569</v>
+        <v>6035.187738690443</v>
       </c>
       <c r="I75">
-        <v>1523.382503418291</v>
+        <v>15541.14362897751</v>
       </c>
       <c r="J75">
-        <v>23958696.76658422</v>
+        <v>408358479.4587519</v>
       </c>
       <c r="K75">
-        <v>-1899860.044099406</v>
+        <v>326352861.6015084</v>
       </c>
       <c r="L75">
-        <v>48285503.28604659</v>
+        <v>492595877.9768564</v>
       </c>
       <c r="M75">
-        <v>79183487.274783</v>
+        <v>1349624680.206757</v>
       </c>
       <c r="N75">
-        <v>-4672793.718693227</v>
+        <v>802679969.2458289</v>
       </c>
       <c r="O75">
-        <v>202609872.9546327</v>
+        <v>2066972102.654009</v>
       </c>
     </row>
     <row r="76">
@@ -4370,40 +4370,40 @@
         </is>
       </c>
       <c r="D76">
-        <v>750.2320052253166</v>
+        <v>10653.86335824187</v>
       </c>
       <c r="E76">
-        <v>-58.59888655784636</v>
+        <v>6694.512127102634</v>
       </c>
       <c r="F76">
-        <v>1509.165805229692</v>
+        <v>14482.60349287247</v>
       </c>
       <c r="G76">
-        <v>1403.175810284757</v>
+        <v>19926.16050267599</v>
       </c>
       <c r="H76">
-        <v>-81.56229408571875</v>
+        <v>9317.920509157588</v>
       </c>
       <c r="I76">
-        <v>3583.652303055574</v>
+        <v>34390.26724672849</v>
       </c>
       <c r="J76">
-        <v>56418197.02494904</v>
+        <v>801181178.403145</v>
       </c>
       <c r="K76">
-        <v>-4406694.868036607</v>
+        <v>503434006.4702458</v>
       </c>
       <c r="L76">
-        <v>113490777.719078</v>
+        <v>1089106265.267507</v>
       </c>
       <c r="M76">
-        <v>186622382.7678727</v>
+        <v>2650179346.855907</v>
       </c>
       <c r="N76">
-        <v>-10847785.11340059</v>
+        <v>1239283427.717959</v>
       </c>
       <c r="O76">
-        <v>476625756.3063914</v>
+        <v>4573905543.814889</v>
       </c>
     </row>
     <row r="77">
@@ -4423,40 +4423,40 @@
         </is>
       </c>
       <c r="D77">
-        <v>565.0595741338583</v>
+        <v>8941.983149294256</v>
       </c>
       <c r="E77">
-        <v>-44.80770043093585</v>
+        <v>6398.95058604467</v>
       </c>
       <c r="F77">
-        <v>1138.800920161337</v>
+        <v>11463.54340542116</v>
       </c>
       <c r="G77">
-        <v>714.2547167528863</v>
+        <v>11302.97394093043</v>
       </c>
       <c r="H77">
-        <v>-42.14975961348913</v>
+        <v>6019.372259375393</v>
       </c>
       <c r="I77">
-        <v>1827.5913627845</v>
+        <v>18397.13381306792</v>
       </c>
       <c r="J77">
-        <v>42493045.03444033</v>
+        <v>672446074.8100735</v>
       </c>
       <c r="K77">
-        <v>-3369583.880106805</v>
+        <v>481207483.021145</v>
       </c>
       <c r="L77">
-        <v>85638967.99705264</v>
+        <v>862069927.6310772</v>
       </c>
       <c r="M77">
-        <v>94995877.32813388</v>
+        <v>1503295534.143747</v>
       </c>
       <c r="N77">
-        <v>-5605918.028594054</v>
+        <v>800576510.4969273</v>
       </c>
       <c r="O77">
-        <v>243069651.2503386</v>
+        <v>2446818797.138033</v>
       </c>
     </row>
     <row r="78">
@@ -4476,40 +4476,40 @@
         </is>
       </c>
       <c r="D78">
-        <v>417.7885341112005</v>
+        <v>7108.358757827328</v>
       </c>
       <c r="E78">
-        <v>-33.12950410340297</v>
+        <v>5665.991304865</v>
       </c>
       <c r="F78">
-        <v>841.9961166182869</v>
+        <v>8588.214098069355</v>
       </c>
       <c r="G78">
-        <v>539.9056050504836</v>
+        <v>9186.089187979447</v>
       </c>
       <c r="H78">
-        <v>-31.86103071227875</v>
+        <v>5449.049959104736</v>
       </c>
       <c r="I78">
-        <v>1381.477500064712</v>
+        <v>14090.83047778473</v>
       </c>
       <c r="J78">
-        <v>31418115.55369638</v>
+        <v>534555686.9473738</v>
       </c>
       <c r="K78">
-        <v>-2491371.838080009</v>
+        <v>426088212.1171517</v>
       </c>
       <c r="L78">
-        <v>63318949.96581168</v>
+        <v>645842288.388914</v>
       </c>
       <c r="M78">
-        <v>71807445.47171432</v>
+        <v>1221749862.001266</v>
       </c>
       <c r="N78">
-        <v>-4237517.084733074</v>
+        <v>724723644.5609299</v>
       </c>
       <c r="O78">
-        <v>183736507.5086067</v>
+        <v>1874080453.54537</v>
       </c>
     </row>
     <row r="79">
@@ -4529,40 +4529,40 @@
         </is>
       </c>
       <c r="D79">
-        <v>634.757902256956</v>
+        <v>9537.057643135129</v>
       </c>
       <c r="E79">
-        <v>-50.33458989540249</v>
+        <v>6351.508969101562</v>
       </c>
       <c r="F79">
-        <v>1279.268445770391</v>
+        <v>12651.42581536369</v>
       </c>
       <c r="G79">
-        <v>814.5378109823686</v>
+        <v>12238.19983686828</v>
       </c>
       <c r="H79">
-        <v>-48.06768807224011</v>
+        <v>6065.458217683724</v>
       </c>
       <c r="I79">
-        <v>2084.189621848592</v>
+        <v>20611.75703438009</v>
       </c>
       <c r="J79">
-        <v>47734429.00762533</v>
+        <v>717196271.8214023</v>
       </c>
       <c r="K79">
-        <v>-3785211.494724163</v>
+        <v>477639825.9854068</v>
       </c>
       <c r="L79">
-        <v>96202266.39037931</v>
+        <v>951399872.7411644</v>
       </c>
       <c r="M79">
-        <v>108333528.860655</v>
+        <v>1627680578.303481</v>
       </c>
       <c r="N79">
-        <v>-6393002.513607934</v>
+        <v>806705942.9519353</v>
       </c>
       <c r="O79">
-        <v>277197219.7058628</v>
+        <v>2741363685.572552</v>
       </c>
     </row>
     <row r="80">
@@ -4582,40 +4582,40 @@
         </is>
       </c>
       <c r="D80">
-        <v>106.6654225461977</v>
+        <v>1844.061590440905</v>
       </c>
       <c r="E80">
-        <v>-8.458280362942812</v>
+        <v>1505.133657368321</v>
       </c>
       <c r="F80">
-        <v>214.9696897556374</v>
+        <v>2195.924251604285</v>
       </c>
       <c r="G80">
-        <v>74.7066357001186</v>
+        <v>1291.549165203779</v>
       </c>
       <c r="H80">
-        <v>-4.408604749028129</v>
+        <v>784.5021807112814</v>
       </c>
       <c r="I80">
-        <v>191.1547784646442</v>
+        <v>1952.65395004158</v>
       </c>
       <c r="J80">
-        <v>8021346.440896623</v>
+        <v>138675275.6627465</v>
       </c>
       <c r="K80">
-        <v>-636071.1415736622</v>
+        <v>113187556.1677549</v>
       </c>
       <c r="L80">
-        <v>16165935.63931368</v>
+        <v>165135699.6448939</v>
       </c>
       <c r="M80">
-        <v>9935982.548115773</v>
+        <v>171776038.9721026</v>
       </c>
       <c r="N80">
-        <v>-586344.4316207411</v>
+        <v>104338790.0346004</v>
       </c>
       <c r="O80">
-        <v>25423585.53579768</v>
+        <v>259702975.3555301</v>
       </c>
     </row>
     <row r="81">
@@ -4635,40 +4635,40 @@
         </is>
       </c>
       <c r="D81">
-        <v>90.84520596236823</v>
+        <v>1607.908134391179</v>
       </c>
       <c r="E81">
-        <v>-7.203779850271619</v>
+        <v>1358.404389117257</v>
       </c>
       <c r="F81">
-        <v>183.0861892761822</v>
+        <v>1872.832787168063</v>
       </c>
       <c r="G81">
-        <v>61.83504622700616</v>
+        <v>1094.444916114159</v>
       </c>
       <c r="H81">
-        <v>-3.649023622841647</v>
+        <v>688.0901149517709</v>
       </c>
       <c r="I81">
-        <v>158.2197411528674</v>
+        <v>1618.467891979235</v>
       </c>
       <c r="J81">
-        <v>6831650.33357606</v>
+        <v>120916299.6143507</v>
       </c>
       <c r="K81">
-        <v>-541731.448520276</v>
+        <v>102153368.4660069</v>
       </c>
       <c r="L81">
-        <v>13768264.51975819</v>
+        <v>140838898.4278252</v>
       </c>
       <c r="M81">
-        <v>8224061.148191819</v>
+        <v>145561173.8431831</v>
       </c>
       <c r="N81">
-        <v>-485320.1418379391</v>
+        <v>91515985.28858553</v>
       </c>
       <c r="O81">
-        <v>21043225.57333136</v>
+        <v>215256229.6332383</v>
       </c>
     </row>
     <row r="82">
@@ -4688,40 +4688,40 @@
         </is>
       </c>
       <c r="D82">
-        <v>136.1006334381682</v>
+        <v>2214.546139233366</v>
       </c>
       <c r="E82">
-        <v>-10.79241320865276</v>
+        <v>1651.285637114598</v>
       </c>
       <c r="F82">
-        <v>274.2923643608771</v>
+        <v>2778.890442344898</v>
       </c>
       <c r="G82">
-        <v>96.44114884562255</v>
+        <v>1569.231299252792</v>
       </c>
       <c r="H82">
-        <v>-5.691206715682126</v>
+        <v>870.7791043361211</v>
       </c>
       <c r="I82">
-        <v>246.7677237730493</v>
+        <v>2500.034846649716</v>
       </c>
       <c r="J82">
-        <v>10234903.73518368</v>
+        <v>166536084.2164893</v>
       </c>
       <c r="K82">
-        <v>-811600.2657038979</v>
+        <v>124178331.1966546</v>
       </c>
       <c r="L82">
-        <v>20627060.09230229</v>
+        <v>208975340.1547795</v>
       </c>
       <c r="M82">
-        <v>12826672.7964678</v>
+        <v>208707762.8006214</v>
       </c>
       <c r="N82">
-        <v>-756930.4931857227</v>
+        <v>115813620.8767041</v>
       </c>
       <c r="O82">
-        <v>32820107.26181556</v>
+        <v>332504634.6044122</v>
       </c>
     </row>
     <row r="83">
@@ -4741,40 +4741,40 @@
         </is>
       </c>
       <c r="D83">
-        <v>3.991716176127684</v>
+        <v>70.01130679053846</v>
       </c>
       <c r="E83">
-        <v>-0.3165323282937225</v>
+        <v>58.36749939691207</v>
       </c>
       <c r="F83">
-        <v>8.044762468391044</v>
+        <v>82.2566296019609</v>
       </c>
       <c r="G83">
-        <v>0.5115473908538007</v>
+        <v>8.972106166553102</v>
       </c>
       <c r="H83">
-        <v>-0.03018754941292878</v>
+        <v>5.566482834948771</v>
       </c>
       <c r="I83">
-        <v>1.308916232894551</v>
+        <v>13.38349493502628</v>
       </c>
       <c r="J83">
-        <v>300181.0481609779</v>
+        <v>5264920.281955283</v>
       </c>
       <c r="K83">
-        <v>-23803.54762001623</v>
+        <v>4389294.322147192</v>
       </c>
       <c r="L83">
-        <v>604974.1823854749</v>
+        <v>6185780.802697074</v>
       </c>
       <c r="M83">
-        <v>68035.80298355549</v>
+        <v>1193290.120151563</v>
       </c>
       <c r="N83">
-        <v>-4014.944071919528</v>
+        <v>740342.2170481866</v>
       </c>
       <c r="O83">
-        <v>174085.8589749753</v>
+        <v>1780004.826358495</v>
       </c>
     </row>
     <row r="84">
@@ -4794,40 +4794,40 @@
         </is>
       </c>
       <c r="D84">
-        <v>2.999099097621881</v>
+        <v>55.81694746323405</v>
       </c>
       <c r="E84">
-        <v>-0.2378204707617101</v>
+        <v>50.64910875521954</v>
       </c>
       <c r="F84">
-        <v>6.044277397232065</v>
+        <v>61.82911616967488</v>
       </c>
       <c r="G84">
-        <v>0.3908539039953398</v>
+        <v>7.274275078941829</v>
       </c>
       <c r="H84">
-        <v>-0.02306515828455687</v>
+        <v>4.912233613318368</v>
       </c>
       <c r="I84">
-        <v>1.00009310725998</v>
+        <v>10.23031685104081</v>
       </c>
       <c r="J84">
-        <v>225535.2512402629</v>
+        <v>4197490.266182661</v>
       </c>
       <c r="K84">
-        <v>-17884.33722175135</v>
+        <v>3808863.627501253</v>
       </c>
       <c r="L84">
-        <v>454535.7045492484</v>
+        <v>4649611.365075718</v>
       </c>
       <c r="M84">
-        <v>51983.56923138019</v>
+        <v>967478.5854992633</v>
       </c>
       <c r="N84">
-        <v>-3067.666051846064</v>
+        <v>653327.0705713429</v>
       </c>
       <c r="O84">
-        <v>133012.3832655773</v>
+        <v>1360632.141188427</v>
       </c>
     </row>
     <row r="85">
@@ -4847,40 +4847,40 @@
         </is>
       </c>
       <c r="D85">
-        <v>4.467609444021941</v>
+        <v>77.09933501371368</v>
       </c>
       <c r="E85">
-        <v>-0.3542693810949135</v>
+        <v>62.76286488264392</v>
       </c>
       <c r="F85">
-        <v>9.003860793921204</v>
+        <v>91.9615467858499</v>
       </c>
       <c r="G85">
-        <v>0.5731216266927552</v>
+        <v>9.890590673523565</v>
       </c>
       <c r="H85">
-        <v>-0.03382118203462903</v>
+        <v>5.991808469730614</v>
       </c>
       <c r="I85">
-        <v>1.466468628349382</v>
+        <v>14.9778774308661</v>
       </c>
       <c r="J85">
-        <v>335968.6977998942</v>
+        <v>5797947.092366267</v>
       </c>
       <c r="K85">
-        <v>-26641.41172771858</v>
+        <v>4719830.202039708</v>
       </c>
       <c r="L85">
-        <v>677099.3355636692</v>
+        <v>6915600.279842707</v>
       </c>
       <c r="M85">
-        <v>76225.17635013645</v>
+        <v>1315448.559578634</v>
       </c>
       <c r="N85">
-        <v>-4498.217210605661</v>
+        <v>796910.5264741717</v>
       </c>
       <c r="O85">
-        <v>195040.3275704678</v>
+        <v>1992057.698305191</v>
       </c>
     </row>
     <row r="86">
@@ -5218,40 +5218,40 @@
         </is>
       </c>
       <c r="D92">
-        <v>70.89371061040806</v>
+        <v>309.7289423863003</v>
       </c>
       <c r="E92">
-        <v>51.72861550672907</v>
+        <v>215.2189248313209</v>
       </c>
       <c r="F92">
-        <v>88.87937326625558</v>
+        <v>402.8575993988115</v>
       </c>
       <c r="G92">
-        <v>551.9102394964336</v>
+        <v>2411.251623022025</v>
       </c>
       <c r="H92">
-        <v>322.9349502980362</v>
+        <v>1343.583471406814</v>
       </c>
       <c r="I92">
-        <v>788.0336211011796</v>
+        <v>3571.867365573599</v>
       </c>
       <c r="J92">
-        <v>1193779.192968661</v>
+        <v>5215525.660842898</v>
       </c>
       <c r="K92">
-        <v>871058.1565178109</v>
+        <v>3624071.475234593</v>
       </c>
       <c r="L92">
-        <v>1496639.766430478</v>
+        <v>6783719.116276563</v>
       </c>
       <c r="M92">
-        <v>73404061.85302567</v>
+        <v>320696465.8619294</v>
       </c>
       <c r="N92">
-        <v>42950348.38963881</v>
+        <v>178696601.6971063</v>
       </c>
       <c r="O92">
-        <v>104808471.6064569</v>
+        <v>475058359.6212887</v>
       </c>
     </row>
     <row r="93">
@@ -5271,40 +5271,40 @@
         </is>
       </c>
       <c r="D93">
-        <v>54.75868394419028</v>
+        <v>244.7986752248992</v>
       </c>
       <c r="E93">
-        <v>42.35670012243911</v>
+        <v>181.6308501862731</v>
       </c>
       <c r="F93">
-        <v>66.49867966287569</v>
+        <v>308.0004340666331</v>
       </c>
       <c r="G93">
-        <v>423.9259822044121</v>
+        <v>1895.160938177811</v>
       </c>
       <c r="H93">
-        <v>262.9557083743219</v>
+        <v>1127.587105116808</v>
       </c>
       <c r="I93">
-        <v>586.3177952289719</v>
+        <v>2715.634902031464</v>
       </c>
       <c r="J93">
-        <v>922081.4789362205</v>
+        <v>4122164.89211207</v>
       </c>
       <c r="K93">
-        <v>713244.4733617528</v>
+        <v>3058481.886286661</v>
       </c>
       <c r="L93">
-        <v>1119771.266843164</v>
+        <v>5186419.309248025</v>
       </c>
       <c r="M93">
-        <v>56382155.63318681</v>
+        <v>252056404.7776488</v>
       </c>
       <c r="N93">
-        <v>34973109.21378481</v>
+        <v>149969084.9805354</v>
       </c>
       <c r="O93">
-        <v>77980266.76545326</v>
+        <v>361179441.9701847</v>
       </c>
     </row>
     <row r="94">
@@ -5324,40 +5324,40 @@
         </is>
       </c>
       <c r="D94">
-        <v>108.9687259484035</v>
+        <v>451.0897139743624</v>
       </c>
       <c r="E94">
-        <v>72.97205094551195</v>
+        <v>279.8029953583146</v>
       </c>
       <c r="F94">
-        <v>142.4090376913466</v>
+        <v>615.5164776572884</v>
       </c>
       <c r="G94">
-        <v>843.2877083010039</v>
+        <v>3490.895280501984</v>
       </c>
       <c r="H94">
-        <v>452.8495091014402</v>
+        <v>1736.399723611141</v>
       </c>
       <c r="I94">
-        <v>1255.146642357282</v>
+        <v>5424.9607522913</v>
       </c>
       <c r="J94">
-        <v>1834924.376245168</v>
+        <v>7595899.693614312</v>
       </c>
       <c r="K94">
-        <v>1228776.365871474</v>
+        <v>4711602.638838658</v>
       </c>
       <c r="L94">
-        <v>2398025.785684585</v>
+        <v>10364681.96727107</v>
       </c>
       <c r="M94">
-        <v>112157265.2040335</v>
+        <v>464289072.3067638</v>
       </c>
       <c r="N94">
-        <v>60228984.71049154</v>
+        <v>230941163.2402818</v>
       </c>
       <c r="O94">
-        <v>166934503.4335185</v>
+        <v>721519780.0547429</v>
       </c>
     </row>
     <row r="95">
@@ -5377,40 +5377,40 @@
         </is>
       </c>
       <c r="D95">
-        <v>136.1610218936238</v>
+        <v>597.2207493420226</v>
       </c>
       <c r="E95">
-        <v>100.3072000231572</v>
+        <v>419.6057178324342</v>
       </c>
       <c r="F95">
-        <v>169.8495780447139</v>
+        <v>772.6350838286609</v>
       </c>
       <c r="G95">
-        <v>791.7274804248713</v>
+        <v>3472.624342548035</v>
       </c>
       <c r="H95">
-        <v>467.7119611090891</v>
+        <v>1956.53565381834</v>
       </c>
       <c r="I95">
-        <v>1124.787313834789</v>
+        <v>5116.586985487669</v>
       </c>
       <c r="J95">
-        <v>2292815.447666733</v>
+        <v>10056600.19817036</v>
       </c>
       <c r="K95">
-        <v>1689072.941189943</v>
+        <v>7065740.68258037</v>
       </c>
       <c r="L95">
-        <v>2860097.044694935</v>
+        <v>13010402.1765908</v>
       </c>
       <c r="M95">
-        <v>105299754.8965079</v>
+        <v>461859037.5588887</v>
       </c>
       <c r="N95">
-        <v>62205690.82750886</v>
+        <v>260219241.9578392</v>
       </c>
       <c r="O95">
-        <v>149596712.7400269</v>
+        <v>680506069.06986</v>
       </c>
     </row>
     <row r="96">
@@ -5430,40 +5430,40 @@
         </is>
       </c>
       <c r="D96">
-        <v>85.65048800681426</v>
+        <v>392.9772858497877</v>
       </c>
       <c r="E96">
-        <v>71.09288186277985</v>
+        <v>314.0604841889348</v>
       </c>
       <c r="F96">
-        <v>99.66664873105965</v>
+        <v>474.0418061226815</v>
       </c>
       <c r="G96">
-        <v>495.9247209530446</v>
+        <v>2275.377004395302</v>
       </c>
       <c r="H96">
-        <v>330.0923708508183</v>
+        <v>1458.218700665107</v>
       </c>
       <c r="I96">
-        <v>657.2321370998264</v>
+        <v>3125.97557236395</v>
       </c>
       <c r="J96">
-        <v>1442268.56754675</v>
+        <v>6617344.516424579</v>
       </c>
       <c r="K96">
-        <v>1197133.037687348</v>
+        <v>5288464.49325743</v>
       </c>
       <c r="L96">
-        <v>1678286.697982312</v>
+        <v>7982389.973299813</v>
       </c>
       <c r="M96">
-        <v>65957987.88675493</v>
+        <v>302625141.5845751</v>
       </c>
       <c r="N96">
-        <v>43902285.32315883</v>
+        <v>193943087.1884593</v>
       </c>
       <c r="O96">
-        <v>87411874.23427692</v>
+        <v>415754751.1244053</v>
       </c>
     </row>
     <row r="97">
@@ -5483,40 +5483,40 @@
         </is>
       </c>
       <c r="D97">
-        <v>184.9351656205262</v>
+        <v>774.7152464051227</v>
       </c>
       <c r="E97">
-        <v>124.6930125106734</v>
+        <v>486.8037478721968</v>
       </c>
       <c r="F97">
-        <v>240.9722314862467</v>
+        <v>1053.129119108578</v>
       </c>
       <c r="G97">
-        <v>1070.702545194627</v>
+        <v>4485.299393134896</v>
       </c>
       <c r="H97">
-        <v>578.9151346672759</v>
+        <v>2260.095025227214</v>
       </c>
       <c r="I97">
-        <v>1588.910202978805</v>
+        <v>6944.068169535984</v>
       </c>
       <c r="J97">
-        <v>3114123.25388403</v>
+        <v>13045430.03421591</v>
       </c>
       <c r="K97">
-        <v>2099705.63766723</v>
+        <v>8197288.31041993</v>
       </c>
       <c r="L97">
-        <v>4057731.405996906</v>
+        <v>17733641.2366694</v>
       </c>
       <c r="M97">
-        <v>142403438.5108854</v>
+        <v>596544819.2869413</v>
       </c>
       <c r="N97">
-        <v>76995712.91074769</v>
+        <v>300592638.3552195</v>
       </c>
       <c r="O97">
-        <v>211325056.996181</v>
+        <v>923561066.548286</v>
       </c>
     </row>
     <row r="98">
@@ -5536,40 +5536,40 @@
         </is>
       </c>
       <c r="D98">
-        <v>653.9674328166136</v>
+        <v>2886.959839330943</v>
       </c>
       <c r="E98">
-        <v>489.5953998024117</v>
+        <v>2065.930235758961</v>
       </c>
       <c r="F98">
-        <v>808.7549579707122</v>
+        <v>3701.057011104981</v>
       </c>
       <c r="G98">
-        <v>2340.405437531038</v>
+        <v>10331.79355247579</v>
       </c>
       <c r="H98">
-        <v>1405.062870407624</v>
+        <v>5928.899389759119</v>
       </c>
       <c r="I98">
-        <v>3296.362411366938</v>
+        <v>15084.94642721469</v>
       </c>
       <c r="J98">
-        <v>11012157.60119895</v>
+        <v>48613516.73449362</v>
       </c>
       <c r="K98">
-        <v>8244296.937272817</v>
+        <v>34788199.23994516</v>
       </c>
       <c r="L98">
-        <v>13618624.73726882</v>
+        <v>62322099.00999656</v>
       </c>
       <c r="M98">
-        <v>311273923.191628</v>
+        <v>1374128542.479281</v>
       </c>
       <c r="N98">
-        <v>186873361.764214</v>
+        <v>788543618.8379629</v>
       </c>
       <c r="O98">
-        <v>438416200.7118027</v>
+        <v>2006297874.819554</v>
       </c>
     </row>
     <row r="99">
@@ -5589,40 +5589,40 @@
         </is>
       </c>
       <c r="D99">
-        <v>482.1464873066591</v>
+        <v>2210.110002825794</v>
       </c>
       <c r="E99">
-        <v>399.1733210350187</v>
+        <v>1761.653355638115</v>
       </c>
       <c r="F99">
-        <v>561.9677175748649</v>
+        <v>2670.222273693173</v>
       </c>
       <c r="G99">
-        <v>1763.025372097715</v>
+        <v>8081.527321447767</v>
       </c>
       <c r="H99">
-        <v>1170.481393402903</v>
+        <v>5165.631984256039</v>
       </c>
       <c r="I99">
-        <v>2340.312990941033</v>
+        <v>11120.13320407811</v>
       </c>
       <c r="J99">
-        <v>8118864.699756844</v>
+        <v>37216042.33758354</v>
       </c>
       <c r="K99">
-        <v>6721679.552908679</v>
+        <v>29664480.85559013</v>
       </c>
       <c r="L99">
-        <v>9462974.396243144</v>
+        <v>44963872.86671932</v>
       </c>
       <c r="M99">
-        <v>234482374.4889961</v>
+        <v>1074843133.752553</v>
       </c>
       <c r="N99">
-        <v>155674025.3225861</v>
+        <v>687029053.9060532</v>
       </c>
       <c r="O99">
-        <v>311261627.7951574</v>
+        <v>1478977716.142389</v>
       </c>
     </row>
     <row r="100">
@@ -5642,40 +5642,40 @@
         </is>
       </c>
       <c r="D100">
-        <v>679.8810634140494</v>
+        <v>2924.340755031123</v>
       </c>
       <c r="E100">
-        <v>478.8040187043862</v>
+        <v>1947.558380090037</v>
       </c>
       <c r="F100">
-        <v>867.8130378550079</v>
+        <v>3879.297106666017</v>
       </c>
       <c r="G100">
-        <v>2482.023960361387</v>
+        <v>10675.81406930325</v>
       </c>
       <c r="H100">
-        <v>1401.697385301856</v>
+        <v>5701.471546713062</v>
       </c>
       <c r="I100">
-        <v>3608.13031998833</v>
+        <v>16129.06109984399</v>
       </c>
       <c r="J100">
-        <v>11448517.22682916</v>
+        <v>49242973.97396905</v>
       </c>
       <c r="K100">
-        <v>8062580.870963153</v>
+        <v>32794935.56233608</v>
       </c>
       <c r="L100">
-        <v>14613103.74444046</v>
+        <v>65323483.97914907</v>
       </c>
       <c r="M100">
-        <v>330109186.7280644</v>
+        <v>1419883271.217332</v>
       </c>
       <c r="N100">
-        <v>186425752.2451469</v>
+        <v>758295715.7128372</v>
       </c>
       <c r="O100">
-        <v>479881332.5584479</v>
+        <v>2145165126.27925</v>
       </c>
     </row>
     <row r="101">
@@ -5695,40 +5695,40 @@
         </is>
       </c>
       <c r="D101">
-        <v>1073.128536701045</v>
+        <v>4960.696744430882</v>
       </c>
       <c r="E101">
-        <v>909.4536814638525</v>
+        <v>4048.94916349032</v>
       </c>
       <c r="F101">
-        <v>1231.91613309592</v>
+        <v>5907.239943838138</v>
       </c>
       <c r="G101">
-        <v>1893.696670209171</v>
+        <v>8753.895349502985</v>
       </c>
       <c r="H101">
-        <v>1286.95306560905</v>
+        <v>5729.601896890215</v>
       </c>
       <c r="I101">
-        <v>2475.841477910278</v>
+        <v>11872.06602787798</v>
       </c>
       <c r="J101">
-        <v>18070411.42950892</v>
+        <v>83533172.47947137</v>
       </c>
       <c r="K101">
-        <v>15314290.54216983</v>
+        <v>68180254.96401349</v>
       </c>
       <c r="L101">
-        <v>20744235.76520216</v>
+        <v>99472013.41429076</v>
       </c>
       <c r="M101">
-        <v>251861657.1378197</v>
+        <v>1164268081.483897</v>
       </c>
       <c r="N101">
-        <v>171164757.7260037</v>
+        <v>762037052.2863986</v>
       </c>
       <c r="O101">
-        <v>329286916.5620669</v>
+        <v>1578984781.707771</v>
       </c>
     </row>
     <row r="102">
@@ -5748,40 +5748,40 @@
         </is>
       </c>
       <c r="D102">
-        <v>935.5499353460502</v>
+        <v>4378.809887093606</v>
       </c>
       <c r="E102">
-        <v>820.8869766200262</v>
+        <v>3699.337320654972</v>
       </c>
       <c r="F102">
-        <v>1048.782450885886</v>
+        <v>5100.278150175398</v>
       </c>
       <c r="G102">
-        <v>1666.686988397232</v>
+        <v>7800.872179831419</v>
       </c>
       <c r="H102">
-        <v>1172.718804747808</v>
+        <v>5284.87180890625</v>
       </c>
       <c r="I102">
-        <v>2127.921014786807</v>
+        <v>10348.17949885494</v>
       </c>
       <c r="J102">
-        <v>15753725.36129215</v>
+        <v>73734779.68876928</v>
       </c>
       <c r="K102">
-        <v>13822915.79930463</v>
+        <v>62293141.14250922</v>
       </c>
       <c r="L102">
-        <v>17660447.69046745</v>
+        <v>85883583.77080359</v>
       </c>
       <c r="M102">
-        <v>221669369.4568319</v>
+        <v>1037515999.917579</v>
       </c>
       <c r="N102">
-        <v>155971601.0314584</v>
+        <v>702887950.5845313</v>
       </c>
       <c r="O102">
-        <v>283013494.9666454</v>
+        <v>1376307873.347707</v>
       </c>
     </row>
     <row r="103">
@@ -5801,40 +5801,40 @@
         </is>
       </c>
       <c r="D103">
-        <v>1350.195737800902</v>
+        <v>6046.476956977966</v>
       </c>
       <c r="E103">
-        <v>1049.186138805141</v>
+        <v>4508.580958109318</v>
       </c>
       <c r="F103">
-        <v>1635.374462628896</v>
+        <v>7587.332107436442</v>
       </c>
       <c r="G103">
-        <v>2483.666506521427</v>
+        <v>11122.41127716712</v>
       </c>
       <c r="H103">
-        <v>1547.649258591167</v>
+        <v>6650.585362348227</v>
       </c>
       <c r="I103">
-        <v>3426.074319695068</v>
+        <v>15895.29754946685</v>
       </c>
       <c r="J103">
-        <v>22735946.0288294</v>
+        <v>101816625.4785521</v>
       </c>
       <c r="K103">
-        <v>17667245.39133975</v>
+        <v>75919994.75360247</v>
       </c>
       <c r="L103">
-        <v>27538070.57620797</v>
+        <v>127763085.3571223</v>
       </c>
       <c r="M103">
-        <v>330327645.3673499</v>
+        <v>1479280699.863227</v>
       </c>
       <c r="N103">
-        <v>205837351.3926252</v>
+        <v>884527853.1923143</v>
       </c>
       <c r="O103">
-        <v>455667884.5194441</v>
+        <v>2114074574.079091</v>
       </c>
     </row>
     <row r="104">
@@ -5854,40 +5854,40 @@
         </is>
       </c>
       <c r="D104">
-        <v>1222.063244749208</v>
+        <v>5692.343261982418</v>
       </c>
       <c r="E104">
-        <v>1057.91985798275</v>
+        <v>4745.63120075452</v>
       </c>
       <c r="F104">
-        <v>1382.889267372711</v>
+        <v>6687.962169724624</v>
       </c>
       <c r="G104">
-        <v>329.5158705084067</v>
+        <v>1534.877555039908</v>
       </c>
       <c r="H104">
-        <v>228.7488266565694</v>
+        <v>1026.12457902752</v>
       </c>
       <c r="I104">
-        <v>424.6714647733252</v>
+        <v>2053.8063010363</v>
       </c>
       <c r="J104">
-        <v>20578322.97833193</v>
+        <v>95853368.18852197</v>
       </c>
       <c r="K104">
-        <v>17814312.48857155</v>
+        <v>79911683.78950502</v>
       </c>
       <c r="L104">
-        <v>23286472.37328907</v>
+        <v>112618594.9759927</v>
       </c>
       <c r="M104">
-        <v>43825610.77761809</v>
+        <v>204138714.8203078</v>
       </c>
       <c r="N104">
-        <v>30423593.94532374</v>
+        <v>136474569.0106601</v>
       </c>
       <c r="O104">
-        <v>56481304.81485225</v>
+        <v>273156238.0378278</v>
       </c>
     </row>
     <row r="105">
@@ -5907,40 +5907,40 @@
         </is>
       </c>
       <c r="D105">
-        <v>981.1317786361486</v>
+        <v>4716.312374648547</v>
       </c>
       <c r="E105">
-        <v>927.8342946252344</v>
+        <v>4279.650343553949</v>
       </c>
       <c r="F105">
-        <v>1039.654283722999</v>
+        <v>5224.316967471177</v>
       </c>
       <c r="G105">
-        <v>257.6487104796974</v>
+        <v>1238.520480130404</v>
       </c>
       <c r="H105">
-        <v>195.3864773983815</v>
+        <v>901.2232140670408</v>
       </c>
       <c r="I105">
-        <v>310.9371387289203</v>
+        <v>1562.475329646448</v>
       </c>
       <c r="J105">
-        <v>16521278.0204541</v>
+        <v>79417984.07670702</v>
       </c>
       <c r="K105">
-        <v>15623801.68719432</v>
+        <v>72065032.13510501</v>
       </c>
       <c r="L105">
-        <v>17506738.48361158</v>
+        <v>87972273.4152469</v>
       </c>
       <c r="M105">
-        <v>34267278.49379975</v>
+        <v>164723223.8573437</v>
       </c>
       <c r="N105">
-        <v>25986401.49398474</v>
+        <v>119862687.4709164</v>
       </c>
       <c r="O105">
-        <v>41354639.45094641</v>
+        <v>207809218.8429776</v>
       </c>
     </row>
     <row r="106">
@@ -5960,40 +5960,40 @@
         </is>
       </c>
       <c r="D106">
-        <v>1324.494077059028</v>
+        <v>6116.8988543818</v>
       </c>
       <c r="E106">
-        <v>1119.53690502002</v>
+        <v>4979.473509467724</v>
       </c>
       <c r="F106">
-        <v>1523.121317426594</v>
+        <v>7296.035433787966</v>
       </c>
       <c r="G106">
-        <v>366.4214814021191</v>
+        <v>1692.240968556339</v>
       </c>
       <c r="H106">
-        <v>248.3663596461094</v>
+        <v>1104.683287308532</v>
       </c>
       <c r="I106">
-        <v>479.8974277265941</v>
+        <v>2298.798261974738</v>
       </c>
       <c r="J106">
-        <v>22303155.76359696</v>
+        <v>103002459.8089352</v>
       </c>
       <c r="K106">
-        <v>18851881.94363211</v>
+        <v>83849354.42592694</v>
       </c>
       <c r="L106">
-        <v>25647839.86414644</v>
+        <v>122857940.6695556</v>
       </c>
       <c r="M106">
-        <v>48734057.02648184</v>
+        <v>225068048.8179931</v>
       </c>
       <c r="N106">
-        <v>33032725.83293255</v>
+        <v>146922877.2120348</v>
       </c>
       <c r="O106">
-        <v>63826357.88763702</v>
+        <v>305740168.8426402</v>
       </c>
     </row>
     <row r="107">
@@ -6013,22 +6013,22 @@
         </is>
       </c>
       <c r="D107">
-        <v>5646.474344533598</v>
+        <v>51335.84745831853</v>
       </c>
       <c r="E107">
-        <v>4010.85457503764</v>
+        <v>35828.24687516459</v>
       </c>
       <c r="F107">
-        <v>6972.852977765641</v>
+        <v>66630.27622617895</v>
       </c>
       <c r="G107">
-        <v>28503.11545069014</v>
+        <v>259140.7482936743</v>
       </c>
       <c r="H107">
-        <v>12524.50171933484</v>
+        <v>111879.1347812806</v>
       </c>
       <c r="I107">
-        <v>53785.90221072586</v>
+        <v>513960.2875325904</v>
       </c>
       <c r="J107">
         <v>0</v>
@@ -6040,13 +6040,13 @@
         <v>0</v>
       </c>
       <c r="M107">
-        <v>3790914354.941788</v>
+        <v>34465719523.05868</v>
       </c>
       <c r="N107">
-        <v>1665758728.671534</v>
+        <v>14879924925.91033</v>
       </c>
       <c r="O107">
-        <v>7153524994.02654</v>
+        <v>68356718241.83452</v>
       </c>
     </row>
     <row r="108">
@@ -6066,22 +6066,22 @@
         </is>
       </c>
       <c r="D108">
-        <v>3359.212760402233</v>
+        <v>32947.46135618048</v>
       </c>
       <c r="E108">
-        <v>2386.146300589806</v>
+        <v>25719.73164870038</v>
       </c>
       <c r="F108">
-        <v>4148.304812895383</v>
+        <v>40299.0895212977</v>
       </c>
       <c r="G108">
-        <v>16932.50715958917</v>
+        <v>166075.555523019</v>
       </c>
       <c r="H108">
-        <v>7440.281936892262</v>
+        <v>80197.11731851513</v>
       </c>
       <c r="I108">
-        <v>31951.95191359431</v>
+        <v>310400.1823933975</v>
       </c>
       <c r="J108">
         <v>0</v>
@@ -6093,13 +6093,13 @@
         <v>0</v>
       </c>
       <c r="M108">
-        <v>2252023452.22536</v>
+        <v>22088048884.56152</v>
       </c>
       <c r="N108">
-        <v>989557497.6066709</v>
+        <v>10666216603.36251</v>
       </c>
       <c r="O108">
-        <v>4249609604.508043</v>
+        <v>41283224258.32187</v>
       </c>
     </row>
     <row r="109">
@@ -6119,22 +6119,22 @@
         </is>
       </c>
       <c r="D109">
-        <v>8905.877206228399</v>
+        <v>77996.94355579496</v>
       </c>
       <c r="E109">
-        <v>6326.103008314508</v>
+        <v>51755.25223047928</v>
       </c>
       <c r="F109">
-        <v>10997.90216122807</v>
+        <v>103635.9611549014</v>
       </c>
       <c r="G109">
-        <v>44857.22473711741</v>
+        <v>392855.9023297211</v>
       </c>
       <c r="H109">
-        <v>19710.63090687565</v>
+        <v>161257.0444816425</v>
       </c>
       <c r="I109">
-        <v>84646.40671750616</v>
+        <v>797644.095198778</v>
       </c>
       <c r="J109">
         <v>0</v>
@@ -6146,13 +6146,13 @@
         <v>0</v>
       </c>
       <c r="M109">
-        <v>5966010890.036615</v>
+        <v>52249835009.85291</v>
       </c>
       <c r="N109">
-        <v>2621513910.614461</v>
+        <v>21447186916.05845</v>
       </c>
       <c r="O109">
-        <v>11257972093.42832</v>
+        <v>106086664661.4375</v>
       </c>
     </row>
     <row r="110">
@@ -6172,22 +6172,22 @@
         </is>
       </c>
       <c r="D110">
-        <v>6364.080663668506</v>
+        <v>58873.60139630693</v>
       </c>
       <c r="E110">
-        <v>4520.591166857031</v>
+        <v>42130.39321005585</v>
       </c>
       <c r="F110">
-        <v>7859.027793044395</v>
+        <v>75475.43691058055</v>
       </c>
       <c r="G110">
-        <v>26162.80152357957</v>
+        <v>242029.9851168186</v>
       </c>
       <c r="H110">
-        <v>11496.14866597874</v>
+        <v>107140.2491005799</v>
       </c>
       <c r="I110">
-        <v>49369.68685897848</v>
+        <v>474129.7249410157</v>
       </c>
       <c r="J110">
         <v>0</v>
@@ -6199,13 +6199,13 @@
         <v>0</v>
       </c>
       <c r="M110">
-        <v>3479652602.636083</v>
+        <v>32189988020.53687</v>
       </c>
       <c r="N110">
-        <v>1528987772.575173</v>
+        <v>14249653130.37713</v>
       </c>
       <c r="O110">
-        <v>6566168352.244138</v>
+        <v>63059253417.15509</v>
       </c>
     </row>
     <row r="111">
@@ -6225,22 +6225,22 @@
         </is>
       </c>
       <c r="D111">
-        <v>6370.941034319718</v>
+        <v>59126.73100357847</v>
       </c>
       <c r="E111">
-        <v>4525.464287203258</v>
+        <v>42510.78882046399</v>
       </c>
       <c r="F111">
-        <v>7867.499691259993</v>
+        <v>75620.14106292164</v>
       </c>
       <c r="G111">
-        <v>26299.71849753301</v>
+        <v>244079.5437748881</v>
       </c>
       <c r="H111">
-        <v>11556.31110256052</v>
+        <v>108556.3534803933</v>
       </c>
       <c r="I111">
-        <v>49628.05170280701</v>
+        <v>477010.539271239</v>
       </c>
       <c r="J111">
         <v>0</v>
@@ -6252,13 +6252,13 @@
         <v>0</v>
       </c>
       <c r="M111">
-        <v>3497862560.17189</v>
+        <v>32462579322.06011</v>
       </c>
       <c r="N111">
-        <v>1536989376.640549</v>
+        <v>14437995012.89231</v>
       </c>
       <c r="O111">
-        <v>6600530876.473332</v>
+        <v>63442401723.07479</v>
       </c>
     </row>
     <row r="112">
@@ -6278,22 +6278,22 @@
         </is>
       </c>
       <c r="D112">
-        <v>15104.03933926087</v>
+        <v>121280.6489397216</v>
       </c>
       <c r="E112">
-        <v>10909.10973564213</v>
+        <v>74932.31517796421</v>
       </c>
       <c r="F112">
-        <v>18597.59953447181</v>
+        <v>165324.3922861908</v>
       </c>
       <c r="G112">
-        <v>62734.26554557034</v>
+        <v>503736.2698299167</v>
       </c>
       <c r="H112">
-        <v>28029.12810701377</v>
+        <v>192526.0183804237</v>
       </c>
       <c r="I112">
-        <v>118035.2104105808</v>
+        <v>1049280.547918638</v>
       </c>
       <c r="J112">
         <v>0</v>
@@ -6305,13 +6305,13 @@
         <v>0</v>
       </c>
       <c r="M112">
-        <v>8343657317.560856</v>
+        <v>66996923887.37891</v>
       </c>
       <c r="N112">
-        <v>3727874038.232832</v>
+        <v>25605960444.59635</v>
       </c>
       <c r="O112">
-        <v>15698682984.60725</v>
+        <v>139554312873.1789</v>
       </c>
     </row>
     <row r="113">
@@ -6331,22 +6331,22 @@
         </is>
       </c>
       <c r="D113">
-        <v>9631.002719211361</v>
+        <v>87290.81466108223</v>
       </c>
       <c r="E113">
-        <v>6841.18070171443</v>
+        <v>60655.08484375716</v>
       </c>
       <c r="F113">
-        <v>11893.36245803295</v>
+        <v>113537.23605226</v>
       </c>
       <c r="G113">
-        <v>32278.32955656146</v>
+        <v>292555.3823456768</v>
       </c>
       <c r="H113">
-        <v>14183.36163033796</v>
+        <v>125752.1238756704</v>
       </c>
       <c r="I113">
-        <v>60909.80054647896</v>
+        <v>581461.3341638115</v>
       </c>
       <c r="J113">
         <v>0</v>
@@ -6358,13 +6358,13 @@
         <v>0</v>
       </c>
       <c r="M113">
-        <v>4293017831.022674</v>
+        <v>38909865851.97502</v>
       </c>
       <c r="N113">
-        <v>1886387096.834948</v>
+        <v>16725032475.46416</v>
       </c>
       <c r="O113">
-        <v>8101003472.681702</v>
+        <v>77334357443.78693</v>
       </c>
     </row>
     <row r="114">
@@ -6384,22 +6384,22 @@
         </is>
       </c>
       <c r="D114">
-        <v>6864.769883456749</v>
+        <v>65080.12797280386</v>
       </c>
       <c r="E114">
-        <v>4876.245248559148</v>
+        <v>48286.85842793956</v>
       </c>
       <c r="F114">
-        <v>8477.330844490209</v>
+        <v>81882.41887469502</v>
       </c>
       <c r="G114">
-        <v>22889.22099023566</v>
+        <v>216996.848624476</v>
       </c>
       <c r="H114">
-        <v>10057.71064367989</v>
+        <v>99596.14933314805</v>
       </c>
       <c r="I114">
-        <v>43192.38028524711</v>
+        <v>417194.5910321973</v>
       </c>
       <c r="J114">
         <v>0</v>
@@ -6411,13 +6411,13 @@
         <v>0</v>
       </c>
       <c r="M114">
-        <v>3044266391.701343</v>
+        <v>28860580867.05531</v>
       </c>
       <c r="N114">
-        <v>1337675515.609425</v>
+        <v>13246287861.30869</v>
       </c>
       <c r="O114">
-        <v>5744586577.937865</v>
+        <v>55486880607.28224</v>
       </c>
     </row>
     <row r="115">
@@ -6437,22 +6437,22 @@
         </is>
       </c>
       <c r="D115">
-        <v>14803.76568130983</v>
+        <v>121574.3649252456</v>
       </c>
       <c r="E115">
-        <v>10596.16312199098</v>
+        <v>75410.43480056316</v>
       </c>
       <c r="F115">
-        <v>18256.88289490419</v>
+        <v>165889.4507101566</v>
       </c>
       <c r="G115">
-        <v>49363.17229453719</v>
+        <v>405389.8482046796</v>
       </c>
       <c r="H115">
-        <v>21856.87472106608</v>
+        <v>155550.3069480236</v>
       </c>
       <c r="I115">
-        <v>93025.16867090882</v>
+        <v>845264.4529666146</v>
       </c>
       <c r="J115">
         <v>0</v>
@@ -6464,13 +6464,13 @@
         <v>0</v>
       </c>
       <c r="M115">
-        <v>6565301915.173446</v>
+        <v>53916849811.22239</v>
       </c>
       <c r="N115">
-        <v>2906964337.901789</v>
+        <v>20688190824.08714</v>
       </c>
       <c r="O115">
-        <v>12372347433.23087</v>
+        <v>112420172244.5597</v>
       </c>
     </row>
     <row r="116">
@@ -6490,22 +6490,22 @@
         </is>
       </c>
       <c r="D116">
-        <v>8010.434213225634</v>
+        <v>73170.07343442291</v>
       </c>
       <c r="E116">
-        <v>5690.043866622397</v>
+        <v>51409.0999368808</v>
       </c>
       <c r="F116">
-        <v>9892.116150489635</v>
+        <v>94661.42273864365</v>
       </c>
       <c r="G116">
-        <v>19809.34553162937</v>
+        <v>180945.4055367009</v>
       </c>
       <c r="H116">
-        <v>8704.388213246468</v>
+        <v>78643.4646258396</v>
       </c>
       <c r="I116">
-        <v>37380.59874422952</v>
+        <v>357709.1702240022</v>
       </c>
       <c r="J116">
         <v>0</v>
@@ -6517,13 +6517,13 @@
         <v>0</v>
       </c>
       <c r="M116">
-        <v>2634642955.706706</v>
+        <v>24065738936.38122</v>
       </c>
       <c r="N116">
-        <v>1157683632.36178</v>
+        <v>10459580795.23667</v>
       </c>
       <c r="O116">
-        <v>4971619632.982527</v>
+        <v>47575319639.7923</v>
       </c>
     </row>
     <row r="117">
@@ -6543,22 +6543,22 @@
         </is>
       </c>
       <c r="D117">
-        <v>4809.182103887862</v>
+        <v>47917.5856352688</v>
       </c>
       <c r="E117">
-        <v>3416.101600150112</v>
+        <v>38294.88544925611</v>
       </c>
       <c r="F117">
-        <v>5938.877555722187</v>
+        <v>57802.16734527414</v>
       </c>
       <c r="G117">
-        <v>11861.5517274533</v>
+        <v>118185.77637306</v>
       </c>
       <c r="H117">
-        <v>5212.06270456557</v>
+        <v>58427.81263206787</v>
       </c>
       <c r="I117">
-        <v>22382.96590363859</v>
+        <v>217849.9099714737</v>
       </c>
       <c r="J117">
         <v>0</v>
@@ -6570,13 +6570,13 @@
         <v>0</v>
       </c>
       <c r="M117">
-        <v>1577586379.751289</v>
+        <v>15718708257.61698</v>
       </c>
       <c r="N117">
-        <v>693204339.7072208</v>
+        <v>7770899080.065027</v>
       </c>
       <c r="O117">
-        <v>2976934465.183933</v>
+        <v>28974038026.206</v>
       </c>
     </row>
     <row r="118">
@@ -6596,22 +6596,22 @@
         </is>
       </c>
       <c r="D118">
-        <v>11295.0041930892</v>
+        <v>93977.76816211695</v>
       </c>
       <c r="E118">
-        <v>8031.545508316425</v>
+        <v>59052.31628042547</v>
       </c>
       <c r="F118">
-        <v>13945.71491461562</v>
+        <v>127751.0990775134</v>
       </c>
       <c r="G118">
-        <v>27853.25872659043</v>
+        <v>231747.332397499</v>
       </c>
       <c r="H118">
-        <v>12251.72696068801</v>
+        <v>90081.39899285974</v>
       </c>
       <c r="I118">
-        <v>52550.07941946424</v>
+        <v>481390.1935863707</v>
       </c>
       <c r="J118">
         <v>0</v>
@@ -6623,13 +6623,13 @@
         <v>0</v>
       </c>
       <c r="M118">
-        <v>3704483410.636528</v>
+        <v>30822395208.86737</v>
       </c>
       <c r="N118">
-        <v>1629479685.771506</v>
+        <v>11980826066.05035</v>
       </c>
       <c r="O118">
-        <v>6989160562.788745</v>
+        <v>64024895746.9873</v>
       </c>
     </row>
     <row r="119">
@@ -6649,22 +6649,22 @@
         </is>
       </c>
       <c r="D119">
-        <v>7663.070146594271</v>
+        <v>70890.44924557382</v>
       </c>
       <c r="E119">
-        <v>5443.301090362211</v>
+        <v>50729.7401673967</v>
       </c>
       <c r="F119">
-        <v>9463.154922900922</v>
+        <v>90880.92969852897</v>
       </c>
       <c r="G119">
-        <v>12595.47227241151</v>
+        <v>116519.7069543019</v>
       </c>
       <c r="H119">
-        <v>5534.553386087244</v>
+        <v>51580.18095231042</v>
       </c>
       <c r="I119">
-        <v>23767.88744773622</v>
+        <v>228258.7282802428</v>
       </c>
       <c r="J119">
         <v>0</v>
@@ -6676,13 +6676,13 @@
         <v>0</v>
       </c>
       <c r="M119">
-        <v>1675197812.230731</v>
+        <v>15497121024.92215</v>
       </c>
       <c r="N119">
-        <v>736095600.3496034</v>
+        <v>6860164066.657287</v>
       </c>
       <c r="O119">
-        <v>3161129030.548918</v>
+        <v>30358410861.27229</v>
       </c>
     </row>
     <row r="120">
@@ -6702,22 +6702,22 @@
         </is>
       </c>
       <c r="D120">
-        <v>5730.884853566849</v>
+        <v>57000.65186666905</v>
       </c>
       <c r="E120">
-        <v>4070.813809009029</v>
+        <v>45434.56638180374</v>
       </c>
       <c r="F120">
-        <v>7077.091841409316</v>
+        <v>68867.34598495335</v>
       </c>
       <c r="G120">
-        <v>9592.396575617324</v>
+        <v>95408.10393939198</v>
       </c>
       <c r="H120">
-        <v>4214.977398232179</v>
+        <v>47043.58376056548</v>
       </c>
       <c r="I120">
-        <v>18101.02846740442</v>
+        <v>176141.5307420951</v>
       </c>
       <c r="J120">
         <v>0</v>
@@ -6729,13 +6729,13 @@
         <v>0</v>
       </c>
       <c r="M120">
-        <v>1275788744.557104</v>
+        <v>12689277823.93913</v>
       </c>
       <c r="N120">
-        <v>560591993.9648799</v>
+        <v>6256796640.155209</v>
       </c>
       <c r="O120">
-        <v>2407436786.164788</v>
+        <v>23426823588.69865</v>
       </c>
     </row>
     <row r="121">
@@ -6755,22 +6755,22 @@
         </is>
       </c>
       <c r="D121">
-        <v>8607.659084033854</v>
+        <v>75602.58889704001</v>
       </c>
       <c r="E121">
-        <v>6114.270022493695</v>
+        <v>50349.9653074341</v>
       </c>
       <c r="F121">
-        <v>10629.63145025229</v>
+        <v>100290.9472366283</v>
       </c>
       <c r="G121">
-        <v>14298.32846879784</v>
+        <v>125584.7424471625</v>
       </c>
       <c r="H121">
-        <v>6282.80230632604</v>
+        <v>51737.79976893525</v>
       </c>
       <c r="I121">
-        <v>26981.2083570317</v>
+        <v>254568.6514513457</v>
       </c>
       <c r="J121">
         <v>0</v>
@@ -6782,13 +6782,13 @@
         <v>0</v>
       </c>
       <c r="M121">
-        <v>1901677686.350113</v>
+        <v>16702770745.47262</v>
       </c>
       <c r="N121">
-        <v>835612706.7413633</v>
+        <v>6881127369.268388</v>
       </c>
       <c r="O121">
-        <v>3588500711.485216</v>
+        <v>33857630643.02898</v>
       </c>
     </row>
     <row r="122">
@@ -6808,22 +6808,22 @@
         </is>
       </c>
       <c r="D122">
-        <v>3035.142459374827</v>
+        <v>30674.40606446256</v>
       </c>
       <c r="E122">
-        <v>2155.949761971351</v>
+        <v>25036.62633977785</v>
       </c>
       <c r="F122">
-        <v>3748.109146423978</v>
+        <v>36527.34405926554</v>
       </c>
       <c r="G122">
-        <v>2598.867380480646</v>
+        <v>26265.22952499884</v>
       </c>
       <c r="H122">
-        <v>1141.963552421604</v>
+        <v>13261.40119771724</v>
       </c>
       <c r="I122">
-        <v>4904.110465643605</v>
+        <v>47793.20006038727</v>
       </c>
       <c r="J122">
         <v>0</v>
@@ -6835,13 +6835,13 @@
         <v>0</v>
       </c>
       <c r="M122">
-        <v>345649361.6039259</v>
+        <v>3493275526.824846</v>
       </c>
       <c r="N122">
-        <v>151881152.4720733</v>
+        <v>1763766359.296392</v>
       </c>
       <c r="O122">
-        <v>652246691.9305995</v>
+        <v>6356495608.031507</v>
       </c>
     </row>
     <row r="123">
@@ -6861,22 +6861,22 @@
         </is>
       </c>
       <c r="D123">
-        <v>2561.140775695088</v>
+        <v>26499.51876802453</v>
       </c>
       <c r="E123">
-        <v>1819.252611579982</v>
+        <v>22387.51196915222</v>
       </c>
       <c r="F123">
-        <v>3162.762636400084</v>
+        <v>30865.67356145843</v>
       </c>
       <c r="G123">
-        <v>2161.176337499466</v>
+        <v>22361.1811814736</v>
       </c>
       <c r="H123">
-        <v>949.6385334306519</v>
+        <v>11686.14182451716</v>
       </c>
       <c r="I123">
-        <v>4078.179430945911</v>
+        <v>39799.30507333456</v>
       </c>
       <c r="J123">
         <v>0</v>
@@ -6888,13 +6888,13 @@
         <v>0</v>
       </c>
       <c r="M123">
-        <v>287436452.8874289</v>
+        <v>2974037097.135988</v>
       </c>
       <c r="N123">
-        <v>126301924.9462767</v>
+        <v>1554256862.660783</v>
       </c>
       <c r="O123">
-        <v>542397864.3158063</v>
+        <v>5293307574.753496</v>
       </c>
     </row>
     <row r="124">
@@ -6914,22 +6914,22 @@
         </is>
       </c>
       <c r="D124">
-        <v>3981.096065912365</v>
+        <v>37868.01689970486</v>
       </c>
       <c r="E124">
-        <v>2827.88805816276</v>
+        <v>28236.4459717883</v>
       </c>
       <c r="F124">
-        <v>4916.270908915475</v>
+        <v>47518.1204712103</v>
       </c>
       <c r="G124">
-        <v>3473.541204035408</v>
+        <v>33040.17658415614</v>
       </c>
       <c r="H124">
-        <v>1526.302374117094</v>
+        <v>15240.12041387843</v>
       </c>
       <c r="I124">
-        <v>6554.636030871216</v>
+        <v>63353.70656548745</v>
       </c>
       <c r="J124">
         <v>0</v>
@@ -6941,13 +6941,13 @@
         <v>0</v>
       </c>
       <c r="M124">
-        <v>461980980.1367093</v>
+        <v>4394343485.692767</v>
       </c>
       <c r="N124">
-        <v>202998215.7575735</v>
+        <v>2026936015.045831</v>
       </c>
       <c r="O124">
-        <v>871766592.1058718</v>
+        <v>8426042973.209831</v>
       </c>
     </row>
     <row r="125">
@@ -6967,22 +6967,22 @@
         </is>
       </c>
       <c r="D125">
-        <v>1243.917789006613</v>
+        <v>12753.97398738799</v>
       </c>
       <c r="E125">
-        <v>883.5909012564545</v>
+        <v>10632.81922796083</v>
       </c>
       <c r="F125">
-        <v>1536.118882319452</v>
+        <v>14984.7069327293</v>
       </c>
       <c r="G125">
-        <v>189.9463980517847</v>
+        <v>1947.533382961878</v>
       </c>
       <c r="H125">
-        <v>83.46399863189156</v>
+        <v>1004.376129534289</v>
       </c>
       <c r="I125">
-        <v>358.4323407933128</v>
+        <v>3496.476505705104</v>
       </c>
       <c r="J125">
         <v>0</v>
@@ -6994,13 +6994,13 @@
         <v>0</v>
       </c>
       <c r="M125">
-        <v>25262870.94088736</v>
+        <v>259021939.9339298</v>
       </c>
       <c r="N125">
-        <v>11100711.81804158</v>
+        <v>133582025.2280604</v>
       </c>
       <c r="O125">
-        <v>47671501.3255106</v>
+        <v>465031375.2587788</v>
       </c>
     </row>
     <row r="126">
@@ -7020,22 +7020,22 @@
         </is>
       </c>
       <c r="D126">
-        <v>967.9019229665148</v>
+        <v>10530.57139032041</v>
       </c>
       <c r="E126">
-        <v>687.5288222422002</v>
+        <v>9555.593414603371</v>
       </c>
       <c r="F126">
-        <v>1195.265823225775</v>
+        <v>11664.84287328765</v>
       </c>
       <c r="G126">
-        <v>144.776892092941</v>
+        <v>1575.142441272095</v>
       </c>
       <c r="H126">
-        <v>63.61614880572994</v>
+        <v>884.1666457094599</v>
       </c>
       <c r="I126">
-        <v>273.1966536765094</v>
+        <v>2666.181845678441</v>
       </c>
       <c r="J126">
         <v>0</v>
@@ -7047,13 +7047,13 @@
         <v>0</v>
       </c>
       <c r="M126">
-        <v>19255326.64836115</v>
+        <v>209493944.6891887</v>
       </c>
       <c r="N126">
-        <v>8460947.791162083</v>
+        <v>117594163.8793582</v>
       </c>
       <c r="O126">
-        <v>36335154.93897575</v>
+        <v>354602185.4752326</v>
       </c>
     </row>
     <row r="127">
@@ -7073,22 +7073,22 @@
         </is>
       </c>
       <c r="D127">
-        <v>1403.586145772859</v>
+        <v>14159.88815434378</v>
       </c>
       <c r="E127">
-        <v>997.0079682877816</v>
+        <v>11526.88472379629</v>
       </c>
       <c r="F127">
-        <v>1733.293952814603</v>
+        <v>16889.44809649098</v>
       </c>
       <c r="G127">
-        <v>212.825249455226</v>
+        <v>2147.058616802557</v>
       </c>
       <c r="H127">
-        <v>93.51715279444343</v>
+        <v>1081.196413916769</v>
       </c>
       <c r="I127">
-        <v>401.6051534778794</v>
+        <v>3913.294328370307</v>
       </c>
       <c r="J127">
         <v>0</v>
@@ -7100,13 +7100,13 @@
         <v>0</v>
       </c>
       <c r="M127">
-        <v>28305758.17754506</v>
+        <v>285558796.0347401</v>
       </c>
       <c r="N127">
-        <v>12437781.32166098</v>
+        <v>143799123.0509303</v>
       </c>
       <c r="O127">
-        <v>53413485.41255796</v>
+        <v>520468145.6732509</v>
       </c>
     </row>
   </sheetData>
